--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75914E77-D7F6-4560-AE98-95E3FB86BF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F66CDF-2D0F-4C9E-A568-0C83DADAFFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -190,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="206">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -260,9 +258,6 @@
   </si>
   <si>
     <t xml:space="preserve">1. La proiectarea TCs se consideră o metodă care poate avea următoarea semnătură: </t>
-  </si>
-  <si>
-    <t>addMovie(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
   </si>
   <si>
     <t>2. Metoda este definită la nivelul repository, service sau ui.</t>
@@ -1069,6 +1064,12 @@
   </si>
   <si>
     <t>TC05_ECP</t>
+  </si>
+  <si>
+    <t>Stanca Vlad Tudor</t>
+  </si>
+  <si>
+    <t>updateProduct(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
   </si>
 </sst>
 </file>
@@ -1800,7 +1801,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1939,258 +1940,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2198,13 +1947,9 @@
     <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2213,10 +1958,10 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2227,6 +1972,261 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2608,12 +2608,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="77"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="83"/>
       <c r="H1" s="51" t="s">
         <v>1</v>
       </c>
@@ -2621,11 +2621,11 @@
       <c r="J1" s="51"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="91" t="s">
+      <c r="H2" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
@@ -2641,7 +2641,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J4" s="2">
         <v>236</v>
@@ -2651,8 +2651,12 @@
       <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J5" s="2">
+        <v>236</v>
+      </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="37"/>
@@ -2736,17 +2740,17 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C20" s="47" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -2763,7 +2767,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -2780,21 +2784,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="48"/>
-      <c r="B24" s="90" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="90"/>
-      <c r="K24" s="90"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
+      <c r="B24" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="80"/>
+      <c r="G24" s="80"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="80"/>
+      <c r="J24" s="80"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="80"/>
+      <c r="N24" s="80"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C26" s="50"/>
@@ -2833,266 +2837,266 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="81" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="83"/>
+      <c r="B3" s="86" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="88"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="G5" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="G5" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="D6" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="E6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="G6" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="86" t="s">
+      <c r="H6" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="I6" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="65" t="s">
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="23" t="s">
         <v>30</v>
-      </c>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="23" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="78" t="s">
-        <v>133</v>
+      <c r="C7" s="97" t="s">
+        <v>132</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="68"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="94"/>
       <c r="I7" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="K7" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="K7" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>143</v>
-      </c>
       <c r="M7" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="78"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G8" s="23">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J8" s="61">
+        <v>10.4</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M8" s="52" t="s">
         <v>144</v>
-      </c>
-      <c r="J8" s="145">
-        <v>10.4</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M8" s="52" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="143" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="144" t="s">
-        <v>176</v>
+      <c r="C9" s="85" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>175</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="19">
         <v>2</v>
       </c>
-      <c r="H9" s="148" t="s">
-        <v>173</v>
+      <c r="H9" s="64" t="s">
+        <v>172</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="145">
+        <v>54</v>
+      </c>
+      <c r="J9" s="61">
         <v>10.4</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M9" s="52" t="s">
         <v>147</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M9" s="52" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="143"/>
+      <c r="C10" s="85"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G10" s="19">
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J10" s="149">
+        <v>143</v>
+      </c>
+      <c r="J10" s="2">
         <v>-40</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M10" s="164" t="s">
-        <v>149</v>
+        <v>145</v>
+      </c>
+      <c r="M10" s="78" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="78" t="s">
-        <v>136</v>
+      <c r="C11" s="97" t="s">
+        <v>135</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="19">
         <v>4</v>
       </c>
-      <c r="H11" s="152" t="s">
-        <v>175</v>
+      <c r="H11" s="67" t="s">
+        <v>174</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J11" s="149">
+        <v>143</v>
+      </c>
+      <c r="J11" s="2">
         <v>40</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M11" s="164" t="s">
-        <v>150</v>
+        <v>145</v>
+      </c>
+      <c r="M11" s="78" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="78"/>
+      <c r="C12" s="97"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G12" s="19">
         <v>5</v>
       </c>
-      <c r="H12" s="152" t="s">
-        <v>174</v>
+      <c r="H12" s="67" t="s">
+        <v>173</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="J12" s="149">
+        <v>143</v>
+      </c>
+      <c r="J12" s="2">
         <v>40</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M12" s="164" t="s">
-        <v>151</v>
+        <v>54</v>
+      </c>
+      <c r="M12" s="78" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>138</v>
+      <c r="C13" s="99" t="s">
+        <v>137</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="19">
@@ -3100,36 +3104,36 @@
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="146"/>
+      <c r="J13" s="62"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
-      <c r="M13" s="165"/>
+      <c r="M13" s="79"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="80"/>
+      <c r="C14" s="100"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G14" s="19">
         <v>8</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="146"/>
+      <c r="J14" s="62"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
-      <c r="M14" s="165"/>
+      <c r="M14" s="79"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="78" t="s">
-        <v>50</v>
+      <c r="C15" s="97" t="s">
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -3138,7 +3142,7 @@
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
-      <c r="J15" s="147"/>
+      <c r="J15" s="63"/>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="21"/>
@@ -3147,7 +3151,7 @@
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="78"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19">
@@ -3155,7 +3159,7 @@
       </c>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
-      <c r="J16" s="147"/>
+      <c r="J16" s="63"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="21"/>
@@ -3164,15 +3168,15 @@
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="78" t="s">
-        <v>50</v>
+      <c r="C17" s="97" t="s">
+        <v>49</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="G17" s="19"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
-      <c r="J17" s="147"/>
+      <c r="J17" s="63"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
       <c r="M17" s="21"/>
@@ -3181,7 +3185,7 @@
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="78"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -3196,8 +3200,8 @@
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="78" t="s">
-        <v>50</v>
+      <c r="C19" s="97" t="s">
+        <v>49</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -3213,22 +3217,22 @@
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="78"/>
+      <c r="C20" s="97"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
+        <v>65</v>
+      </c>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="M24" s="151"/>
+      <c r="M24" s="66"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="M26" s="150"/>
+      <c r="M26" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3277,110 +3281,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="153" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="83"/>
+      <c r="B3" s="105" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="88"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="3"/>
-      <c r="G5" s="85" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
     </row>
     <row r="6" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="G6" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="G6" s="86" t="s">
+      <c r="H6" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="86" t="s">
+      <c r="I6" s="91" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="86" t="s">
+      <c r="J6" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="67" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="94" t="s">
+      <c r="K6" s="107" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="95"/>
-      <c r="M6" s="95"/>
-      <c r="N6" s="95"/>
-      <c r="O6" s="56" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="79">
+      <c r="B7" s="99">
         <v>1</v>
       </c>
-      <c r="C7" s="100" t="s">
+      <c r="C7" s="102" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="O7" s="55" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="101"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="M7" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="N7" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="O7" s="55" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="99"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="G8" s="23">
         <v>1</v>
@@ -3389,198 +3393,198 @@
         <v>1</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J8" s="16"/>
       <c r="K8" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L8" s="34">
         <v>10</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O8" s="57" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="99"/>
-      <c r="C9" s="101"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G9" s="154">
+        <v>155</v>
+      </c>
+      <c r="G9" s="68">
         <v>2</v>
       </c>
       <c r="H9" s="17">
         <v>2</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K9" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L9" s="34">
         <v>10</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O9" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="99"/>
-      <c r="C10" s="101"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G10" s="154">
+        <v>156</v>
+      </c>
+      <c r="G10" s="68">
         <v>3</v>
       </c>
       <c r="H10" s="17">
         <v>3</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L10" s="34">
         <v>10</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O10" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="99"/>
-      <c r="C11" s="101"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="103"/>
       <c r="D11" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G11" s="154">
+        <v>157</v>
+      </c>
+      <c r="G11" s="68">
         <v>4</v>
       </c>
       <c r="H11" s="17">
         <v>4</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L11" s="34">
         <v>10</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O11" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="80"/>
-      <c r="C12" s="102"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="104"/>
       <c r="D12" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" s="154">
+        <v>158</v>
+      </c>
+      <c r="G12" s="68">
         <v>5</v>
       </c>
       <c r="H12" s="17">
         <v>5</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J12" s="16"/>
       <c r="K12" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L12" s="34">
         <v>10</v>
       </c>
       <c r="M12" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N12" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O12" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="79">
+      <c r="B13" s="99">
         <v>2</v>
       </c>
-      <c r="C13" s="100" t="s">
-        <v>135</v>
+      <c r="C13" s="102" t="s">
+        <v>134</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G13" s="154">
+        <v>159</v>
+      </c>
+      <c r="G13" s="68">
         <v>6</v>
       </c>
       <c r="H13" s="17">
         <v>6</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L13" s="34">
         <v>10</v>
       </c>
       <c r="M13" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O13" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="99"/>
-      <c r="C14" s="101"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="103"/>
       <c r="D14" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G14" s="23">
         <v>7</v>
@@ -3589,30 +3593,30 @@
         <v>7</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J14" s="16"/>
       <c r="K14" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L14" s="34">
         <v>0</v>
       </c>
       <c r="M14" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N14" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O14" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="99"/>
-      <c r="C15" s="101"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="103"/>
       <c r="D15" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G15" s="23">
         <v>8</v>
@@ -3621,30 +3625,30 @@
         <v>8</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J15" s="16"/>
       <c r="K15" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L15" s="34">
         <v>-1</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N15" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O15" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="99"/>
-      <c r="C16" s="101"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="103"/>
       <c r="D16" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G16" s="23">
         <v>9</v>
@@ -3653,30 +3657,30 @@
         <v>9</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J16" s="16"/>
       <c r="K16" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L16" s="34">
         <v>1</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N16" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O16" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="99"/>
-      <c r="C17" s="101"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="103"/>
       <c r="D17" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G17" s="23">
         <v>10</v>
@@ -3685,30 +3689,30 @@
         <v>10</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J17" s="16"/>
       <c r="K17" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="L17" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="M17" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="N17" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="O17" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="L17" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="M17" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="N17" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="O17" s="57" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="80"/>
-      <c r="C18" s="102"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="104"/>
       <c r="D18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G18" s="23">
         <v>11</v>
@@ -3717,36 +3721,36 @@
         <v>11</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K18" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M18" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N18" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O18" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="79">
+      <c r="B19" s="99">
         <v>3</v>
       </c>
-      <c r="C19" s="100" t="s">
-        <v>136</v>
+      <c r="C19" s="102" t="s">
+        <v>135</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G19" s="23">
         <v>12</v>
@@ -3755,30 +3759,30 @@
         <v>12</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J19" s="16"/>
       <c r="K19" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="L19" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="M19" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="N19" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="O19" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="L19" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="M19" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="N19" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="O19" s="57" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="99"/>
-      <c r="C20" s="101"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="103"/>
       <c r="D20" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G20" s="23">
         <v>13</v>
@@ -3787,30 +3791,30 @@
         <v>13</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J20" s="16"/>
       <c r="K20" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L20" s="34">
         <v>10</v>
       </c>
       <c r="M20" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N20" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O20" s="57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="99"/>
-      <c r="C21" s="101"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="103"/>
       <c r="D21" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G21" s="23">
         <v>14</v>
@@ -3819,32 +3823,32 @@
         <v>14</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K21" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L21" s="34">
         <v>10</v>
       </c>
       <c r="M21" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N21" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O21" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="99"/>
-      <c r="C22" s="101"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="103"/>
       <c r="D22" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G22" s="23">
         <v>15</v>
@@ -3853,30 +3857,30 @@
         <v>15</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J22" s="16"/>
       <c r="K22" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L22" s="34">
         <v>10</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N22" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O22" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="99"/>
-      <c r="C23" s="101"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="103"/>
       <c r="D23" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G23" s="23">
         <v>16</v>
@@ -3885,30 +3889,30 @@
         <v>16</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J23" s="16"/>
       <c r="K23" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L23" s="34">
         <v>10</v>
       </c>
       <c r="M23" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N23" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O23" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="80"/>
-      <c r="C24" s="102"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G24" s="23">
         <v>17</v>
@@ -3917,34 +3921,34 @@
         <v>17</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J24" s="16"/>
       <c r="K24" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L24" s="34">
         <v>10</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O24" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="79">
+      <c r="B25" s="99">
         <v>4</v>
       </c>
-      <c r="C25" s="100" t="s">
-        <v>138</v>
+      <c r="C25" s="102" t="s">
+        <v>137</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G25" s="23">
         <v>18</v>
@@ -3953,32 +3957,32 @@
         <v>18</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K25" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L25" s="34">
         <v>10</v>
       </c>
       <c r="M25" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N25" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O25" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="99"/>
-      <c r="C26" s="101"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="103"/>
       <c r="D26" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G26" s="23">
         <v>19</v>
@@ -3987,182 +3991,182 @@
         <v>19</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J26" s="16"/>
       <c r="K26" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L26" s="34">
         <v>10</v>
       </c>
       <c r="M26" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N26" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O26" s="57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="99"/>
-      <c r="C27" s="101"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="103"/>
       <c r="D27" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G27" s="154">
+        <v>184</v>
+      </c>
+      <c r="G27" s="68">
         <v>20</v>
       </c>
       <c r="H27" s="17">
         <v>20</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K27" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L27" s="34">
         <v>10</v>
       </c>
       <c r="M27" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N27" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O27" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="99"/>
-      <c r="C28" s="101"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="103"/>
       <c r="D28" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G28" s="154">
+        <v>185</v>
+      </c>
+      <c r="G28" s="68">
         <v>21</v>
       </c>
       <c r="H28" s="17">
         <v>21</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J28" s="16"/>
       <c r="K28" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L28" s="34">
         <v>10</v>
       </c>
       <c r="M28" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N28" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O28" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="99"/>
-      <c r="C29" s="101"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="103"/>
       <c r="D29" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G29" s="154">
+        <v>186</v>
+      </c>
+      <c r="G29" s="68">
         <v>22</v>
       </c>
       <c r="H29" s="17">
         <v>22</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J29" s="16"/>
       <c r="K29" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L29" s="34">
         <v>10</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O29" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="80"/>
-      <c r="C30" s="102"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="104"/>
       <c r="D30" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G30" s="154">
+        <v>187</v>
+      </c>
+      <c r="G30" s="68">
         <v>23</v>
       </c>
       <c r="H30" s="17">
         <v>23</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J30" s="16"/>
       <c r="K30" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L30" s="34">
         <v>10</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N30" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O30" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G31" s="154">
+      <c r="G31" s="68">
         <v>24</v>
       </c>
       <c r="H31" s="17">
         <v>24</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J31" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K31" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L31" s="34">
         <v>10</v>
       </c>
       <c r="M31" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N31" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O31" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4210,114 +4214,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="111" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="111"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="142"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="142"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="142"/>
-      <c r="M3" s="142"/>
-      <c r="N3" s="142"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="86" t="s">
+      <c r="C4" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="D4" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="E4" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="F4" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="119"/>
+    </row>
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="112"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="J5" s="26"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="69"/>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="115"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="J5" s="26"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="163"/>
-      <c r="M5" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="113" t="s">
-        <v>110</v>
+      <c r="C6" s="109" t="s">
+        <v>109</v>
       </c>
       <c r="D6" s="30" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" s="61">
+        <v>10.4</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J6" s="29"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="75"/>
+      <c r="M6" s="54" t="s">
         <v>144</v>
-      </c>
-      <c r="G6" s="145">
-        <v>10.4</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="160"/>
-      <c r="L6" s="161"/>
-      <c r="M6" s="54" t="s">
-        <v>145</v>
       </c>
       <c r="N6" s="24"/>
     </row>
@@ -4325,30 +4329,30 @@
       <c r="B7" s="12">
         <v>2</v>
       </c>
-      <c r="C7" s="113"/>
+      <c r="C7" s="109"/>
       <c r="D7" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="145">
+        <v>54</v>
+      </c>
+      <c r="G7" s="61">
         <v>10.4</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="54" t="s">
         <v>147</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="158"/>
-      <c r="L7" s="159"/>
-      <c r="M7" s="54" t="s">
-        <v>148</v>
       </c>
       <c r="N7" s="12"/>
     </row>
@@ -4356,30 +4360,30 @@
       <c r="B8" s="24">
         <v>3</v>
       </c>
-      <c r="C8" s="113"/>
+      <c r="C8" s="109"/>
       <c r="D8" s="31" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G8" s="149">
+        <v>143</v>
+      </c>
+      <c r="G8" s="2">
         <v>-40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="157" t="s">
-        <v>149</v>
+      <c r="M8" s="71" t="s">
+        <v>148</v>
       </c>
       <c r="N8" s="12"/>
     </row>
@@ -4387,30 +4391,30 @@
       <c r="B9" s="24">
         <v>4</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="109"/>
       <c r="D9" s="30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G9" s="149">
+        <v>143</v>
+      </c>
+      <c r="G9" s="2">
         <v>40</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="155"/>
-      <c r="L9" s="156"/>
-      <c r="M9" s="157" t="s">
-        <v>150</v>
+      <c r="K9" s="69"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="71" t="s">
+        <v>149</v>
       </c>
       <c r="N9" s="12"/>
     </row>
@@ -4418,30 +4422,30 @@
       <c r="B10" s="12">
         <v>5</v>
       </c>
-      <c r="C10" s="113"/>
+      <c r="C10" s="109"/>
       <c r="D10" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G10" s="149">
+        <v>143</v>
+      </c>
+      <c r="G10" s="2">
         <v>40</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="155"/>
-      <c r="L10" s="156"/>
-      <c r="M10" s="157" t="s">
-        <v>151</v>
+      <c r="K10" s="69"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="71" t="s">
+        <v>150</v>
       </c>
       <c r="N10" s="12"/>
     </row>
@@ -4449,30 +4453,30 @@
       <c r="B11" s="24">
         <v>6</v>
       </c>
-      <c r="C11" s="113"/>
+      <c r="C11" s="109"/>
       <c r="D11" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="F11" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="I11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="J11" s="12"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="141"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="132"/>
       <c r="M11" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N11" s="12"/>
     </row>
@@ -4480,31 +4484,31 @@
       <c r="B12" s="24">
         <v>7</v>
       </c>
-      <c r="C12" s="113"/>
+      <c r="C12" s="109"/>
       <c r="D12" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" s="12" t="str">
         <f>"TC" &amp; (B12 - 6) &amp; "_BVA"</f>
         <v>TC1_BVA</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" s="34">
         <v>10</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I12" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J12" s="12"/>
       <c r="K12" s="58"/>
       <c r="L12" s="59"/>
       <c r="M12" s="57" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="N12" s="12"/>
     </row>
@@ -4512,29 +4516,29 @@
       <c r="B13" s="12">
         <v>8</v>
       </c>
-      <c r="C13" s="113"/>
+      <c r="C13" s="109"/>
       <c r="D13" s="31"/>
       <c r="E13" s="12" t="str">
         <f t="shared" ref="E13:E35" si="0">"TC" &amp; (B13 - 6) &amp; "_BVA"</f>
         <v>TC2_BVA</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13" s="34">
         <v>10</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I13" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J13" s="12"/>
       <c r="K13" s="58"/>
       <c r="L13" s="59"/>
       <c r="M13" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N13" s="12"/>
     </row>
@@ -4542,29 +4546,29 @@
       <c r="B14" s="24">
         <v>9</v>
       </c>
-      <c r="C14" s="113"/>
+      <c r="C14" s="109"/>
       <c r="D14" s="31"/>
       <c r="E14" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC3_BVA</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G14" s="34">
         <v>10</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I14" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J14" s="12"/>
       <c r="K14" s="58"/>
       <c r="L14" s="59"/>
       <c r="M14" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N14" s="12"/>
     </row>
@@ -4572,29 +4576,29 @@
       <c r="B15" s="12">
         <v>10</v>
       </c>
-      <c r="C15" s="113"/>
+      <c r="C15" s="109"/>
       <c r="D15" s="31"/>
       <c r="E15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC4_BVA</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G15" s="34">
         <v>10</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I15" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J15" s="12"/>
       <c r="K15" s="58"/>
       <c r="L15" s="59"/>
       <c r="M15" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N15" s="12"/>
     </row>
@@ -4602,29 +4606,29 @@
       <c r="B16" s="24">
         <v>11</v>
       </c>
-      <c r="C16" s="113"/>
+      <c r="C16" s="109"/>
       <c r="D16" s="31"/>
       <c r="E16" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC5_BVA</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G16" s="34">
         <v>10</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I16" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="58"/>
       <c r="L16" s="59"/>
       <c r="M16" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N16" s="12"/>
     </row>
@@ -4632,29 +4636,29 @@
       <c r="B17" s="24">
         <v>12</v>
       </c>
-      <c r="C17" s="113"/>
+      <c r="C17" s="109"/>
       <c r="D17" s="31"/>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC6_BVA</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G17" s="34">
         <v>10</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I17" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J17" s="12"/>
       <c r="K17" s="58"/>
       <c r="L17" s="59"/>
       <c r="M17" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N17" s="12"/>
     </row>
@@ -4662,29 +4666,29 @@
       <c r="B18" s="12">
         <v>13</v>
       </c>
-      <c r="C18" s="113"/>
+      <c r="C18" s="109"/>
       <c r="D18" s="31"/>
       <c r="E18" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC7_BVA</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G18" s="34">
         <v>0</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I18" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J18" s="12"/>
       <c r="K18" s="58"/>
       <c r="L18" s="59"/>
       <c r="M18" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N18" s="12"/>
     </row>
@@ -4692,29 +4696,29 @@
       <c r="B19" s="24">
         <v>14</v>
       </c>
-      <c r="C19" s="113"/>
+      <c r="C19" s="109"/>
       <c r="D19" s="31"/>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC8_BVA</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G19" s="34">
         <v>-1</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I19" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J19" s="12"/>
       <c r="K19" s="58"/>
       <c r="L19" s="59"/>
       <c r="M19" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N19" s="12"/>
     </row>
@@ -4722,29 +4726,29 @@
       <c r="B20" s="24">
         <v>15</v>
       </c>
-      <c r="C20" s="113"/>
+      <c r="C20" s="109"/>
       <c r="D20" s="31"/>
       <c r="E20" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC9_BVA</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G20" s="34">
         <v>1</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J20" s="12"/>
       <c r="K20" s="58"/>
       <c r="L20" s="59"/>
       <c r="M20" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N20" s="12"/>
     </row>
@@ -4752,29 +4756,29 @@
       <c r="B21" s="12">
         <v>16</v>
       </c>
-      <c r="C21" s="113"/>
+      <c r="C21" s="109"/>
       <c r="D21" s="31"/>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC10_BVA</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I21" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="58"/>
       <c r="L21" s="59"/>
       <c r="M21" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N21" s="12"/>
     </row>
@@ -4782,29 +4786,29 @@
       <c r="B22" s="24">
         <v>17</v>
       </c>
-      <c r="C22" s="113"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="31"/>
       <c r="E22" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC11_BVA</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I22" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J22" s="12"/>
       <c r="K22" s="58"/>
       <c r="L22" s="59"/>
       <c r="M22" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N22" s="12"/>
     </row>
@@ -4812,29 +4816,29 @@
       <c r="B23" s="12">
         <v>18</v>
       </c>
-      <c r="C23" s="113"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="31"/>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC12_BVA</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H23" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I23" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J23" s="12"/>
       <c r="K23" s="58"/>
       <c r="L23" s="59"/>
       <c r="M23" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N23" s="12"/>
     </row>
@@ -4842,29 +4846,29 @@
       <c r="B24" s="24">
         <v>19</v>
       </c>
-      <c r="C24" s="113"/>
+      <c r="C24" s="109"/>
       <c r="D24" s="31"/>
       <c r="E24" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC13_BVA</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G24" s="34">
         <v>10</v>
       </c>
       <c r="H24" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I24" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J24" s="12"/>
       <c r="K24" s="58"/>
       <c r="L24" s="59"/>
       <c r="M24" s="57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N24" s="12"/>
     </row>
@@ -4872,29 +4876,29 @@
       <c r="B25" s="24">
         <v>20</v>
       </c>
-      <c r="C25" s="113"/>
+      <c r="C25" s="109"/>
       <c r="D25" s="31"/>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC14_BVA</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G25" s="34">
         <v>10</v>
       </c>
       <c r="H25" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I25" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J25" s="12"/>
       <c r="K25" s="58"/>
       <c r="L25" s="59"/>
       <c r="M25" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N25" s="12"/>
     </row>
@@ -4902,29 +4906,29 @@
       <c r="B26" s="12">
         <v>21</v>
       </c>
-      <c r="C26" s="113"/>
+      <c r="C26" s="109"/>
       <c r="D26" s="31"/>
       <c r="E26" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC15_BVA</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G26" s="34">
         <v>10</v>
       </c>
       <c r="H26" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I26" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J26" s="12"/>
       <c r="K26" s="58"/>
       <c r="L26" s="59"/>
       <c r="M26" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N26" s="12"/>
     </row>
@@ -4932,29 +4936,29 @@
       <c r="B27" s="24">
         <v>22</v>
       </c>
-      <c r="C27" s="113"/>
+      <c r="C27" s="109"/>
       <c r="D27" s="31"/>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC16_BVA</v>
       </c>
       <c r="F27" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G27" s="34">
         <v>10</v>
       </c>
       <c r="H27" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I27" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J27" s="12"/>
       <c r="K27" s="58"/>
       <c r="L27" s="59"/>
       <c r="M27" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N27" s="12"/>
     </row>
@@ -4962,29 +4966,29 @@
       <c r="B28" s="24">
         <v>23</v>
       </c>
-      <c r="C28" s="113"/>
+      <c r="C28" s="109"/>
       <c r="D28" s="31"/>
       <c r="E28" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC17_BVA</v>
       </c>
       <c r="F28" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G28" s="34">
         <v>10</v>
       </c>
       <c r="H28" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I28" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J28" s="12"/>
       <c r="K28" s="58"/>
       <c r="L28" s="59"/>
       <c r="M28" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N28" s="12"/>
     </row>
@@ -4992,29 +4996,29 @@
       <c r="B29" s="12">
         <v>24</v>
       </c>
-      <c r="C29" s="113"/>
+      <c r="C29" s="109"/>
       <c r="D29" s="31"/>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC18_BVA</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G29" s="34">
         <v>10</v>
       </c>
       <c r="H29" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I29" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J29" s="12"/>
       <c r="K29" s="58"/>
       <c r="L29" s="59"/>
       <c r="M29" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N29" s="12"/>
     </row>
@@ -5022,29 +5026,29 @@
       <c r="B30" s="24">
         <v>25</v>
       </c>
-      <c r="C30" s="113"/>
+      <c r="C30" s="109"/>
       <c r="D30" s="31"/>
       <c r="E30" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC19_BVA</v>
       </c>
       <c r="F30" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G30" s="34">
         <v>10</v>
       </c>
       <c r="H30" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I30" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J30" s="12"/>
       <c r="K30" s="58"/>
       <c r="L30" s="59"/>
       <c r="M30" s="57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N30" s="12"/>
     </row>
@@ -5052,29 +5056,29 @@
       <c r="B31" s="12">
         <v>26</v>
       </c>
-      <c r="C31" s="113"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="31"/>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC20_BVA</v>
       </c>
       <c r="F31" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G31" s="34">
         <v>10</v>
       </c>
       <c r="H31" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I31" s="34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J31" s="12"/>
       <c r="K31" s="58"/>
       <c r="L31" s="59"/>
       <c r="M31" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N31" s="12"/>
     </row>
@@ -5082,29 +5086,29 @@
       <c r="B32" s="24">
         <v>27</v>
       </c>
-      <c r="C32" s="113"/>
+      <c r="C32" s="109"/>
       <c r="D32" s="31"/>
       <c r="E32" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC21_BVA</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G32" s="34">
         <v>10</v>
       </c>
       <c r="H32" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I32" s="34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J32" s="11"/>
-      <c r="K32" s="133"/>
-      <c r="L32" s="134"/>
+      <c r="K32" s="129"/>
+      <c r="L32" s="130"/>
       <c r="M32" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N32" s="12"/>
     </row>
@@ -5112,29 +5116,29 @@
       <c r="B33" s="24">
         <v>28</v>
       </c>
-      <c r="C33" s="113"/>
+      <c r="C33" s="109"/>
       <c r="D33" s="31"/>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC22_BVA</v>
       </c>
       <c r="F33" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G33" s="34">
         <v>10</v>
       </c>
       <c r="H33" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I33" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J33" s="11"/>
-      <c r="K33" s="133"/>
-      <c r="L33" s="134"/>
+      <c r="K33" s="129"/>
+      <c r="L33" s="130"/>
       <c r="M33" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N33" s="12"/>
     </row>
@@ -5142,29 +5146,29 @@
       <c r="B34" s="12">
         <v>29</v>
       </c>
-      <c r="C34" s="113"/>
+      <c r="C34" s="109"/>
       <c r="D34" s="31"/>
       <c r="E34" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC23_BVA</v>
       </c>
       <c r="F34" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G34" s="34">
         <v>10</v>
       </c>
       <c r="H34" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I34" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J34" s="11"/>
-      <c r="K34" s="133"/>
-      <c r="L34" s="134"/>
+      <c r="K34" s="129"/>
+      <c r="L34" s="130"/>
       <c r="M34" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N34" s="12"/>
     </row>
@@ -5172,29 +5176,29 @@
       <c r="B35" s="24">
         <v>30</v>
       </c>
-      <c r="C35" s="114"/>
+      <c r="C35" s="110"/>
       <c r="D35" s="32"/>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
         <v>TC24_BVA</v>
       </c>
       <c r="F35" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G35" s="34">
         <v>10</v>
       </c>
       <c r="H35" s="34" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I35" s="34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J35" s="25"/>
-      <c r="K35" s="127"/>
-      <c r="L35" s="128"/>
+      <c r="K35" s="135"/>
+      <c r="L35" s="136"/>
       <c r="M35" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N35" s="25"/>
     </row>
@@ -5215,7 +5219,7 @@
     </row>
     <row r="37" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C37" s="27"/>
       <c r="D37" s="28"/>
@@ -5225,102 +5229,102 @@
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="112"/>
+      <c r="K37" s="143"/>
+      <c r="L37" s="143"/>
       <c r="M37" s="7"/>
     </row>
     <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M38" s="7"/>
     </row>
     <row r="39" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="106" t="s">
+      <c r="C39" s="120" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="121"/>
+      <c r="E39" s="121"/>
+      <c r="F39" s="122"/>
+      <c r="G39" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="D39" s="108"/>
-      <c r="E39" s="108"/>
-      <c r="F39" s="109"/>
-      <c r="G39" s="39" t="s">
+      <c r="H39" s="120" t="s">
         <v>121</v>
       </c>
-      <c r="H39" s="106" t="s">
+      <c r="I39" s="123"/>
+      <c r="J39" s="121"/>
+      <c r="K39" s="121"/>
+      <c r="L39" s="122"/>
+      <c r="M39" s="120" t="s">
         <v>122</v>
       </c>
-      <c r="I39" s="107"/>
-      <c r="J39" s="108"/>
-      <c r="K39" s="108"/>
-      <c r="L39" s="109"/>
-      <c r="M39" s="106" t="s">
+      <c r="N39" s="123"/>
+      <c r="O39" s="121"/>
+      <c r="P39" s="122"/>
+    </row>
+    <row r="40" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="124" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="125" t="s">
         <v>123</v>
       </c>
-      <c r="N39" s="107"/>
-      <c r="O39" s="108"/>
-      <c r="P39" s="109"/>
-    </row>
-    <row r="40" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="121" t="s">
+      <c r="D40" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="D40" s="105" t="s">
+      <c r="E40" s="126" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="105" t="s">
+      <c r="F40" s="127" t="s">
         <v>126</v>
       </c>
-      <c r="F40" s="104" t="s">
+      <c r="G40" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G40" s="126" t="s">
+      <c r="H40" s="137" t="s">
         <v>128</v>
       </c>
-      <c r="H40" s="122" t="s">
-        <v>129</v>
-      </c>
-      <c r="I40" s="123"/>
-      <c r="J40" s="105" t="s">
+      <c r="I40" s="138"/>
+      <c r="J40" s="126" t="s">
+        <v>123</v>
+      </c>
+      <c r="K40" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="K40" s="105" t="s">
+      <c r="L40" s="127" t="s">
         <v>125</v>
       </c>
-      <c r="L40" s="104" t="s">
-        <v>126</v>
-      </c>
-      <c r="M40" s="110" t="s">
-        <v>129</v>
-      </c>
-      <c r="N40" s="105" t="s">
+      <c r="M40" s="141" t="s">
+        <v>128</v>
+      </c>
+      <c r="N40" s="126" t="s">
+        <v>123</v>
+      </c>
+      <c r="O40" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="O40" s="105" t="s">
+      <c r="P40" s="127" t="s">
         <v>125</v>
       </c>
-      <c r="P40" s="104" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="120"/>
-      <c r="C41" s="121"/>
-      <c r="D41" s="105"/>
-      <c r="E41" s="105"/>
-      <c r="F41" s="104"/>
-      <c r="G41" s="126"/>
-      <c r="H41" s="124"/>
-      <c r="I41" s="125"/>
-      <c r="J41" s="105"/>
-      <c r="K41" s="105"/>
-      <c r="L41" s="104"/>
-      <c r="M41" s="111"/>
-      <c r="N41" s="105"/>
-      <c r="O41" s="105"/>
-      <c r="P41" s="104"/>
+      <c r="B41" s="124"/>
+      <c r="C41" s="125"/>
+      <c r="D41" s="126"/>
+      <c r="E41" s="126"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="128"/>
+      <c r="H41" s="139"/>
+      <c r="I41" s="140"/>
+      <c r="J41" s="126"/>
+      <c r="K41" s="126"/>
+      <c r="L41" s="127"/>
+      <c r="M41" s="142"/>
+      <c r="N41" s="126"/>
+      <c r="O41" s="126"/>
+      <c r="P41" s="127"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B42" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C42" s="38">
         <v>8</v>
@@ -5333,10 +5337,10 @@
       </c>
       <c r="F42" s="41"/>
       <c r="G42" s="46"/>
-      <c r="H42" s="118" t="s">
-        <v>130</v>
-      </c>
-      <c r="I42" s="119"/>
+      <c r="H42" s="133" t="s">
+        <v>129</v>
+      </c>
+      <c r="I42" s="134"/>
       <c r="J42" s="2">
         <v>3</v>
       </c>
@@ -5347,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N42" s="2">
         <v>5</v>
@@ -5364,10 +5368,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="O40:O41"/>
-    <mergeCell ref="P40:P41"/>
     <mergeCell ref="H42:I42"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="K34:L34"/>
@@ -5376,8 +5376,6 @@
     <mergeCell ref="J40:J41"/>
     <mergeCell ref="K40:K41"/>
     <mergeCell ref="L40:L41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="N40:N41"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="H39:L39"/>
@@ -5388,6 +5386,10 @@
     <mergeCell ref="E40:E41"/>
     <mergeCell ref="F40:F41"/>
     <mergeCell ref="G40:G41"/>
+    <mergeCell ref="O40:O41"/>
+    <mergeCell ref="P40:P41"/>
+    <mergeCell ref="M40:M41"/>
+    <mergeCell ref="N40:N41"/>
     <mergeCell ref="C6:C35"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B3:N3"/>
@@ -5397,6 +5399,8 @@
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K11:L11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5427,366 +5431,366 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="83"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="88"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
+      <c r="E5" s="89"/>
+      <c r="G5" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="G5" s="85" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="D6" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="E6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="G6" s="91" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="86" t="s">
+      <c r="H6" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="I6" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="65" t="s">
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="96"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="66"/>
-      <c r="P6" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" s="69"/>
+      <c r="Q6" s="119"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="78" t="s">
+      <c r="C7" s="97" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="23" t="s">
+      <c r="J7" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="K7" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="L7" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="M7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="N7" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="65" t="s">
+      <c r="O7" s="118"/>
+      <c r="P7" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="O7" s="66"/>
-      <c r="P7" s="65" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q7" s="66"/>
+      <c r="Q7" s="118"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="78"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="23">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="K8" s="2">
         <v>2012</v>
       </c>
       <c r="L8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="61" t="s">
+      <c r="O8" s="145" t="s">
         <v>46</v>
       </c>
-      <c r="O8" s="62" t="s">
+      <c r="P8" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="P8" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="62"/>
+      <c r="Q8" s="145"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="78" t="s">
-        <v>49</v>
+      <c r="C9" s="97" t="s">
+        <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="23">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="144" t="s">
+        <v>49</v>
+      </c>
+      <c r="O9" s="145" t="s">
         <v>51</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="O9" s="62" t="s">
-        <v>52</v>
-      </c>
-      <c r="P9" s="61" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="62"/>
+      <c r="P9" s="144" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q9" s="145"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="78"/>
+      <c r="C10" s="97"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" s="36">
         <v>3</v>
       </c>
       <c r="H10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="14" t="s">
-        <v>55</v>
-      </c>
       <c r="J10" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K10" s="14">
         <v>2012</v>
       </c>
       <c r="L10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="N10" s="150" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="73" t="s">
-        <v>46</v>
-      </c>
-      <c r="O10" s="74"/>
-      <c r="P10" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q10" s="74"/>
+      <c r="O10" s="151"/>
+      <c r="P10" s="150" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q10" s="151"/>
     </row>
     <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="78" t="s">
-        <v>57</v>
+      <c r="C11" s="97" t="s">
+        <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="36">
         <v>4</v>
       </c>
       <c r="H11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>51</v>
-      </c>
       <c r="M11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="73" t="s">
-        <v>50</v>
-      </c>
-      <c r="O11" s="74"/>
-      <c r="P11" s="73" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q11" s="74"/>
+        <v>49</v>
+      </c>
+      <c r="N11" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="O11" s="151"/>
+      <c r="P11" s="150" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q11" s="151"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="78"/>
+      <c r="C12" s="97"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G12" s="13">
         <v>5</v>
       </c>
       <c r="H12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="I12" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="L12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="M12" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="9"/>
+      <c r="P12" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q12" s="72"/>
+      <c r="Q12" s="149"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>63</v>
+      <c r="C13" s="99" t="s">
+        <v>62</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" s="4"/>
       <c r="G13" s="13">
         <v>6</v>
       </c>
       <c r="H13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="M13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="N13" s="71" t="s">
-        <v>50</v>
-      </c>
-      <c r="O13" s="72"/>
-      <c r="P13" s="71" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q13" s="72"/>
+        <v>49</v>
+      </c>
+      <c r="N13" s="148" t="s">
+        <v>49</v>
+      </c>
+      <c r="O13" s="149"/>
+      <c r="P13" s="148" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q13" s="149"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="80"/>
+      <c r="C14" s="100"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G14" s="19">
         <v>7</v>
@@ -5795,33 +5799,33 @@
         <v>10</v>
       </c>
       <c r="I14" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M14" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="N14" s="88" t="s">
-        <v>65</v>
-      </c>
-      <c r="O14" s="89"/>
-      <c r="P14" s="63"/>
-      <c r="Q14" s="64"/>
+        <v>64</v>
+      </c>
+      <c r="N14" s="152" t="s">
+        <v>64</v>
+      </c>
+      <c r="O14" s="153"/>
+      <c r="P14" s="146"/>
+      <c r="Q14" s="147"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="78" t="s">
-        <v>50</v>
+      <c r="C15" s="97" t="s">
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -5829,23 +5833,23 @@
         <v>8</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="63"/>
-      <c r="Q15" s="64"/>
+      <c r="N15" s="144"/>
+      <c r="O15" s="145"/>
+      <c r="P15" s="146"/>
+      <c r="Q15" s="147"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="78"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19"/>
@@ -5855,17 +5859,17 @@
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="62"/>
-      <c r="P16" s="63"/>
-      <c r="Q16" s="64"/>
+      <c r="N16" s="144"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="146"/>
+      <c r="Q16" s="147"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="78" t="s">
-        <v>50</v>
+      <c r="C17" s="97" t="s">
+        <v>49</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -5876,16 +5880,16 @@
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="62"/>
-      <c r="P17" s="63"/>
-      <c r="Q17" s="64"/>
+      <c r="N17" s="144"/>
+      <c r="O17" s="145"/>
+      <c r="P17" s="146"/>
+      <c r="Q17" s="147"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="78"/>
+      <c r="C18" s="97"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -5895,17 +5899,17 @@
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="63"/>
-      <c r="Q18" s="64"/>
+      <c r="N18" s="144"/>
+      <c r="O18" s="145"/>
+      <c r="P18" s="146"/>
+      <c r="Q18" s="147"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="78" t="s">
-        <v>50</v>
+      <c r="C19" s="97" t="s">
+        <v>49</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -5916,25 +5920,25 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="63"/>
-      <c r="Q19" s="64"/>
+      <c r="N19" s="144"/>
+      <c r="O19" s="145"/>
+      <c r="P19" s="146"/>
+      <c r="Q19" s="147"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="78"/>
+      <c r="C20" s="97"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
+        <v>65</v>
+      </c>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -6011,123 +6015,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="83"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="88"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="106" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="3"/>
+      <c r="G5" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="3"/>
-      <c r="G5" s="85" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="85"/>
-      <c r="I5" s="85"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-      <c r="R5" s="85"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
     </row>
     <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="G6" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="G6" s="86" t="s">
+      <c r="H6" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="86" t="s">
+      <c r="I6" s="91" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="86" t="s">
+      <c r="J6" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="67" t="s">
+      <c r="K6" s="107" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="108"/>
+      <c r="P6" s="156"/>
+      <c r="Q6" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" s="156"/>
+    </row>
+    <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="99">
+        <v>1</v>
+      </c>
+      <c r="C7" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="95"/>
-      <c r="M6" s="95"/>
-      <c r="N6" s="95"/>
-      <c r="O6" s="95"/>
-      <c r="P6" s="96"/>
-      <c r="Q6" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="R6" s="96"/>
-    </row>
-    <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="79">
-        <v>1</v>
-      </c>
-      <c r="C7" s="100" t="s">
+      <c r="D7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q7" s="65" t="s">
+      <c r="R7" s="118"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B8" s="101"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="R7" s="66"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="99"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="G8" s="23">
         <v>1</v>
@@ -6136,7 +6140,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J8" s="16"/>
       <c r="K8" s="34"/>
@@ -6145,14 +6149,14 @@
       <c r="N8" s="34"/>
       <c r="O8" s="34"/>
       <c r="P8" s="34"/>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="93"/>
+      <c r="Q8" s="154"/>
+      <c r="R8" s="155"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="99"/>
-      <c r="C9" s="101"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" s="19">
         <v>2</v>
@@ -6162,34 +6166,34 @@
       </c>
       <c r="I9" s="21"/>
       <c r="J9" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K9" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N9" s="18"/>
       <c r="O9" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P9" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="R9" s="72"/>
+        <v>49</v>
+      </c>
+      <c r="Q9" s="148" t="s">
+        <v>61</v>
+      </c>
+      <c r="R9" s="149"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="99"/>
-      <c r="C10" s="101"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G10" s="23">
         <v>3</v>
@@ -6200,33 +6204,33 @@
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
       <c r="K10" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="34" t="s">
         <v>82</v>
-      </c>
-      <c r="L10" s="34" t="s">
-        <v>83</v>
       </c>
       <c r="M10" s="34">
         <v>2010</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O10" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q10" s="154" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10" s="155"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B11" s="101"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="P10" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q10" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="R10" s="93"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="99"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G11" s="23">
         <v>4</v>
@@ -6237,33 +6241,33 @@
       <c r="I11" s="16"/>
       <c r="J11" s="16"/>
       <c r="K11" s="33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L11" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M11" s="34">
         <v>2010</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O11" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q11" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" s="93"/>
+        <v>45</v>
+      </c>
+      <c r="Q11" s="154" t="s">
+        <v>47</v>
+      </c>
+      <c r="R11" s="155"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="80"/>
-      <c r="C12" s="102"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="104"/>
       <c r="D12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G12" s="23">
         <v>5</v>
@@ -6274,37 +6278,37 @@
       <c r="I12" s="16"/>
       <c r="J12" s="16"/>
       <c r="K12" s="33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L12" s="34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M12" s="34">
         <v>2010</v>
       </c>
       <c r="N12" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O12" s="34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P12" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q12" s="92" t="s">
-        <v>48</v>
-      </c>
-      <c r="R12" s="93"/>
+        <v>45</v>
+      </c>
+      <c r="Q12" s="154" t="s">
+        <v>47</v>
+      </c>
+      <c r="R12" s="155"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="79">
+      <c r="B13" s="99">
         <v>2</v>
       </c>
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="G13" s="19">
         <v>6</v>
@@ -6314,36 +6318,36 @@
       </c>
       <c r="I13" s="21"/>
       <c r="J13" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K13" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M13" s="18">
         <v>2010</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O13" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P13" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q13" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="R13" s="72"/>
+        <v>45</v>
+      </c>
+      <c r="Q13" s="148" t="s">
+        <v>61</v>
+      </c>
+      <c r="R13" s="149"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="99"/>
-      <c r="C14" s="99"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
       <c r="D14" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G14" s="23">
         <v>7</v>
@@ -6352,10 +6356,10 @@
         <v>7</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K14" s="34"/>
       <c r="L14" s="34"/>
@@ -6363,14 +6367,14 @@
       <c r="N14" s="34"/>
       <c r="O14" s="34"/>
       <c r="P14" s="34"/>
-      <c r="Q14" s="92"/>
-      <c r="R14" s="93"/>
+      <c r="Q14" s="154"/>
+      <c r="R14" s="155"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="99"/>
-      <c r="C15" s="99"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
       <c r="D15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="23">
         <v>8</v>
@@ -6379,10 +6383,10 @@
         <v>8</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K15" s="34"/>
       <c r="L15" s="34"/>
@@ -6390,14 +6394,14 @@
       <c r="N15" s="34"/>
       <c r="O15" s="34"/>
       <c r="P15" s="34"/>
-      <c r="Q15" s="92"/>
-      <c r="R15" s="93"/>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="155"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="99"/>
-      <c r="C16" s="99"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="101"/>
       <c r="D16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" s="23">
         <v>9</v>
@@ -6411,14 +6415,14 @@
       <c r="N16" s="34"/>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
-      <c r="Q16" s="92"/>
-      <c r="R16" s="93"/>
+      <c r="Q16" s="154"/>
+      <c r="R16" s="155"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="99"/>
-      <c r="C17" s="99"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="101"/>
       <c r="D17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G17" s="23">
         <v>10</v>
@@ -6432,14 +6436,14 @@
       <c r="N17" s="34"/>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
-      <c r="Q17" s="92"/>
-      <c r="R17" s="93"/>
+      <c r="Q17" s="154"/>
+      <c r="R17" s="155"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="80"/>
-      <c r="C18" s="80"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
       <c r="D18" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G18" s="23">
         <v>11</v>
@@ -6453,18 +6457,18 @@
       <c r="N18" s="34"/>
       <c r="O18" s="34"/>
       <c r="P18" s="34"/>
-      <c r="Q18" s="92"/>
-      <c r="R18" s="93"/>
+      <c r="Q18" s="154"/>
+      <c r="R18" s="155"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="79">
+      <c r="B19" s="99">
         <v>3</v>
       </c>
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="102" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="G19" s="23">
         <v>12</v>
@@ -6478,14 +6482,14 @@
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
       <c r="P19" s="34"/>
-      <c r="Q19" s="92"/>
-      <c r="R19" s="93"/>
+      <c r="Q19" s="154"/>
+      <c r="R19" s="155"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="99"/>
-      <c r="C20" s="101"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="103"/>
       <c r="D20" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G20" s="23">
         <v>13</v>
@@ -6499,14 +6503,14 @@
       <c r="N20" s="34"/>
       <c r="O20" s="34"/>
       <c r="P20" s="34"/>
-      <c r="Q20" s="92"/>
-      <c r="R20" s="93"/>
+      <c r="Q20" s="154"/>
+      <c r="R20" s="155"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="99"/>
-      <c r="C21" s="101"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="103"/>
       <c r="D21" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" s="23">
         <v>14</v>
@@ -6520,14 +6524,14 @@
       <c r="N21" s="34"/>
       <c r="O21" s="34"/>
       <c r="P21" s="34"/>
-      <c r="Q21" s="92"/>
-      <c r="R21" s="93"/>
+      <c r="Q21" s="154"/>
+      <c r="R21" s="155"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="99"/>
-      <c r="C22" s="101"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="103"/>
       <c r="D22" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G22" s="23">
         <v>15</v>
@@ -6541,14 +6545,14 @@
       <c r="N22" s="34"/>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
-      <c r="Q22" s="92"/>
-      <c r="R22" s="93"/>
+      <c r="Q22" s="154"/>
+      <c r="R22" s="155"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="99"/>
-      <c r="C23" s="101"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="103"/>
       <c r="D23" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G23" s="23">
         <v>16</v>
@@ -6562,14 +6566,14 @@
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
       <c r="P23" s="34"/>
-      <c r="Q23" s="92"/>
-      <c r="R23" s="93"/>
+      <c r="Q23" s="154"/>
+      <c r="R23" s="155"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="80"/>
-      <c r="C24" s="102"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="104"/>
       <c r="D24" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G24" s="23">
         <v>17</v>
@@ -6583,18 +6587,18 @@
       <c r="N24" s="34"/>
       <c r="O24" s="34"/>
       <c r="P24" s="34"/>
-      <c r="Q24" s="92"/>
-      <c r="R24" s="93"/>
+      <c r="Q24" s="154"/>
+      <c r="R24" s="155"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="79">
+      <c r="B25" s="99">
         <v>4</v>
       </c>
-      <c r="C25" s="100" t="s">
-        <v>50</v>
+      <c r="C25" s="102" t="s">
+        <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G25" s="23">
         <v>18</v>
@@ -6608,56 +6612,56 @@
       <c r="N25" s="34"/>
       <c r="O25" s="34"/>
       <c r="P25" s="34"/>
-      <c r="Q25" s="92"/>
-      <c r="R25" s="93"/>
+      <c r="Q25" s="154"/>
+      <c r="R25" s="155"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="99"/>
-      <c r="C26" s="101"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="103"/>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="99"/>
-      <c r="C27" s="101"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="103"/>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="99"/>
-      <c r="C28" s="101"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="103"/>
       <c r="D28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="97"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="97"/>
-      <c r="L28" s="97"/>
-      <c r="M28" s="97"/>
+        <v>49</v>
+      </c>
+      <c r="G28" s="98"/>
+      <c r="H28" s="98"/>
+      <c r="I28" s="157"/>
+      <c r="J28" s="157"/>
+      <c r="K28" s="157"/>
+      <c r="L28" s="157"/>
+      <c r="M28" s="157"/>
       <c r="N28" s="43"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="99"/>
-      <c r="C29" s="101"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="103"/>
       <c r="D29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I29" s="103"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="103"/>
-      <c r="L29" s="103"/>
-      <c r="M29" s="103"/>
+        <v>49</v>
+      </c>
+      <c r="I29" s="158"/>
+      <c r="J29" s="158"/>
+      <c r="K29" s="158"/>
+      <c r="L29" s="158"/>
+      <c r="M29" s="158"/>
       <c r="N29" s="44"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="80"/>
-      <c r="C30" s="102"/>
+      <c r="B30" s="100"/>
+      <c r="C30" s="104"/>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -6728,127 +6732,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="83"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="111" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="111"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="142"/>
-      <c r="D3" s="142"/>
-      <c r="E3" s="142"/>
-      <c r="F3" s="142"/>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="142"/>
-      <c r="M3" s="142"/>
-      <c r="N3" s="142"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="86" t="s">
+      <c r="C4" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="136" t="s">
+      <c r="D4" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="E4" s="93" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="F4" s="95" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="119" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="119"/>
+    </row>
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="112"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="159" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="160"/>
+      <c r="M5" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="26" t="s">
         <v>108</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="69"/>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="115"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="129" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="130"/>
-      <c r="M5" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="113" t="s">
+      <c r="C6" s="109" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="E6" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="29" t="s">
         <v>111</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>112</v>
       </c>
       <c r="H6" s="29">
         <v>2010</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="K6" s="131" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="161" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="162" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="132" t="s">
+      <c r="M6" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="29" t="s">
-        <v>48</v>
-      </c>
       <c r="N6" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -6856,37 +6860,37 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="113"/>
+      <c r="C7" s="109"/>
       <c r="D7" s="31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H7" s="8">
         <v>2010</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" s="138" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="139"/>
+        <v>83</v>
+      </c>
+      <c r="K7" s="163" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="164"/>
       <c r="M7" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
@@ -6894,37 +6898,37 @@
         <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="113"/>
+      <c r="C8" s="109"/>
       <c r="D8" s="31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -6932,37 +6936,37 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="113"/>
+      <c r="C9" s="109"/>
       <c r="D9" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="F9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="I9" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="J9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="140" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="141"/>
+        <v>49</v>
+      </c>
+      <c r="K9" s="131" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="132"/>
       <c r="M9" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -6970,37 +6974,37 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="113"/>
+      <c r="C10" s="109"/>
       <c r="D10" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H10" s="11">
         <v>2010</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K10" s="133" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="134"/>
+        <v>83</v>
+      </c>
+      <c r="K10" s="129" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="130"/>
       <c r="M10" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -7008,37 +7012,37 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="113"/>
+      <c r="C11" s="109"/>
       <c r="D11" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H11" s="11">
         <v>2010</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K11" s="133" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" s="134"/>
+        <v>83</v>
+      </c>
+      <c r="K11" s="129" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" s="130"/>
       <c r="M11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
@@ -7046,37 +7050,37 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="113"/>
+      <c r="C12" s="109"/>
       <c r="D12" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H12" s="11">
         <v>2010</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="K12" s="133" t="s">
-        <v>46</v>
-      </c>
-      <c r="L12" s="134"/>
+        <v>83</v>
+      </c>
+      <c r="K12" s="129" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="130"/>
       <c r="M12" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -7084,37 +7088,37 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="114"/>
+      <c r="C13" s="110"/>
       <c r="D13" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>51</v>
-      </c>
       <c r="J13" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="127" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="128"/>
+        <v>49</v>
+      </c>
+      <c r="K13" s="135" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="136"/>
       <c r="M13" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N13" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -7134,7 +7138,7 @@
     </row>
     <row r="15" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="28"/>
@@ -7144,102 +7148,102 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="112"/>
-      <c r="L15" s="112"/>
+      <c r="K15" s="143"/>
+      <c r="L15" s="143"/>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="106" t="s">
+      <c r="C17" s="120" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="122"/>
+      <c r="G17" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="108"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="109"/>
-      <c r="G17" s="39" t="s">
+      <c r="H17" s="120" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="106" t="s">
+      <c r="I17" s="123"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="121"/>
+      <c r="L17" s="122"/>
+      <c r="M17" s="120" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="107"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="108"/>
-      <c r="L17" s="109"/>
-      <c r="M17" s="106" t="s">
+      <c r="N17" s="123"/>
+      <c r="O17" s="121"/>
+      <c r="P17" s="122"/>
+    </row>
+    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="124" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="125" t="s">
         <v>123</v>
       </c>
-      <c r="N17" s="107"/>
-      <c r="O17" s="108"/>
-      <c r="P17" s="109"/>
-    </row>
-    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="120" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="121" t="s">
+      <c r="D18" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="105" t="s">
+      <c r="E18" s="126" t="s">
         <v>125</v>
       </c>
-      <c r="E18" s="105" t="s">
+      <c r="F18" s="127" t="s">
         <v>126</v>
       </c>
-      <c r="F18" s="104" t="s">
+      <c r="G18" s="128" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="126" t="s">
+      <c r="H18" s="137" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="122" t="s">
-        <v>129</v>
-      </c>
-      <c r="I18" s="123"/>
-      <c r="J18" s="105" t="s">
+      <c r="I18" s="138"/>
+      <c r="J18" s="126" t="s">
+        <v>123</v>
+      </c>
+      <c r="K18" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="K18" s="105" t="s">
+      <c r="L18" s="127" t="s">
         <v>125</v>
       </c>
-      <c r="L18" s="104" t="s">
-        <v>126</v>
-      </c>
-      <c r="M18" s="110" t="s">
-        <v>129</v>
-      </c>
-      <c r="N18" s="105" t="s">
+      <c r="M18" s="141" t="s">
+        <v>128</v>
+      </c>
+      <c r="N18" s="126" t="s">
+        <v>123</v>
+      </c>
+      <c r="O18" s="126" t="s">
         <v>124</v>
       </c>
-      <c r="O18" s="105" t="s">
+      <c r="P18" s="127" t="s">
         <v>125</v>
       </c>
-      <c r="P18" s="104" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="120"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="105"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="126"/>
-      <c r="H19" s="124"/>
-      <c r="I19" s="125"/>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="111"/>
-      <c r="N19" s="105"/>
-      <c r="O19" s="105"/>
-      <c r="P19" s="104"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="126"/>
+      <c r="F19" s="127"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="139"/>
+      <c r="I19" s="140"/>
+      <c r="J19" s="126"/>
+      <c r="K19" s="126"/>
+      <c r="L19" s="127"/>
+      <c r="M19" s="142"/>
+      <c r="N19" s="126"/>
+      <c r="O19" s="126"/>
+      <c r="P19" s="127"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C20" s="38">
         <v>8</v>
@@ -7252,10 +7256,10 @@
       </c>
       <c r="F20" s="41"/>
       <c r="G20" s="46"/>
-      <c r="H20" s="118" t="s">
-        <v>130</v>
-      </c>
-      <c r="I20" s="119"/>
+      <c r="H20" s="133" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="134"/>
       <c r="J20" s="2">
         <v>3</v>
       </c>
@@ -7266,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N20" s="2">
         <v>5</v>

--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F66CDF-2D0F-4C9E-A568-0C83DADAFFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE1128C-7222-452A-A5AB-D6205B85212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="1725" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -1069,7 +1069,7 @@
     <t>Stanca Vlad Tudor</t>
   </si>
   <si>
-    <t>updateProduct(String title, String director, int year, List&lt;String&gt; actors, String category, List&lt;String&gt; keywords): void</t>
+    <t>updateProduct(int id, String nume, double pret, String categorie, String tip): void</t>
   </si>
 </sst>
 </file>
@@ -1974,22 +1974,151 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2007,36 +2136,12 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2061,109 +2166,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2172,44 +2196,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2608,12 +2608,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="83"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="106"/>
       <c r="H1" s="51" t="s">
         <v>1</v>
       </c>
@@ -2621,11 +2621,11 @@
       <c r="J1" s="51"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
+      <c r="I2" s="123"/>
+      <c r="J2" s="123"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
@@ -2784,21 +2784,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="48"/>
-      <c r="B24" s="80" t="s">
+      <c r="B24" s="122" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="80"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="80"/>
-      <c r="G24" s="80"/>
-      <c r="H24" s="80"/>
-      <c r="I24" s="80"/>
-      <c r="J24" s="80"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="80"/>
-      <c r="M24" s="80"/>
-      <c r="N24" s="80"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="122"/>
+      <c r="I24" s="122"/>
+      <c r="J24" s="122"/>
+      <c r="K24" s="122"/>
+      <c r="L24" s="122"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="122"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C26" s="50"/>
@@ -2837,39 +2837,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="129" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="131"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="132" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="G5" s="90" t="s">
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="G5" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
@@ -2884,18 +2884,18 @@
       <c r="E6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="91" t="s">
+      <c r="G6" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="93" t="s">
+      <c r="H6" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="95" t="s">
+      <c r="I6" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
       <c r="M6" s="23" t="s">
         <v>30</v>
       </c>
@@ -2904,15 +2904,15 @@
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="97" t="s">
+      <c r="C7" s="124" t="s">
         <v>132</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>132</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="94"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="135"/>
       <c r="I7" s="23" t="s">
         <v>140</v>
       </c>
@@ -2933,7 +2933,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="97"/>
+      <c r="C8" s="124"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>133</v>
@@ -2964,7 +2964,7 @@
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="85" t="s">
+      <c r="C9" s="128" t="s">
         <v>134</v>
       </c>
       <c r="D9" s="60" t="s">
@@ -2997,7 +2997,7 @@
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="85"/>
+      <c r="C10" s="128"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>139</v>
@@ -3028,7 +3028,7 @@
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="97" t="s">
+      <c r="C11" s="124" t="s">
         <v>135</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -3061,7 +3061,7 @@
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="97"/>
+      <c r="C12" s="124"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>136</v>
@@ -3092,7 +3092,7 @@
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="99" t="s">
+      <c r="C13" s="126" t="s">
         <v>137</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -3113,7 +3113,7 @@
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="100"/>
+      <c r="C14" s="127"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>138</v>
@@ -3132,7 +3132,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="124" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="4"/>
@@ -3151,7 +3151,7 @@
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="97"/>
+      <c r="C16" s="124"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19">
@@ -3168,7 +3168,7 @@
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="124" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="4"/>
@@ -3185,7 +3185,7 @@
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="97"/>
+      <c r="C18" s="124"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -3200,7 +3200,7 @@
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="124" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4"/>
@@ -3217,7 +3217,7 @@
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="97"/>
+      <c r="C20" s="124"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -3225,8 +3225,8 @@
       <c r="D22" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="M24" s="66"/>
@@ -3236,12 +3236,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B3:G3"/>
@@ -3251,6 +3245,12 @@
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="C7:C8"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3281,41 +3281,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="140" t="s">
         <v>151</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="131"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="141" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="90" t="s">
+      <c r="G5" s="133" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="133"/>
     </row>
     <row r="6" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -3328,42 +3328,42 @@
         <v>66</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="91" t="s">
+      <c r="G6" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="91" t="s">
+      <c r="H6" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="91" t="s">
+      <c r="I6" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="93" t="s">
+      <c r="J6" s="114" t="s">
         <v>72</v>
       </c>
-      <c r="K6" s="107" t="s">
+      <c r="K6" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="108"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="143"/>
+      <c r="N6" s="143"/>
       <c r="O6" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="99">
+      <c r="B7" s="126">
         <v>1</v>
       </c>
-      <c r="C7" s="102" t="s">
+      <c r="C7" s="137" t="s">
         <v>152</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="94"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
       <c r="K7" s="23" t="s">
         <v>140</v>
       </c>
@@ -3381,8 +3381,8 @@
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="101"/>
-      <c r="C8" s="103"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="138"/>
       <c r="D8" s="2" t="s">
         <v>154</v>
       </c>
@@ -3413,8 +3413,8 @@
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="101"/>
-      <c r="C9" s="103"/>
+      <c r="B9" s="136"/>
+      <c r="C9" s="138"/>
       <c r="D9" s="2" t="s">
         <v>155</v>
       </c>
@@ -3447,8 +3447,8 @@
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="101"/>
-      <c r="C10" s="103"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="138"/>
       <c r="D10" s="2" t="s">
         <v>156</v>
       </c>
@@ -3479,8 +3479,8 @@
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="101"/>
-      <c r="C11" s="103"/>
+      <c r="B11" s="136"/>
+      <c r="C11" s="138"/>
       <c r="D11" s="2" t="s">
         <v>157</v>
       </c>
@@ -3511,8 +3511,8 @@
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="100"/>
-      <c r="C12" s="104"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="139"/>
       <c r="D12" s="2" t="s">
         <v>158</v>
       </c>
@@ -3543,10 +3543,10 @@
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="99">
+      <c r="B13" s="126">
         <v>2</v>
       </c>
-      <c r="C13" s="102" t="s">
+      <c r="C13" s="137" t="s">
         <v>134</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -3581,8 +3581,8 @@
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="101"/>
-      <c r="C14" s="103"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="138"/>
       <c r="D14" s="2" t="s">
         <v>160</v>
       </c>
@@ -3613,8 +3613,8 @@
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="101"/>
-      <c r="C15" s="103"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="138"/>
       <c r="D15" s="2" t="s">
         <v>161</v>
       </c>
@@ -3645,8 +3645,8 @@
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="101"/>
-      <c r="C16" s="103"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="138"/>
       <c r="D16" s="2" t="s">
         <v>162</v>
       </c>
@@ -3677,8 +3677,8 @@
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="101"/>
-      <c r="C17" s="103"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="138"/>
       <c r="D17" s="2" t="s">
         <v>163</v>
       </c>
@@ -3709,8 +3709,8 @@
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="100"/>
-      <c r="C18" s="104"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="139"/>
       <c r="D18" s="2" t="s">
         <v>164</v>
       </c>
@@ -3743,10 +3743,10 @@
       </c>
     </row>
     <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="99">
+      <c r="B19" s="126">
         <v>3</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="137" t="s">
         <v>135</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -3779,8 +3779,8 @@
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="101"/>
-      <c r="C20" s="103"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="138"/>
       <c r="D20" s="2" t="s">
         <v>177</v>
       </c>
@@ -3811,8 +3811,8 @@
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="101"/>
-      <c r="C21" s="103"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="138"/>
       <c r="D21" s="2" t="s">
         <v>178</v>
       </c>
@@ -3845,8 +3845,8 @@
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="101"/>
-      <c r="C22" s="103"/>
+      <c r="B22" s="136"/>
+      <c r="C22" s="138"/>
       <c r="D22" s="2" t="s">
         <v>179</v>
       </c>
@@ -3877,8 +3877,8 @@
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="101"/>
-      <c r="C23" s="103"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="138"/>
       <c r="D23" s="2" t="s">
         <v>180</v>
       </c>
@@ -3909,8 +3909,8 @@
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="100"/>
-      <c r="C24" s="104"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="139"/>
       <c r="D24" s="2" t="s">
         <v>181</v>
       </c>
@@ -3941,10 +3941,10 @@
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="99">
+      <c r="B25" s="126">
         <v>4</v>
       </c>
-      <c r="C25" s="102" t="s">
+      <c r="C25" s="137" t="s">
         <v>137</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -3979,8 +3979,8 @@
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="101"/>
-      <c r="C26" s="103"/>
+      <c r="B26" s="136"/>
+      <c r="C26" s="138"/>
       <c r="D26" s="2" t="s">
         <v>183</v>
       </c>
@@ -4011,8 +4011,8 @@
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="101"/>
-      <c r="C27" s="103"/>
+      <c r="B27" s="136"/>
+      <c r="C27" s="138"/>
       <c r="D27" s="2" t="s">
         <v>184</v>
       </c>
@@ -4045,8 +4045,8 @@
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="101"/>
-      <c r="C28" s="103"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="138"/>
       <c r="D28" s="2" t="s">
         <v>185</v>
       </c>
@@ -4077,8 +4077,8 @@
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="101"/>
-      <c r="C29" s="103"/>
+      <c r="B29" s="136"/>
+      <c r="C29" s="138"/>
       <c r="D29" s="2" t="s">
         <v>186</v>
       </c>
@@ -4109,8 +4109,8 @@
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="100"/>
-      <c r="C30" s="104"/>
+      <c r="B30" s="127"/>
+      <c r="C30" s="139"/>
       <c r="D30" s="2" t="s">
         <v>187</v>
       </c>
@@ -4171,12 +4171,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="C7:C12"/>
     <mergeCell ref="B1:E1"/>
@@ -4188,6 +4182,12 @@
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="K6:N6"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4214,51 +4214,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="D4" s="112" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="93" t="s">
+      <c r="E4" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
       <c r="L4" s="118"/>
       <c r="M4" s="119" t="s">
         <v>30</v>
@@ -4266,10 +4266,10 @@
       <c r="N4" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="112"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="117"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="115"/>
       <c r="F5" s="26" t="s">
         <v>140</v>
       </c>
@@ -4296,7 +4296,7 @@
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="109" t="s">
+      <c r="C6" s="102" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -4329,7 +4329,7 @@
       <c r="B7" s="12">
         <v>2</v>
       </c>
-      <c r="C7" s="109"/>
+      <c r="C7" s="102"/>
       <c r="D7" s="31" t="s">
         <v>200</v>
       </c>
@@ -4360,7 +4360,7 @@
       <c r="B8" s="24">
         <v>3</v>
       </c>
-      <c r="C8" s="109"/>
+      <c r="C8" s="102"/>
       <c r="D8" s="31" t="s">
         <v>201</v>
       </c>
@@ -4391,7 +4391,7 @@
       <c r="B9" s="24">
         <v>4</v>
       </c>
-      <c r="C9" s="109"/>
+      <c r="C9" s="102"/>
       <c r="D9" s="30" t="s">
         <v>202</v>
       </c>
@@ -4422,7 +4422,7 @@
       <c r="B10" s="12">
         <v>5</v>
       </c>
-      <c r="C10" s="109"/>
+      <c r="C10" s="102"/>
       <c r="D10" s="30" t="s">
         <v>203</v>
       </c>
@@ -4453,7 +4453,7 @@
       <c r="B11" s="24">
         <v>6</v>
       </c>
-      <c r="C11" s="109"/>
+      <c r="C11" s="102"/>
       <c r="D11" s="31" t="s">
         <v>49</v>
       </c>
@@ -4473,8 +4473,8 @@
         <v>50</v>
       </c>
       <c r="J11" s="12"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="132"/>
+      <c r="K11" s="120"/>
+      <c r="L11" s="121"/>
       <c r="M11" s="12" t="s">
         <v>49</v>
       </c>
@@ -4484,7 +4484,7 @@
       <c r="B12" s="24">
         <v>7</v>
       </c>
-      <c r="C12" s="109"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="31" t="s">
         <v>65</v>
       </c>
@@ -4516,7 +4516,7 @@
       <c r="B13" s="12">
         <v>8</v>
       </c>
-      <c r="C13" s="109"/>
+      <c r="C13" s="102"/>
       <c r="D13" s="31"/>
       <c r="E13" s="12" t="str">
         <f t="shared" ref="E13:E35" si="0">"TC" &amp; (B13 - 6) &amp; "_BVA"</f>
@@ -4546,7 +4546,7 @@
       <c r="B14" s="24">
         <v>9</v>
       </c>
-      <c r="C14" s="109"/>
+      <c r="C14" s="102"/>
       <c r="D14" s="31"/>
       <c r="E14" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4576,7 +4576,7 @@
       <c r="B15" s="12">
         <v>10</v>
       </c>
-      <c r="C15" s="109"/>
+      <c r="C15" s="102"/>
       <c r="D15" s="31"/>
       <c r="E15" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4606,7 +4606,7 @@
       <c r="B16" s="24">
         <v>11</v>
       </c>
-      <c r="C16" s="109"/>
+      <c r="C16" s="102"/>
       <c r="D16" s="31"/>
       <c r="E16" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4636,7 +4636,7 @@
       <c r="B17" s="24">
         <v>12</v>
       </c>
-      <c r="C17" s="109"/>
+      <c r="C17" s="102"/>
       <c r="D17" s="31"/>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4666,7 +4666,7 @@
       <c r="B18" s="12">
         <v>13</v>
       </c>
-      <c r="C18" s="109"/>
+      <c r="C18" s="102"/>
       <c r="D18" s="31"/>
       <c r="E18" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4696,7 +4696,7 @@
       <c r="B19" s="24">
         <v>14</v>
       </c>
-      <c r="C19" s="109"/>
+      <c r="C19" s="102"/>
       <c r="D19" s="31"/>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4726,7 +4726,7 @@
       <c r="B20" s="24">
         <v>15</v>
       </c>
-      <c r="C20" s="109"/>
+      <c r="C20" s="102"/>
       <c r="D20" s="31"/>
       <c r="E20" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4756,7 +4756,7 @@
       <c r="B21" s="12">
         <v>16</v>
       </c>
-      <c r="C21" s="109"/>
+      <c r="C21" s="102"/>
       <c r="D21" s="31"/>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4786,7 +4786,7 @@
       <c r="B22" s="24">
         <v>17</v>
       </c>
-      <c r="C22" s="109"/>
+      <c r="C22" s="102"/>
       <c r="D22" s="31"/>
       <c r="E22" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4816,7 +4816,7 @@
       <c r="B23" s="12">
         <v>18</v>
       </c>
-      <c r="C23" s="109"/>
+      <c r="C23" s="102"/>
       <c r="D23" s="31"/>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4846,7 +4846,7 @@
       <c r="B24" s="24">
         <v>19</v>
       </c>
-      <c r="C24" s="109"/>
+      <c r="C24" s="102"/>
       <c r="D24" s="31"/>
       <c r="E24" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4876,7 +4876,7 @@
       <c r="B25" s="24">
         <v>20</v>
       </c>
-      <c r="C25" s="109"/>
+      <c r="C25" s="102"/>
       <c r="D25" s="31"/>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4906,7 +4906,7 @@
       <c r="B26" s="12">
         <v>21</v>
       </c>
-      <c r="C26" s="109"/>
+      <c r="C26" s="102"/>
       <c r="D26" s="31"/>
       <c r="E26" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4936,7 +4936,7 @@
       <c r="B27" s="24">
         <v>22</v>
       </c>
-      <c r="C27" s="109"/>
+      <c r="C27" s="102"/>
       <c r="D27" s="31"/>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4966,7 +4966,7 @@
       <c r="B28" s="24">
         <v>23</v>
       </c>
-      <c r="C28" s="109"/>
+      <c r="C28" s="102"/>
       <c r="D28" s="31"/>
       <c r="E28" s="12" t="str">
         <f t="shared" si="0"/>
@@ -4996,7 +4996,7 @@
       <c r="B29" s="12">
         <v>24</v>
       </c>
-      <c r="C29" s="109"/>
+      <c r="C29" s="102"/>
       <c r="D29" s="31"/>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5026,7 +5026,7 @@
       <c r="B30" s="24">
         <v>25</v>
       </c>
-      <c r="C30" s="109"/>
+      <c r="C30" s="102"/>
       <c r="D30" s="31"/>
       <c r="E30" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5056,7 +5056,7 @@
       <c r="B31" s="12">
         <v>26</v>
       </c>
-      <c r="C31" s="109"/>
+      <c r="C31" s="102"/>
       <c r="D31" s="31"/>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5086,7 +5086,7 @@
       <c r="B32" s="24">
         <v>27</v>
       </c>
-      <c r="C32" s="109"/>
+      <c r="C32" s="102"/>
       <c r="D32" s="31"/>
       <c r="E32" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5105,8 +5105,8 @@
         <v>81</v>
       </c>
       <c r="J32" s="11"/>
-      <c r="K32" s="129"/>
-      <c r="L32" s="130"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="85"/>
       <c r="M32" s="57" t="s">
         <v>144</v>
       </c>
@@ -5116,7 +5116,7 @@
       <c r="B33" s="24">
         <v>28</v>
       </c>
-      <c r="C33" s="109"/>
+      <c r="C33" s="102"/>
       <c r="D33" s="31"/>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5135,8 +5135,8 @@
         <v>167</v>
       </c>
       <c r="J33" s="11"/>
-      <c r="K33" s="129"/>
-      <c r="L33" s="130"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="85"/>
       <c r="M33" s="57" t="s">
         <v>144</v>
       </c>
@@ -5146,7 +5146,7 @@
       <c r="B34" s="12">
         <v>29</v>
       </c>
-      <c r="C34" s="109"/>
+      <c r="C34" s="102"/>
       <c r="D34" s="31"/>
       <c r="E34" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5165,8 +5165,8 @@
         <v>168</v>
       </c>
       <c r="J34" s="11"/>
-      <c r="K34" s="129"/>
-      <c r="L34" s="130"/>
+      <c r="K34" s="84"/>
+      <c r="L34" s="85"/>
       <c r="M34" s="57" t="s">
         <v>144</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="B35" s="24">
         <v>30</v>
       </c>
-      <c r="C35" s="110"/>
+      <c r="C35" s="103"/>
       <c r="D35" s="32"/>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
@@ -5195,8 +5195,8 @@
         <v>169</v>
       </c>
       <c r="J35" s="25"/>
-      <c r="K35" s="135"/>
-      <c r="L35" s="136"/>
+      <c r="K35" s="82"/>
+      <c r="L35" s="83"/>
       <c r="M35" s="53" t="s">
         <v>61</v>
       </c>
@@ -5229,98 +5229,98 @@
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
-      <c r="K37" s="143"/>
-      <c r="L37" s="143"/>
+      <c r="K37" s="92"/>
+      <c r="L37" s="92"/>
       <c r="M37" s="7"/>
     </row>
     <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M38" s="7"/>
     </row>
     <row r="39" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="120" t="s">
+      <c r="C39" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="D39" s="121"/>
-      <c r="E39" s="121"/>
-      <c r="F39" s="122"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
+      <c r="F39" s="95"/>
       <c r="G39" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="H39" s="120" t="s">
+      <c r="H39" s="93" t="s">
         <v>121</v>
       </c>
-      <c r="I39" s="123"/>
-      <c r="J39" s="121"/>
-      <c r="K39" s="121"/>
-      <c r="L39" s="122"/>
-      <c r="M39" s="120" t="s">
+      <c r="I39" s="96"/>
+      <c r="J39" s="94"/>
+      <c r="K39" s="94"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="N39" s="123"/>
-      <c r="O39" s="121"/>
-      <c r="P39" s="122"/>
+      <c r="N39" s="96"/>
+      <c r="O39" s="94"/>
+      <c r="P39" s="95"/>
     </row>
     <row r="40" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="124" t="s">
+      <c r="B40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="125" t="s">
+      <c r="C40" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="D40" s="126" t="s">
+      <c r="D40" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="E40" s="126" t="s">
+      <c r="E40" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="F40" s="127" t="s">
+      <c r="F40" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="G40" s="128" t="s">
+      <c r="G40" s="99" t="s">
         <v>127</v>
       </c>
-      <c r="H40" s="137" t="s">
+      <c r="H40" s="86" t="s">
         <v>128</v>
       </c>
-      <c r="I40" s="138"/>
-      <c r="J40" s="126" t="s">
+      <c r="I40" s="87"/>
+      <c r="J40" s="90" t="s">
         <v>123</v>
       </c>
-      <c r="K40" s="126" t="s">
+      <c r="K40" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="L40" s="127" t="s">
+      <c r="L40" s="91" t="s">
         <v>125</v>
       </c>
-      <c r="M40" s="141" t="s">
+      <c r="M40" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="N40" s="126" t="s">
+      <c r="N40" s="90" t="s">
         <v>123</v>
       </c>
-      <c r="O40" s="126" t="s">
+      <c r="O40" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="P40" s="127" t="s">
+      <c r="P40" s="91" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="124"/>
-      <c r="C41" s="125"/>
-      <c r="D41" s="126"/>
-      <c r="E41" s="126"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="128"/>
-      <c r="H41" s="139"/>
-      <c r="I41" s="140"/>
-      <c r="J41" s="126"/>
-      <c r="K41" s="126"/>
-      <c r="L41" s="127"/>
-      <c r="M41" s="142"/>
-      <c r="N41" s="126"/>
-      <c r="O41" s="126"/>
-      <c r="P41" s="127"/>
+      <c r="B41" s="97"/>
+      <c r="C41" s="98"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="99"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="101"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="90"/>
+      <c r="P41" s="91"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B42" s="42" t="s">
@@ -5337,10 +5337,10 @@
       </c>
       <c r="F42" s="41"/>
       <c r="G42" s="46"/>
-      <c r="H42" s="133" t="s">
+      <c r="H42" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="I42" s="134"/>
+      <c r="I42" s="81"/>
       <c r="J42" s="2">
         <v>3</v>
       </c>
@@ -5368,15 +5368,17 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="H40:I41"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="C6:C35"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="H39:L39"/>
     <mergeCell ref="M39:P39"/>
@@ -5390,17 +5392,15 @@
     <mergeCell ref="P40:P41"/>
     <mergeCell ref="M40:M41"/>
     <mergeCell ref="N40:N41"/>
-    <mergeCell ref="C6:C35"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B3:N3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="H40:I41"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="L40:L41"/>
+    <mergeCell ref="K37:L37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5431,43 +5431,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="131"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="132" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="G5" s="90" t="s">
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="G5" s="133" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="90"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="133"/>
+      <c r="Q5" s="133"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
@@ -5482,20 +5482,20 @@
       <c r="E6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="91" t="s">
+      <c r="G6" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="93" t="s">
+      <c r="H6" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="95" t="s">
+      <c r="I6" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="96"/>
-      <c r="K6" s="96"/>
-      <c r="L6" s="96"/>
-      <c r="M6" s="96"/>
-      <c r="N6" s="96"/>
+      <c r="J6" s="117"/>
+      <c r="K6" s="117"/>
+      <c r="L6" s="117"/>
+      <c r="M6" s="117"/>
+      <c r="N6" s="117"/>
       <c r="O6" s="118"/>
       <c r="P6" s="119" t="s">
         <v>30</v>
@@ -5506,15 +5506,15 @@
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="97" t="s">
+      <c r="C7" s="124" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="94"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="135"/>
       <c r="I7" s="23" t="s">
         <v>32</v>
       </c>
@@ -5530,11 +5530,11 @@
       <c r="M7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="95" t="s">
+      <c r="N7" s="116" t="s">
         <v>37</v>
       </c>
       <c r="O7" s="118"/>
-      <c r="P7" s="95" t="s">
+      <c r="P7" s="116" t="s">
         <v>38</v>
       </c>
       <c r="Q7" s="118"/>
@@ -5543,7 +5543,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="97"/>
+      <c r="C8" s="124"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>39</v>
@@ -5569,22 +5569,22 @@
       <c r="M8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N8" s="144" t="s">
+      <c r="N8" s="152" t="s">
         <v>45</v>
       </c>
-      <c r="O8" s="145" t="s">
+      <c r="O8" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="144" t="s">
+      <c r="P8" s="152" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="145"/>
+      <c r="Q8" s="153"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="124" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -5612,22 +5612,22 @@
       <c r="M9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="144" t="s">
+      <c r="N9" s="152" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="145" t="s">
+      <c r="O9" s="153" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="144" t="s">
+      <c r="P9" s="152" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" s="145"/>
+      <c r="Q9" s="153"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="97"/>
+      <c r="C10" s="124"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>52</v>
@@ -5653,20 +5653,20 @@
       <c r="M10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="N10" s="150" t="s">
+      <c r="N10" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="151"/>
-      <c r="P10" s="150" t="s">
+      <c r="O10" s="147"/>
+      <c r="P10" s="146" t="s">
         <v>55</v>
       </c>
-      <c r="Q10" s="151"/>
+      <c r="Q10" s="147"/>
     </row>
     <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="97" t="s">
+      <c r="C11" s="124" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -5694,20 +5694,20 @@
       <c r="M11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="150" t="s">
+      <c r="N11" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="O11" s="151"/>
-      <c r="P11" s="150" t="s">
+      <c r="O11" s="147"/>
+      <c r="P11" s="146" t="s">
         <v>49</v>
       </c>
-      <c r="Q11" s="151"/>
+      <c r="Q11" s="147"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="97"/>
+      <c r="C12" s="124"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>58</v>
@@ -5746,7 +5746,7 @@
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="99" t="s">
+      <c r="C13" s="126" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -5787,7 +5787,7 @@
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="100"/>
+      <c r="C14" s="127"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>63</v>
@@ -5813,18 +5813,18 @@
       <c r="M14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="152" t="s">
+      <c r="N14" s="144" t="s">
         <v>64</v>
       </c>
-      <c r="O14" s="153"/>
-      <c r="P14" s="146"/>
-      <c r="Q14" s="147"/>
+      <c r="O14" s="145"/>
+      <c r="P14" s="150"/>
+      <c r="Q14" s="151"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="97" t="s">
+      <c r="C15" s="124" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="4"/>
@@ -5840,16 +5840,16 @@
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-      <c r="N15" s="144"/>
-      <c r="O15" s="145"/>
-      <c r="P15" s="146"/>
-      <c r="Q15" s="147"/>
+      <c r="N15" s="152"/>
+      <c r="O15" s="153"/>
+      <c r="P15" s="150"/>
+      <c r="Q15" s="151"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="97"/>
+      <c r="C16" s="124"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19"/>
@@ -5859,16 +5859,16 @@
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
-      <c r="N16" s="144"/>
-      <c r="O16" s="145"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="147"/>
+      <c r="N16" s="152"/>
+      <c r="O16" s="153"/>
+      <c r="P16" s="150"/>
+      <c r="Q16" s="151"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="97" t="s">
+      <c r="C17" s="124" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="4"/>
@@ -5880,16 +5880,16 @@
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
-      <c r="N17" s="144"/>
-      <c r="O17" s="145"/>
-      <c r="P17" s="146"/>
-      <c r="Q17" s="147"/>
+      <c r="N17" s="152"/>
+      <c r="O17" s="153"/>
+      <c r="P17" s="150"/>
+      <c r="Q17" s="151"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="97"/>
+      <c r="C18" s="124"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -5899,16 +5899,16 @@
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
-      <c r="N18" s="144"/>
-      <c r="O18" s="145"/>
-      <c r="P18" s="146"/>
-      <c r="Q18" s="147"/>
+      <c r="N18" s="152"/>
+      <c r="O18" s="153"/>
+      <c r="P18" s="150"/>
+      <c r="Q18" s="151"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="124" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4"/>
@@ -5920,16 +5920,16 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="144"/>
-      <c r="O19" s="145"/>
-      <c r="P19" s="146"/>
-      <c r="Q19" s="147"/>
+      <c r="N19" s="152"/>
+      <c r="O19" s="153"/>
+      <c r="P19" s="150"/>
+      <c r="Q19" s="151"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="97"/>
+      <c r="C20" s="124"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -5937,11 +5937,36 @@
       <c r="D22" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
@@ -5958,31 +5983,6 @@
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6015,44 +6015,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
-      <c r="G3" s="88"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="131"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="141" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
+      <c r="C5" s="141"/>
+      <c r="D5" s="141"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="90" t="s">
+      <c r="G5" s="133" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="90"/>
-      <c r="O5" s="90"/>
-      <c r="P5" s="90"/>
-      <c r="Q5" s="90"/>
-      <c r="R5" s="90"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="133"/>
+      <c r="M5" s="133"/>
+      <c r="N5" s="133"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="133"/>
+      <c r="Q5" s="133"/>
+      <c r="R5" s="133"/>
     </row>
     <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -6065,45 +6065,45 @@
         <v>66</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="91" t="s">
+      <c r="G6" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="91" t="s">
+      <c r="H6" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="91" t="s">
+      <c r="I6" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="93" t="s">
+      <c r="J6" s="114" t="s">
         <v>72</v>
       </c>
-      <c r="K6" s="107" t="s">
+      <c r="K6" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="108"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="143"/>
+      <c r="N6" s="143"/>
+      <c r="O6" s="143"/>
       <c r="P6" s="156"/>
-      <c r="Q6" s="107" t="s">
+      <c r="Q6" s="142" t="s">
         <v>30</v>
       </c>
       <c r="R6" s="156"/>
     </row>
     <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="99">
+      <c r="B7" s="126">
         <v>1</v>
       </c>
-      <c r="C7" s="102" t="s">
+      <c r="C7" s="137" t="s">
         <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="94"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="135"/>
       <c r="K7" s="23" t="s">
         <v>32</v>
       </c>
@@ -6122,14 +6122,14 @@
       <c r="P7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="Q7" s="95" t="s">
+      <c r="Q7" s="116" t="s">
         <v>75</v>
       </c>
       <c r="R7" s="118"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="101"/>
-      <c r="C8" s="103"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="138"/>
       <c r="D8" s="2" t="s">
         <v>76</v>
       </c>
@@ -6149,12 +6149,12 @@
       <c r="N8" s="34"/>
       <c r="O8" s="34"/>
       <c r="P8" s="34"/>
-      <c r="Q8" s="154"/>
-      <c r="R8" s="155"/>
+      <c r="Q8" s="157"/>
+      <c r="R8" s="158"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="101"/>
-      <c r="C9" s="103"/>
+      <c r="B9" s="136"/>
+      <c r="C9" s="138"/>
       <c r="D9" s="2" t="s">
         <v>78</v>
       </c>
@@ -6190,8 +6190,8 @@
       <c r="R9" s="149"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="101"/>
-      <c r="C10" s="103"/>
+      <c r="B10" s="136"/>
+      <c r="C10" s="138"/>
       <c r="D10" s="2" t="s">
         <v>80</v>
       </c>
@@ -6221,14 +6221,14 @@
       <c r="P10" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q10" s="154" t="s">
+      <c r="Q10" s="157" t="s">
         <v>47</v>
       </c>
-      <c r="R10" s="155"/>
+      <c r="R10" s="158"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="101"/>
-      <c r="C11" s="103"/>
+      <c r="B11" s="136"/>
+      <c r="C11" s="138"/>
       <c r="D11" s="2" t="s">
         <v>84</v>
       </c>
@@ -6258,14 +6258,14 @@
       <c r="P11" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q11" s="154" t="s">
+      <c r="Q11" s="157" t="s">
         <v>47</v>
       </c>
-      <c r="R11" s="155"/>
+      <c r="R11" s="158"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="100"/>
-      <c r="C12" s="104"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="139"/>
       <c r="D12" s="2" t="s">
         <v>86</v>
       </c>
@@ -6295,16 +6295,16 @@
       <c r="P12" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q12" s="154" t="s">
+      <c r="Q12" s="157" t="s">
         <v>47</v>
       </c>
-      <c r="R12" s="155"/>
+      <c r="R12" s="158"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="99">
+      <c r="B13" s="126">
         <v>2</v>
       </c>
-      <c r="C13" s="99" t="s">
+      <c r="C13" s="126" t="s">
         <v>88</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -6344,8 +6344,8 @@
       <c r="R13" s="149"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="136"/>
       <c r="D14" s="2" t="s">
         <v>91</v>
       </c>
@@ -6367,12 +6367,12 @@
       <c r="N14" s="34"/>
       <c r="O14" s="34"/>
       <c r="P14" s="34"/>
-      <c r="Q14" s="154"/>
-      <c r="R14" s="155"/>
+      <c r="Q14" s="157"/>
+      <c r="R14" s="158"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
+      <c r="B15" s="136"/>
+      <c r="C15" s="136"/>
       <c r="D15" s="2" t="s">
         <v>92</v>
       </c>
@@ -6394,12 +6394,12 @@
       <c r="N15" s="34"/>
       <c r="O15" s="34"/>
       <c r="P15" s="34"/>
-      <c r="Q15" s="154"/>
-      <c r="R15" s="155"/>
+      <c r="Q15" s="157"/>
+      <c r="R15" s="158"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="136"/>
       <c r="D16" s="2" t="s">
         <v>93</v>
       </c>
@@ -6415,12 +6415,12 @@
       <c r="N16" s="34"/>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
-      <c r="Q16" s="154"/>
-      <c r="R16" s="155"/>
+      <c r="Q16" s="157"/>
+      <c r="R16" s="158"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="101"/>
-      <c r="C17" s="101"/>
+      <c r="B17" s="136"/>
+      <c r="C17" s="136"/>
       <c r="D17" s="2" t="s">
         <v>94</v>
       </c>
@@ -6436,12 +6436,12 @@
       <c r="N17" s="34"/>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
-      <c r="Q17" s="154"/>
-      <c r="R17" s="155"/>
+      <c r="Q17" s="157"/>
+      <c r="R17" s="158"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="100"/>
-      <c r="C18" s="100"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="127"/>
       <c r="D18" s="2" t="s">
         <v>95</v>
       </c>
@@ -6457,14 +6457,14 @@
       <c r="N18" s="34"/>
       <c r="O18" s="34"/>
       <c r="P18" s="34"/>
-      <c r="Q18" s="154"/>
-      <c r="R18" s="155"/>
+      <c r="Q18" s="157"/>
+      <c r="R18" s="158"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="99">
+      <c r="B19" s="126">
         <v>3</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="137" t="s">
         <v>96</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -6482,12 +6482,12 @@
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
       <c r="P19" s="34"/>
-      <c r="Q19" s="154"/>
-      <c r="R19" s="155"/>
+      <c r="Q19" s="157"/>
+      <c r="R19" s="158"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="101"/>
-      <c r="C20" s="103"/>
+      <c r="B20" s="136"/>
+      <c r="C20" s="138"/>
       <c r="D20" s="2" t="s">
         <v>98</v>
       </c>
@@ -6503,12 +6503,12 @@
       <c r="N20" s="34"/>
       <c r="O20" s="34"/>
       <c r="P20" s="34"/>
-      <c r="Q20" s="154"/>
-      <c r="R20" s="155"/>
+      <c r="Q20" s="157"/>
+      <c r="R20" s="158"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="101"/>
-      <c r="C21" s="103"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="138"/>
       <c r="D21" s="2" t="s">
         <v>99</v>
       </c>
@@ -6524,12 +6524,12 @@
       <c r="N21" s="34"/>
       <c r="O21" s="34"/>
       <c r="P21" s="34"/>
-      <c r="Q21" s="154"/>
-      <c r="R21" s="155"/>
+      <c r="Q21" s="157"/>
+      <c r="R21" s="158"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="101"/>
-      <c r="C22" s="103"/>
+      <c r="B22" s="136"/>
+      <c r="C22" s="138"/>
       <c r="D22" s="2" t="s">
         <v>100</v>
       </c>
@@ -6545,12 +6545,12 @@
       <c r="N22" s="34"/>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
-      <c r="Q22" s="154"/>
-      <c r="R22" s="155"/>
+      <c r="Q22" s="157"/>
+      <c r="R22" s="158"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="101"/>
-      <c r="C23" s="103"/>
+      <c r="B23" s="136"/>
+      <c r="C23" s="138"/>
       <c r="D23" s="2" t="s">
         <v>101</v>
       </c>
@@ -6566,12 +6566,12 @@
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
       <c r="P23" s="34"/>
-      <c r="Q23" s="154"/>
-      <c r="R23" s="155"/>
+      <c r="Q23" s="157"/>
+      <c r="R23" s="158"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="100"/>
-      <c r="C24" s="104"/>
+      <c r="B24" s="127"/>
+      <c r="C24" s="139"/>
       <c r="D24" s="2" t="s">
         <v>102</v>
       </c>
@@ -6587,14 +6587,14 @@
       <c r="N24" s="34"/>
       <c r="O24" s="34"/>
       <c r="P24" s="34"/>
-      <c r="Q24" s="154"/>
-      <c r="R24" s="155"/>
+      <c r="Q24" s="157"/>
+      <c r="R24" s="158"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="99">
+      <c r="B25" s="126">
         <v>4</v>
       </c>
-      <c r="C25" s="102" t="s">
+      <c r="C25" s="137" t="s">
         <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -6612,60 +6612,84 @@
       <c r="N25" s="34"/>
       <c r="O25" s="34"/>
       <c r="P25" s="34"/>
-      <c r="Q25" s="154"/>
-      <c r="R25" s="155"/>
+      <c r="Q25" s="157"/>
+      <c r="R25" s="158"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="101"/>
-      <c r="C26" s="103"/>
+      <c r="B26" s="136"/>
+      <c r="C26" s="138"/>
       <c r="D26" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="101"/>
-      <c r="C27" s="103"/>
+      <c r="B27" s="136"/>
+      <c r="C27" s="138"/>
       <c r="D27" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="101"/>
-      <c r="C28" s="103"/>
+      <c r="B28" s="136"/>
+      <c r="C28" s="138"/>
       <c r="D28" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G28" s="98"/>
-      <c r="H28" s="98"/>
-      <c r="I28" s="157"/>
-      <c r="J28" s="157"/>
-      <c r="K28" s="157"/>
-      <c r="L28" s="157"/>
-      <c r="M28" s="157"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
+      <c r="I28" s="155"/>
+      <c r="J28" s="155"/>
+      <c r="K28" s="155"/>
+      <c r="L28" s="155"/>
+      <c r="M28" s="155"/>
       <c r="N28" s="43"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="101"/>
-      <c r="C29" s="103"/>
+      <c r="B29" s="136"/>
+      <c r="C29" s="138"/>
       <c r="D29" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I29" s="158"/>
-      <c r="J29" s="158"/>
-      <c r="K29" s="158"/>
-      <c r="L29" s="158"/>
-      <c r="M29" s="158"/>
+      <c r="I29" s="154"/>
+      <c r="J29" s="154"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="154"/>
+      <c r="M29" s="154"/>
       <c r="N29" s="44"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="100"/>
-      <c r="C30" s="104"/>
+      <c r="B30" s="127"/>
+      <c r="C30" s="139"/>
       <c r="D30" s="2" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="I6:I7"/>
@@ -6682,30 +6706,6 @@
     <mergeCell ref="G5:R5"/>
     <mergeCell ref="B3:G3"/>
     <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="I28:M28"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6732,51 +6732,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="83"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="106"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="111"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="107"/>
+      <c r="G3" s="107"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="107"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="107"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="113" t="s">
+      <c r="C4" s="110" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="D4" s="112" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="93" t="s">
+      <c r="E4" s="114" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
       <c r="L4" s="118"/>
       <c r="M4" s="119" t="s">
         <v>30</v>
@@ -6784,10 +6784,10 @@
       <c r="N4" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="112"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="117"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="115"/>
       <c r="F5" s="26" t="s">
         <v>32</v>
       </c>
@@ -6818,7 +6818,7 @@
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="109" t="s">
+      <c r="C6" s="102" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -6860,7 +6860,7 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="109"/>
+      <c r="C7" s="102"/>
       <c r="D7" s="31" t="s">
         <v>112</v>
       </c>
@@ -6898,7 +6898,7 @@
         <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="109"/>
+      <c r="C8" s="102"/>
       <c r="D8" s="31" t="s">
         <v>114</v>
       </c>
@@ -6936,7 +6936,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="109"/>
+      <c r="C9" s="102"/>
       <c r="D9" s="31" t="s">
         <v>49</v>
       </c>
@@ -6958,10 +6958,10 @@
       <c r="J9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="131" t="s">
+      <c r="K9" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="132"/>
+      <c r="L9" s="121"/>
       <c r="M9" s="12" t="s">
         <v>49</v>
       </c>
@@ -6974,7 +6974,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="109"/>
+      <c r="C10" s="102"/>
       <c r="D10" s="31" t="s">
         <v>51</v>
       </c>
@@ -6996,10 +6996,10 @@
       <c r="J10" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="129" t="s">
+      <c r="K10" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="L10" s="130"/>
+      <c r="L10" s="85"/>
       <c r="M10" s="6" t="s">
         <v>61</v>
       </c>
@@ -7012,7 +7012,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="109"/>
+      <c r="C11" s="102"/>
       <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
@@ -7034,10 +7034,10 @@
       <c r="J11" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="129" t="s">
+      <c r="K11" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="L11" s="130"/>
+      <c r="L11" s="85"/>
       <c r="M11" s="5" t="s">
         <v>47</v>
       </c>
@@ -7050,7 +7050,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="109"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="31" t="s">
         <v>51</v>
       </c>
@@ -7072,10 +7072,10 @@
       <c r="J12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="129" t="s">
+      <c r="K12" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="130"/>
+      <c r="L12" s="85"/>
       <c r="M12" s="5" t="s">
         <v>47</v>
       </c>
@@ -7088,7 +7088,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="110"/>
+      <c r="C13" s="103"/>
       <c r="D13" s="32" t="s">
         <v>49</v>
       </c>
@@ -7110,10 +7110,10 @@
       <c r="J13" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="K13" s="135" t="s">
+      <c r="K13" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="136"/>
+      <c r="L13" s="83"/>
       <c r="M13" s="25" t="s">
         <v>49</v>
       </c>
@@ -7148,98 +7148,98 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="143"/>
-      <c r="L15" s="143"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="92"/>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="120" t="s">
+      <c r="C17" s="93" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="95"/>
       <c r="G17" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="120" t="s">
+      <c r="H17" s="93" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="123"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
-      <c r="L17" s="122"/>
-      <c r="M17" s="120" t="s">
+      <c r="I17" s="96"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="94"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="93" t="s">
         <v>122</v>
       </c>
-      <c r="N17" s="123"/>
-      <c r="O17" s="121"/>
-      <c r="P17" s="122"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="95"/>
     </row>
     <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="124" t="s">
+      <c r="B18" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="125" t="s">
+      <c r="C18" s="98" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="126" t="s">
+      <c r="D18" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="E18" s="126" t="s">
+      <c r="E18" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="F18" s="127" t="s">
+      <c r="F18" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="128" t="s">
+      <c r="G18" s="99" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="137" t="s">
+      <c r="H18" s="86" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="138"/>
-      <c r="J18" s="126" t="s">
+      <c r="I18" s="87"/>
+      <c r="J18" s="90" t="s">
         <v>123</v>
       </c>
-      <c r="K18" s="126" t="s">
+      <c r="K18" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="L18" s="127" t="s">
+      <c r="L18" s="91" t="s">
         <v>125</v>
       </c>
-      <c r="M18" s="141" t="s">
+      <c r="M18" s="100" t="s">
         <v>128</v>
       </c>
-      <c r="N18" s="126" t="s">
+      <c r="N18" s="90" t="s">
         <v>123</v>
       </c>
-      <c r="O18" s="126" t="s">
+      <c r="O18" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="P18" s="127" t="s">
+      <c r="P18" s="91" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="124"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="126"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="139"/>
-      <c r="I19" s="140"/>
-      <c r="J19" s="126"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="127"/>
-      <c r="M19" s="142"/>
-      <c r="N19" s="126"/>
-      <c r="O19" s="126"/>
-      <c r="P19" s="127"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="91"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="90"/>
+      <c r="P19" s="91"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="42" t="s">
@@ -7256,10 +7256,10 @@
       </c>
       <c r="F20" s="41"/>
       <c r="G20" s="46"/>
-      <c r="H20" s="133" t="s">
+      <c r="H20" s="80" t="s">
         <v>129</v>
       </c>
-      <c r="I20" s="134"/>
+      <c r="I20" s="81"/>
       <c r="J20" s="2">
         <v>3</v>
       </c>
@@ -7287,20 +7287,12 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
@@ -7317,12 +7309,20 @@
     <mergeCell ref="H18:I19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="K18:K19"/>
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7340,12 +7340,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E819BB071F23F542A5DF0E9C9037AD04" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="798a38e6de461387c626d04793181ea9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="301f98df-4edd-4096-94f8-2f8af3eee570" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b4b8dab68acb31e3ac71f6347d499c29" ns2:_="">
     <xsd:import namespace="301f98df-4edd-4096-94f8-2f8af3eee570"/>
@@ -7483,6 +7477,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
@@ -7492,15 +7492,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E854E7-906F-4C7C-AFC0-1BC802AE88F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7516,4 +7507,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE1128C-7222-452A-A5AB-D6205B85212A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB41C950-DB73-400C-B495-A0D2754EBD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="1725" windowWidth="28800" windowHeight="15345" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="H40" authorId="0" shapeId="0" xr:uid="{496CB4D3-ABDB-41C5-A0C3-A8BB1BA95B38}">
+    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{496CB4D3-ABDB-41C5-A0C3-A8BB1BA95B38}">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M40" authorId="0" shapeId="0" xr:uid="{5D3D9773-D24F-404E-862A-A82F2FC9C874}">
+    <comment ref="M19" authorId="0" shapeId="0" xr:uid="{5D3D9773-D24F-404E-862A-A82F2FC9C874}">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="209">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -807,9 +807,6 @@
     <t>"Cappucino"</t>
   </si>
   <si>
-    <t>product added</t>
-  </si>
-  <si>
     <t>"SIMPLE"</t>
   </si>
   <si>
@@ -1070,6 +1067,18 @@
   </si>
   <si>
     <t>updateProduct(int id, String nume, double pret, String categorie, String tip): void</t>
+  </si>
+  <si>
+    <t>product updated</t>
+  </si>
+  <si>
+    <t>TC1_BVA</t>
+  </si>
+  <si>
+    <t>TC7_BVA</t>
+  </si>
+  <si>
+    <t>TC9_BVA</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1371,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1797,11 +1806,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1935,9 +1983,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1974,6 +2019,195 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1986,12 +2220,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2004,166 +2232,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2172,45 +2259,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2227,6 +2275,55 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2608,12 +2705,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="106"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="94"/>
       <c r="H1" s="51" t="s">
         <v>1</v>
       </c>
@@ -2621,11 +2718,11 @@
       <c r="J1" s="51"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="123" t="s">
+      <c r="H2" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H3" s="2"/>
@@ -2652,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J5" s="2">
         <v>236</v>
@@ -2740,7 +2837,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C20" s="47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -2784,21 +2881,21 @@
     </row>
     <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="48"/>
-      <c r="B24" s="122" t="s">
+      <c r="B24" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="122"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="122"/>
-      <c r="L24" s="122"/>
-      <c r="M24" s="122"/>
-      <c r="N24" s="122"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="110"/>
+      <c r="L24" s="110"/>
+      <c r="M24" s="110"/>
+      <c r="N24" s="110"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C26" s="50"/>
@@ -2837,39 +2934,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="106"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="105" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="G5" s="133" t="s">
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="G5" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
@@ -2884,18 +2981,18 @@
       <c r="E6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="108" t="s">
+      <c r="G6" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="114" t="s">
+      <c r="H6" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="116" t="s">
+      <c r="I6" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
       <c r="M6" s="23" t="s">
         <v>30</v>
       </c>
@@ -2904,15 +3001,15 @@
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="124" t="s">
+      <c r="C7" s="115" t="s">
         <v>132</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>132</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="135"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="96"/>
       <c r="I7" s="23" t="s">
         <v>140</v>
       </c>
@@ -2933,7 +3030,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="124"/>
+      <c r="C8" s="115"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>133</v>
@@ -2942,62 +3039,62 @@
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="J8" s="61">
+      <c r="J8" s="60">
         <v>10.4</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M8" s="52" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="128" t="s">
+      <c r="C9" s="112" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="60" t="s">
-        <v>175</v>
+      <c r="D9" s="59" t="s">
+        <v>174</v>
       </c>
       <c r="E9" s="4"/>
       <c r="G9" s="19">
         <v>2</v>
       </c>
-      <c r="H9" s="64" t="s">
-        <v>172</v>
+      <c r="H9" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="61">
+      <c r="J9" s="60">
         <v>10.4</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="M9" s="52" t="s">
         <v>146</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="M9" s="52" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="128"/>
+      <c r="C10" s="112"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>139</v>
@@ -3006,7 +3103,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>143</v>
@@ -3015,20 +3112,20 @@
         <v>-40</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="M10" s="78" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="M10" s="77" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="124" t="s">
+      <c r="C11" s="115" t="s">
         <v>135</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -3038,8 +3135,8 @@
       <c r="G11" s="19">
         <v>4</v>
       </c>
-      <c r="H11" s="67" t="s">
-        <v>174</v>
+      <c r="H11" s="66" t="s">
+        <v>173</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>143</v>
@@ -3051,17 +3148,17 @@
         <v>54</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="M11" s="78" t="s">
-        <v>149</v>
+        <v>144</v>
+      </c>
+      <c r="M11" s="77" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="124"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>136</v>
@@ -3069,8 +3166,8 @@
       <c r="G12" s="19">
         <v>5</v>
       </c>
-      <c r="H12" s="67" t="s">
-        <v>173</v>
+      <c r="H12" s="66" t="s">
+        <v>172</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>143</v>
@@ -3079,20 +3176,20 @@
         <v>40</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M12" s="78" t="s">
-        <v>150</v>
+      <c r="M12" s="77" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="126" t="s">
+      <c r="C13" s="97" t="s">
         <v>137</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -3104,16 +3201,16 @@
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9"/>
-      <c r="J13" s="62"/>
+      <c r="J13" s="61"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
-      <c r="M13" s="79"/>
+      <c r="M13" s="78"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="127"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>138</v>
@@ -3123,16 +3220,16 @@
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9"/>
-      <c r="J14" s="62"/>
+      <c r="J14" s="61"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
-      <c r="M14" s="79"/>
+      <c r="M14" s="78"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="124" t="s">
+      <c r="C15" s="115" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="4"/>
@@ -3142,7 +3239,7 @@
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
-      <c r="J15" s="63"/>
+      <c r="J15" s="62"/>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="21"/>
@@ -3151,7 +3248,7 @@
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="124"/>
+      <c r="C16" s="115"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19">
@@ -3159,7 +3256,7 @@
       </c>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
-      <c r="J16" s="63"/>
+      <c r="J16" s="62"/>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="21"/>
@@ -3168,7 +3265,7 @@
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="115" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="4"/>
@@ -3176,7 +3273,7 @@
       <c r="G17" s="19"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
-      <c r="J17" s="63"/>
+      <c r="J17" s="62"/>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
       <c r="M17" s="21"/>
@@ -3185,7 +3282,7 @@
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="124"/>
+      <c r="C18" s="115"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -3200,7 +3297,7 @@
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="124" t="s">
+      <c r="C19" s="115" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4"/>
@@ -3217,7 +3314,7 @@
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="124"/>
+      <c r="C20" s="115"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -3225,17 +3322,23 @@
       <c r="D22" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="M24" s="66"/>
+      <c r="M24" s="65"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="M26" s="65"/>
+      <c r="M26" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="C13:C14"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B3:G3"/>
@@ -3245,12 +3348,6 @@
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="C7:C8"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3281,41 +3378,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="106"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="140" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
+      <c r="B3" s="116" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="141" t="s">
+      <c r="B5" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="141"/>
-      <c r="D5" s="141"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="133" t="s">
+      <c r="G5" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="133"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
     </row>
     <row r="6" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -3328,42 +3425,42 @@
         <v>66</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="108" t="s">
+      <c r="G6" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="108" t="s">
+      <c r="H6" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="114" t="s">
+      <c r="J6" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="K6" s="142" t="s">
+      <c r="K6" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="143"/>
-      <c r="M6" s="143"/>
-      <c r="N6" s="143"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
       <c r="O6" s="56" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="126">
+      <c r="B7" s="97">
         <v>1</v>
       </c>
-      <c r="C7" s="137" t="s">
+      <c r="C7" s="100" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="135"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="96"/>
       <c r="K7" s="23" t="s">
         <v>140</v>
       </c>
@@ -3381,10 +3478,10 @@
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="136"/>
-      <c r="C8" s="138"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="101"/>
       <c r="D8" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G8" s="23">
         <v>1</v>
@@ -3393,7 +3490,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J8" s="16"/>
       <c r="K8" s="34" t="s">
@@ -3403,29 +3500,29 @@
         <v>10</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O8" s="57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="136"/>
-      <c r="C9" s="138"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="101"/>
       <c r="D9" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G9" s="68">
+        <v>154</v>
+      </c>
+      <c r="G9" s="67">
         <v>2</v>
       </c>
       <c r="H9" s="17">
         <v>2</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>79</v>
@@ -3437,29 +3534,29 @@
         <v>10</v>
       </c>
       <c r="M9" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O9" s="53" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="136"/>
-      <c r="C10" s="138"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="101"/>
       <c r="D10" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G10" s="68">
+        <v>155</v>
+      </c>
+      <c r="G10" s="67">
         <v>3</v>
       </c>
       <c r="H10" s="17">
         <v>3</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J10" s="16"/>
       <c r="K10" s="34" t="s">
@@ -3469,122 +3566,122 @@
         <v>10</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O10" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="136"/>
-      <c r="C11" s="138"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="101"/>
       <c r="D11" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G11" s="68">
+        <v>156</v>
+      </c>
+      <c r="G11" s="67">
         <v>4</v>
       </c>
       <c r="H11" s="17">
         <v>4</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J11" s="16"/>
       <c r="K11" s="34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L11" s="34">
         <v>10</v>
       </c>
       <c r="M11" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N11" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O11" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="127"/>
-      <c r="C12" s="139"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G12" s="68">
+        <v>157</v>
+      </c>
+      <c r="G12" s="67">
         <v>5</v>
       </c>
       <c r="H12" s="17">
         <v>5</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J12" s="16"/>
       <c r="K12" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L12" s="34">
         <v>10</v>
       </c>
       <c r="M12" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N12" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O12" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="126">
+      <c r="B13" s="97">
         <v>2</v>
       </c>
-      <c r="C13" s="137" t="s">
+      <c r="C13" s="100" t="s">
         <v>134</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G13" s="68">
+        <v>158</v>
+      </c>
+      <c r="G13" s="67">
         <v>6</v>
       </c>
       <c r="H13" s="17">
         <v>6</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>79</v>
       </c>
       <c r="K13" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L13" s="34">
         <v>10</v>
       </c>
       <c r="M13" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O13" s="53" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="136"/>
-      <c r="C14" s="138"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="101"/>
       <c r="D14" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G14" s="23">
         <v>7</v>
@@ -3593,7 +3690,7 @@
         <v>7</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J14" s="16"/>
       <c r="K14" s="34" t="s">
@@ -3603,20 +3700,20 @@
         <v>0</v>
       </c>
       <c r="M14" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N14" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O14" s="57" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="136"/>
-      <c r="C15" s="138"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="101"/>
       <c r="D15" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G15" s="23">
         <v>8</v>
@@ -3625,7 +3722,7 @@
         <v>8</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J15" s="16"/>
       <c r="K15" s="34" t="s">
@@ -3635,20 +3732,20 @@
         <v>-1</v>
       </c>
       <c r="M15" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N15" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O15" s="57" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="136"/>
-      <c r="C16" s="138"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="101"/>
       <c r="D16" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G16" s="23">
         <v>9</v>
@@ -3667,20 +3764,20 @@
         <v>1</v>
       </c>
       <c r="M16" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N16" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O16" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="136"/>
-      <c r="C17" s="138"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="101"/>
       <c r="D17" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G17" s="23">
         <v>10</v>
@@ -3696,23 +3793,23 @@
         <v>143</v>
       </c>
       <c r="L17" s="34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O17" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="127"/>
-      <c r="C18" s="139"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="102"/>
       <c r="D18" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G18" s="23">
         <v>11</v>
@@ -3721,7 +3818,7 @@
         <v>11</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>79</v>
@@ -3730,27 +3827,27 @@
         <v>143</v>
       </c>
       <c r="L18" s="34" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M18" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N18" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O18" s="53" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="126">
+      <c r="B19" s="97">
         <v>3</v>
       </c>
-      <c r="C19" s="137" t="s">
+      <c r="C19" s="100" t="s">
         <v>135</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G19" s="23">
         <v>12</v>
@@ -3766,23 +3863,23 @@
         <v>143</v>
       </c>
       <c r="L19" s="34" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M19" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N19" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O19" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="136"/>
-      <c r="C20" s="138"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G20" s="23">
         <v>13</v>
@@ -3791,7 +3888,7 @@
         <v>13</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J20" s="16"/>
       <c r="K20" s="34" t="s">
@@ -3804,17 +3901,17 @@
         <v>54</v>
       </c>
       <c r="N20" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O20" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="136"/>
-      <c r="C21" s="138"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="101"/>
       <c r="D21" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G21" s="23">
         <v>14</v>
@@ -3823,7 +3920,7 @@
         <v>14</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>79</v>
@@ -3838,17 +3935,17 @@
         <v>64</v>
       </c>
       <c r="N21" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O21" s="53" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="136"/>
-      <c r="C22" s="138"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="101"/>
       <c r="D22" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G22" s="23">
         <v>15</v>
@@ -3857,7 +3954,7 @@
         <v>15</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J22" s="16"/>
       <c r="K22" s="34" t="s">
@@ -3870,17 +3967,17 @@
         <v>81</v>
       </c>
       <c r="N22" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O22" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="136"/>
-      <c r="C23" s="138"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="101"/>
       <c r="D23" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G23" s="23">
         <v>16</v>
@@ -3889,7 +3986,7 @@
         <v>16</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J23" s="16"/>
       <c r="K23" s="34" t="s">
@@ -3899,20 +3996,20 @@
         <v>10</v>
       </c>
       <c r="M23" s="34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N23" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O23" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="127"/>
-      <c r="C24" s="139"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="102"/>
       <c r="D24" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G24" s="23">
         <v>17</v>
@@ -3921,7 +4018,7 @@
         <v>17</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J24" s="16"/>
       <c r="K24" s="34" t="s">
@@ -3931,24 +4028,24 @@
         <v>10</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O24" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="126">
+      <c r="B25" s="97">
         <v>4</v>
       </c>
-      <c r="C25" s="137" t="s">
+      <c r="C25" s="100" t="s">
         <v>137</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G25" s="23">
         <v>18</v>
@@ -3957,7 +4054,7 @@
         <v>18</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>79</v>
@@ -3969,20 +4066,20 @@
         <v>10</v>
       </c>
       <c r="M25" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N25" s="34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O25" s="53" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="136"/>
-      <c r="C26" s="138"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="101"/>
       <c r="D26" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G26" s="23">
         <v>19</v>
@@ -3991,7 +4088,7 @@
         <v>19</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J26" s="16"/>
       <c r="K26" s="34" t="s">
@@ -4001,29 +4098,29 @@
         <v>10</v>
       </c>
       <c r="M26" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N26" s="34" t="s">
         <v>54</v>
       </c>
       <c r="O26" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="136"/>
-      <c r="C27" s="138"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="101"/>
       <c r="D27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G27" s="68">
+        <v>183</v>
+      </c>
+      <c r="G27" s="67">
         <v>20</v>
       </c>
       <c r="H27" s="17">
         <v>20</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>79</v>
@@ -4035,7 +4132,7 @@
         <v>10</v>
       </c>
       <c r="M27" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N27" s="34" t="s">
         <v>64</v>
@@ -4045,19 +4142,19 @@
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="136"/>
-      <c r="C28" s="138"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="101"/>
       <c r="D28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" s="68">
+        <v>184</v>
+      </c>
+      <c r="G28" s="67">
         <v>21</v>
       </c>
       <c r="H28" s="17">
         <v>21</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J28" s="16"/>
       <c r="K28" s="34" t="s">
@@ -4067,29 +4164,29 @@
         <v>10</v>
       </c>
       <c r="M28" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N28" s="34" t="s">
         <v>81</v>
       </c>
       <c r="O28" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="136"/>
-      <c r="C29" s="138"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="101"/>
       <c r="D29" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G29" s="68">
+        <v>185</v>
+      </c>
+      <c r="G29" s="67">
         <v>22</v>
       </c>
       <c r="H29" s="17">
         <v>22</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J29" s="16"/>
       <c r="K29" s="34" t="s">
@@ -4099,29 +4196,29 @@
         <v>10</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O29" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="127"/>
-      <c r="C30" s="139"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="102"/>
       <c r="D30" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G30" s="68">
+        <v>186</v>
+      </c>
+      <c r="G30" s="67">
         <v>23</v>
       </c>
       <c r="H30" s="17">
         <v>23</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J30" s="16"/>
       <c r="K30" s="34" t="s">
@@ -4131,24 +4228,24 @@
         <v>10</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N30" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O30" s="57" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G31" s="68">
+      <c r="G31" s="67">
         <v>24</v>
       </c>
       <c r="H31" s="17">
         <v>24</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J31" s="16" t="s">
         <v>79</v>
@@ -4160,10 +4257,10 @@
         <v>10</v>
       </c>
       <c r="M31" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N31" s="34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O31" s="53" t="s">
         <v>61</v>
@@ -4171,6 +4268,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="C7:C12"/>
     <mergeCell ref="B1:E1"/>
@@ -4182,12 +4285,6 @@
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
     <mergeCell ref="K6:N6"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4198,7 +4295,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B1:P43"/>
+  <dimension ref="B1:P22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -4214,62 +4311,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="106"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="119"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="121" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="112" t="s">
+      <c r="D4" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="114" t="s">
+      <c r="E4" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="116" t="s">
+      <c r="F4" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="119" t="s">
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="119"/>
+      <c r="N4" s="126"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="109"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="115"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="125"/>
       <c r="F5" s="26" t="s">
         <v>140</v>
       </c>
@@ -4283,8 +4380,8 @@
         <v>142</v>
       </c>
       <c r="J5" s="26"/>
-      <c r="K5" s="76"/>
-      <c r="L5" s="77"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="76"/>
       <c r="M5" s="26" t="s">
         <v>38</v>
       </c>
@@ -4293,45 +4390,45 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="24">
+      <c r="B6" s="165">
         <v>1</v>
       </c>
-      <c r="C6" s="102" t="s">
+      <c r="C6" s="166" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="E6" s="167" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="168" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" s="169">
+        <v>10.4</v>
+      </c>
+      <c r="H6" s="168" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" s="168" t="s">
+        <v>144</v>
+      </c>
+      <c r="J6" s="170"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="171" t="s">
+        <v>205</v>
+      </c>
+      <c r="N6" s="172"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="58">
+        <v>2</v>
+      </c>
+      <c r="C7" s="173"/>
+      <c r="D7" s="31" t="s">
         <v>199</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G6" s="61">
-        <v>10.4</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="75"/>
-      <c r="M6" s="54" t="s">
-        <v>144</v>
-      </c>
-      <c r="N6" s="24"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="12">
-        <v>2</v>
-      </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="31" t="s">
-        <v>200</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>51</v>
@@ -4339,30 +4436,30 @@
       <c r="F7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="61">
+      <c r="G7" s="60">
         <v>10.4</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="N7" s="12"/>
+      <c r="N7" s="174"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="24">
+      <c r="B8" s="165">
         <v>3</v>
       </c>
-      <c r="C8" s="102"/>
+      <c r="C8" s="173"/>
       <c r="D8" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>51</v>
@@ -4374,26 +4471,26 @@
         <v>-40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="71" t="s">
-        <v>148</v>
-      </c>
-      <c r="N8" s="12"/>
+      <c r="M8" s="70" t="s">
+        <v>147</v>
+      </c>
+      <c r="N8" s="174"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="24">
+      <c r="B9" s="165">
         <v>4</v>
       </c>
-      <c r="C9" s="102"/>
+      <c r="C9" s="173"/>
       <c r="D9" s="30" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>51</v>
@@ -4408,23 +4505,23 @@
         <v>54</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="71" t="s">
-        <v>149</v>
-      </c>
-      <c r="N9" s="12"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="70" t="s">
+        <v>148</v>
+      </c>
+      <c r="N9" s="174"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="12">
+      <c r="B10" s="58">
         <v>5</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="173"/>
       <c r="D10" s="30" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>51</v>
@@ -4436,939 +4533,329 @@
         <v>40</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>54</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="69"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="71" t="s">
-        <v>150</v>
-      </c>
-      <c r="N10" s="12"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="N10" s="174"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="24">
+      <c r="B11" s="165">
         <v>6</v>
       </c>
-      <c r="C11" s="102"/>
+      <c r="C11" s="173"/>
       <c r="D11" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="120"/>
-      <c r="L11" s="121"/>
-      <c r="M11" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="N11" s="12"/>
+        <v>51</v>
+      </c>
+      <c r="E11" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="34">
+        <v>10</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="J11" s="67"/>
+      <c r="K11" s="177"/>
+      <c r="L11" s="178"/>
+      <c r="M11" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="N11" s="174"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="24">
+      <c r="B12" s="58">
         <v>7</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="173"/>
       <c r="D12" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="12" t="str">
-        <f>"TC" &amp; (B12 - 6) &amp; "_BVA"</f>
-        <v>TC1_BVA</v>
+        <v>51</v>
+      </c>
+      <c r="E12" s="67" t="s">
+        <v>115</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="G12" s="34">
         <v>10</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I12" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="J12" s="67"/>
+      <c r="K12" s="177"/>
+      <c r="L12" s="178"/>
+      <c r="M12" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="N12" s="174"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="165">
+        <v>8</v>
+      </c>
+      <c r="C13" s="173"/>
+      <c r="D13" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="67" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="G13" s="34">
+        <v>0</v>
+      </c>
+      <c r="H13" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="J12" s="12"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="N12" s="12"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="12">
-        <v>8</v>
-      </c>
-      <c r="C13" s="102"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="12" t="str">
-        <f t="shared" ref="E13:E35" si="0">"TC" &amp; (B13 - 6) &amp; "_BVA"</f>
-        <v>TC2_BVA</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="34">
-        <v>10</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>146</v>
-      </c>
       <c r="I13" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="J13" s="67"/>
+      <c r="K13" s="177"/>
+      <c r="L13" s="178"/>
+      <c r="M13" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="N13" s="174"/>
+    </row>
+    <row r="14" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="165">
+        <v>9</v>
+      </c>
+      <c r="C14" s="175"/>
+      <c r="D14" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="179" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="180" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" s="180">
+        <v>1</v>
+      </c>
+      <c r="H14" s="180" t="s">
         <v>145</v>
       </c>
-      <c r="J13" s="12"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="59"/>
-      <c r="M13" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="N13" s="12"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="24">
+      <c r="I14" s="180" t="s">
+        <v>144</v>
+      </c>
+      <c r="J14" s="179"/>
+      <c r="K14" s="181"/>
+      <c r="L14" s="182"/>
+      <c r="M14" s="183" t="s">
+        <v>205</v>
+      </c>
+      <c r="N14" s="176"/>
+    </row>
+    <row r="15" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+    </row>
+    <row r="16" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="150"/>
+      <c r="L16" s="150"/>
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="131" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="132"/>
+      <c r="E18" s="132"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="H18" s="131" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="134"/>
+      <c r="J18" s="132"/>
+      <c r="K18" s="132"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="131" t="s">
+        <v>122</v>
+      </c>
+      <c r="N18" s="134"/>
+      <c r="O18" s="132"/>
+      <c r="P18" s="133"/>
+    </row>
+    <row r="19" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="135" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="136" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="137" t="s">
+        <v>125</v>
+      </c>
+      <c r="F19" s="138" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="139" t="s">
+        <v>127</v>
+      </c>
+      <c r="H19" s="146" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" s="147"/>
+      <c r="J19" s="137" t="s">
+        <v>123</v>
+      </c>
+      <c r="K19" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="L19" s="138" t="s">
+        <v>125</v>
+      </c>
+      <c r="M19" s="140" t="s">
+        <v>128</v>
+      </c>
+      <c r="N19" s="137" t="s">
+        <v>123</v>
+      </c>
+      <c r="O19" s="137" t="s">
+        <v>124</v>
+      </c>
+      <c r="P19" s="138" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="135"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="138"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="148"/>
+      <c r="I20" s="149"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="137"/>
+      <c r="L20" s="138"/>
+      <c r="M20" s="141"/>
+      <c r="N20" s="137"/>
+      <c r="O20" s="137"/>
+      <c r="P20" s="138"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="38">
         <v>9</v>
       </c>
-      <c r="C14" s="102"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC3_BVA</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="34">
-        <v>10</v>
-      </c>
-      <c r="H14" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J14" s="12"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N14" s="12"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="12">
-        <v>10</v>
-      </c>
-      <c r="C15" s="102"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC4_BVA</v>
-      </c>
-      <c r="F15" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="G15" s="34">
-        <v>10</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I15" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J15" s="12"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="59"/>
-      <c r="M15" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N15" s="12"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="24">
-        <v>11</v>
-      </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC5_BVA</v>
-      </c>
-      <c r="F16" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="G16" s="34">
-        <v>10</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I16" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J16" s="12"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N16" s="12"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="24">
-        <v>12</v>
-      </c>
-      <c r="C17" s="102"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC6_BVA</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="G17" s="34">
-        <v>10</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I17" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J17" s="12"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="N17" s="12"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="12">
-        <v>13</v>
-      </c>
-      <c r="C18" s="102"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC7_BVA</v>
-      </c>
-      <c r="F18" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G18" s="34">
+      <c r="D21" s="40">
+        <v>9</v>
+      </c>
+      <c r="E21" s="40">
         <v>0</v>
       </c>
-      <c r="H18" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I18" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J18" s="12"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="N18" s="12"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="24">
-        <v>14</v>
-      </c>
-      <c r="C19" s="102"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC8_BVA</v>
-      </c>
-      <c r="F19" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G19" s="34">
-        <v>-1</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J19" s="12"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="24">
-        <v>15</v>
-      </c>
-      <c r="C20" s="102"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC9_BVA</v>
-      </c>
-      <c r="F20" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G20" s="34">
-        <v>1</v>
-      </c>
-      <c r="H20" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I20" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J20" s="12"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N20" s="12"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B21" s="12">
-        <v>16</v>
-      </c>
-      <c r="C21" s="102"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC10_BVA</v>
-      </c>
-      <c r="F21" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="H21" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J21" s="12"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N21" s="12"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B22" s="24">
-        <v>17</v>
-      </c>
-      <c r="C22" s="102"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC11_BVA</v>
-      </c>
-      <c r="F22" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="H22" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I22" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J22" s="12"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="59"/>
-      <c r="M22" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="12">
-        <v>18</v>
-      </c>
-      <c r="C23" s="102"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC12_BVA</v>
-      </c>
-      <c r="F23" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G23" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="H23" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I23" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J23" s="12"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="59"/>
-      <c r="M23" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="24">
-        <v>19</v>
-      </c>
-      <c r="C24" s="102"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC13_BVA</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G24" s="34">
-        <v>10</v>
-      </c>
-      <c r="H24" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B25" s="24">
-        <v>20</v>
-      </c>
-      <c r="C25" s="102"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC14_BVA</v>
-      </c>
-      <c r="F25" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G25" s="34">
-        <v>10</v>
-      </c>
-      <c r="H25" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="N25" s="12"/>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B26" s="12">
-        <v>21</v>
-      </c>
-      <c r="C26" s="102"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC15_BVA</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G26" s="34">
-        <v>10</v>
-      </c>
-      <c r="H26" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="I26" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J26" s="12"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N26" s="12"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="24">
-        <v>22</v>
-      </c>
-      <c r="C27" s="102"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC16_BVA</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G27" s="34">
-        <v>10</v>
-      </c>
-      <c r="H27" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N27" s="12"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="24">
-        <v>23</v>
-      </c>
-      <c r="C28" s="102"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC17_BVA</v>
-      </c>
-      <c r="F28" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G28" s="34">
-        <v>10</v>
-      </c>
-      <c r="H28" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="I28" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J28" s="12"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N28" s="12"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B29" s="12">
-        <v>24</v>
-      </c>
-      <c r="C29" s="102"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC18_BVA</v>
-      </c>
-      <c r="F29" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G29" s="34">
-        <v>10</v>
-      </c>
-      <c r="H29" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="I29" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="J29" s="12"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="59"/>
-      <c r="M29" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="N29" s="12"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="24">
-        <v>25</v>
-      </c>
-      <c r="C30" s="102"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC19_BVA</v>
-      </c>
-      <c r="F30" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G30" s="34">
-        <v>10</v>
-      </c>
-      <c r="H30" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I30" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="J30" s="12"/>
-      <c r="K30" s="58"/>
-      <c r="L30" s="59"/>
-      <c r="M30" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="N30" s="12"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="12">
-        <v>26</v>
-      </c>
-      <c r="C31" s="102"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC20_BVA</v>
-      </c>
-      <c r="F31" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G31" s="34">
-        <v>10</v>
-      </c>
-      <c r="H31" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I31" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="12"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="59"/>
-      <c r="M31" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="N31" s="12"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="24">
-        <v>27</v>
-      </c>
-      <c r="C32" s="102"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC21_BVA</v>
-      </c>
-      <c r="F32" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G32" s="34">
-        <v>10</v>
-      </c>
-      <c r="H32" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I32" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="J32" s="11"/>
-      <c r="K32" s="84"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N32" s="12"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B33" s="24">
-        <v>28</v>
-      </c>
-      <c r="C33" s="102"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC22_BVA</v>
-      </c>
-      <c r="F33" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G33" s="34">
-        <v>10</v>
-      </c>
-      <c r="H33" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I33" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="J33" s="11"/>
-      <c r="K33" s="84"/>
-      <c r="L33" s="85"/>
-      <c r="M33" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N33" s="12"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="12">
-        <v>29</v>
-      </c>
-      <c r="C34" s="102"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC23_BVA</v>
-      </c>
-      <c r="F34" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G34" s="34">
-        <v>10</v>
-      </c>
-      <c r="H34" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I34" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="J34" s="11"/>
-      <c r="K34" s="84"/>
-      <c r="L34" s="85"/>
-      <c r="M34" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="N34" s="12"/>
-    </row>
-    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="24">
-        <v>30</v>
-      </c>
-      <c r="C35" s="103"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="12" t="str">
-        <f t="shared" si="0"/>
-        <v>TC24_BVA</v>
-      </c>
-      <c r="F35" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G35" s="34">
-        <v>10</v>
-      </c>
-      <c r="H35" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="I35" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="J35" s="25"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="53" t="s">
-        <v>61</v>
-      </c>
-      <c r="N35" s="25"/>
-    </row>
-    <row r="36" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-    </row>
-    <row r="37" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="92"/>
-      <c r="L37" s="92"/>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M38" s="7"/>
-    </row>
-    <row r="39" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="93" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="95"/>
-      <c r="G39" s="39" t="s">
-        <v>120</v>
-      </c>
-      <c r="H39" s="93" t="s">
-        <v>121</v>
-      </c>
-      <c r="I39" s="96"/>
-      <c r="J39" s="94"/>
-      <c r="K39" s="94"/>
-      <c r="L39" s="95"/>
-      <c r="M39" s="93" t="s">
-        <v>122</v>
-      </c>
-      <c r="N39" s="96"/>
-      <c r="O39" s="94"/>
-      <c r="P39" s="95"/>
-    </row>
-    <row r="40" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" s="98" t="s">
-        <v>123</v>
-      </c>
-      <c r="D40" s="90" t="s">
-        <v>124</v>
-      </c>
-      <c r="E40" s="90" t="s">
-        <v>125</v>
-      </c>
-      <c r="F40" s="91" t="s">
-        <v>126</v>
-      </c>
-      <c r="G40" s="99" t="s">
-        <v>127</v>
-      </c>
-      <c r="H40" s="86" t="s">
-        <v>128</v>
-      </c>
-      <c r="I40" s="87"/>
-      <c r="J40" s="90" t="s">
-        <v>123</v>
-      </c>
-      <c r="K40" s="90" t="s">
-        <v>124</v>
-      </c>
-      <c r="L40" s="91" t="s">
-        <v>125</v>
-      </c>
-      <c r="M40" s="100" t="s">
-        <v>128</v>
-      </c>
-      <c r="N40" s="90" t="s">
-        <v>123</v>
-      </c>
-      <c r="O40" s="90" t="s">
-        <v>124</v>
-      </c>
-      <c r="P40" s="91" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="97"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="99"/>
-      <c r="H41" s="88"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="91"/>
-      <c r="M41" s="101"/>
-      <c r="N41" s="90"/>
-      <c r="O41" s="90"/>
-      <c r="P41" s="91"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B42" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" s="38">
-        <v>8</v>
-      </c>
-      <c r="D42" s="40">
-        <v>5</v>
-      </c>
-      <c r="E42" s="40">
-        <v>3</v>
-      </c>
-      <c r="F42" s="41"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="80" t="s">
+      <c r="F21" s="41"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="142" t="s">
         <v>129</v>
       </c>
-      <c r="I42" s="81"/>
-      <c r="J42" s="2">
-        <v>3</v>
-      </c>
-      <c r="K42" s="40">
-        <v>3</v>
-      </c>
-      <c r="L42" s="41">
+      <c r="I21" s="143"/>
+      <c r="J21" s="2">
         <v>0</v>
       </c>
-      <c r="M42" s="45" t="s">
+      <c r="K21" s="40">
+        <v>0</v>
+      </c>
+      <c r="L21" s="41">
+        <v>0</v>
+      </c>
+      <c r="M21" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="N42" s="2">
-        <v>5</v>
-      </c>
-      <c r="O42" s="40">
-        <v>5</v>
-      </c>
-      <c r="P42" s="41">
+      <c r="N21" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="M43" s="3"/>
+      <c r="O21" s="40">
+        <v>0</v>
+      </c>
+      <c r="P21" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="M22" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="C6:C35"/>
+  <mergeCells count="28">
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="L19:L20"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="C6:C14"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="B4:B5"/>
@@ -5377,30 +4864,6 @@
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:L4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="H39:L39"/>
-    <mergeCell ref="M39:P39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="O40:O41"/>
-    <mergeCell ref="P40:P41"/>
-    <mergeCell ref="M40:M41"/>
-    <mergeCell ref="N40:N41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="H40:I41"/>
-    <mergeCell ref="J40:J41"/>
-    <mergeCell ref="K40:K41"/>
-    <mergeCell ref="L40:L41"/>
-    <mergeCell ref="K37:L37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5431,43 +4894,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="106"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="G5" s="133" t="s">
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
+      <c r="G5" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="133"/>
-      <c r="P5" s="133"/>
-      <c r="Q5" s="133"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="23" t="s">
@@ -5482,39 +4945,39 @@
       <c r="E6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="108" t="s">
+      <c r="G6" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="114" t="s">
+      <c r="H6" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="116" t="s">
+      <c r="I6" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="117"/>
-      <c r="K6" s="117"/>
-      <c r="L6" s="117"/>
-      <c r="M6" s="117"/>
-      <c r="N6" s="117"/>
-      <c r="O6" s="118"/>
-      <c r="P6" s="119" t="s">
+      <c r="J6" s="114"/>
+      <c r="K6" s="114"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="114"/>
+      <c r="N6" s="114"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="119"/>
+      <c r="Q6" s="126"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="124" t="s">
+      <c r="C7" s="115" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="135"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="96"/>
       <c r="I7" s="23" t="s">
         <v>32</v>
       </c>
@@ -5530,20 +4993,20 @@
       <c r="M7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="116" t="s">
+      <c r="N7" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="118"/>
-      <c r="P7" s="116" t="s">
+      <c r="O7" s="109"/>
+      <c r="P7" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="Q7" s="118"/>
+      <c r="Q7" s="109"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="124"/>
+      <c r="C8" s="115"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>39</v>
@@ -5569,22 +5032,22 @@
       <c r="M8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N8" s="152" t="s">
+      <c r="N8" s="151" t="s">
         <v>45</v>
       </c>
-      <c r="O8" s="153" t="s">
+      <c r="O8" s="152" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="152" t="s">
+      <c r="P8" s="151" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="153"/>
+      <c r="Q8" s="152"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="124" t="s">
+      <c r="C9" s="115" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -5612,22 +5075,22 @@
       <c r="M9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="152" t="s">
+      <c r="N9" s="151" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="153" t="s">
+      <c r="O9" s="152" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="152" t="s">
+      <c r="P9" s="151" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" s="153"/>
+      <c r="Q9" s="152"/>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="124"/>
+      <c r="C10" s="115"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>52</v>
@@ -5653,20 +5116,20 @@
       <c r="M10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="N10" s="146" t="s">
+      <c r="N10" s="155" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="147"/>
-      <c r="P10" s="146" t="s">
+      <c r="O10" s="156"/>
+      <c r="P10" s="155" t="s">
         <v>55</v>
       </c>
-      <c r="Q10" s="147"/>
+      <c r="Q10" s="156"/>
     </row>
     <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="124" t="s">
+      <c r="C11" s="115" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -5694,20 +5157,20 @@
       <c r="M11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="146" t="s">
+      <c r="N11" s="155" t="s">
         <v>49</v>
       </c>
-      <c r="O11" s="147"/>
-      <c r="P11" s="146" t="s">
+      <c r="O11" s="156"/>
+      <c r="P11" s="155" t="s">
         <v>49</v>
       </c>
-      <c r="Q11" s="147"/>
+      <c r="Q11" s="156"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="124"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>58</v>
@@ -5737,16 +5200,16 @@
         <v>45</v>
       </c>
       <c r="O12" s="9"/>
-      <c r="P12" s="148" t="s">
+      <c r="P12" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="149"/>
+      <c r="Q12" s="83"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="126" t="s">
+      <c r="C13" s="97" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -5774,20 +5237,20 @@
       <c r="M13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="148" t="s">
+      <c r="N13" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="O13" s="149"/>
-      <c r="P13" s="148" t="s">
+      <c r="O13" s="83"/>
+      <c r="P13" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="Q13" s="149"/>
+      <c r="Q13" s="83"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="127"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>63</v>
@@ -5813,18 +5276,18 @@
       <c r="M14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="144" t="s">
+      <c r="N14" s="157" t="s">
         <v>64</v>
       </c>
-      <c r="O14" s="145"/>
-      <c r="P14" s="150"/>
-      <c r="Q14" s="151"/>
+      <c r="O14" s="158"/>
+      <c r="P14" s="153"/>
+      <c r="Q14" s="154"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="124" t="s">
+      <c r="C15" s="115" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="4"/>
@@ -5840,16 +5303,16 @@
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-      <c r="N15" s="152"/>
-      <c r="O15" s="153"/>
-      <c r="P15" s="150"/>
-      <c r="Q15" s="151"/>
+      <c r="N15" s="151"/>
+      <c r="O15" s="152"/>
+      <c r="P15" s="153"/>
+      <c r="Q15" s="154"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="124"/>
+      <c r="C16" s="115"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19"/>
@@ -5859,16 +5322,16 @@
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
-      <c r="N16" s="152"/>
-      <c r="O16" s="153"/>
-      <c r="P16" s="150"/>
-      <c r="Q16" s="151"/>
+      <c r="N16" s="151"/>
+      <c r="O16" s="152"/>
+      <c r="P16" s="153"/>
+      <c r="Q16" s="154"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="115" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="4"/>
@@ -5880,16 +5343,16 @@
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
-      <c r="N17" s="152"/>
-      <c r="O17" s="153"/>
-      <c r="P17" s="150"/>
-      <c r="Q17" s="151"/>
+      <c r="N17" s="151"/>
+      <c r="O17" s="152"/>
+      <c r="P17" s="153"/>
+      <c r="Q17" s="154"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="124"/>
+      <c r="C18" s="115"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -5899,16 +5362,16 @@
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
-      <c r="N18" s="152"/>
-      <c r="O18" s="153"/>
-      <c r="P18" s="150"/>
-      <c r="Q18" s="151"/>
+      <c r="N18" s="151"/>
+      <c r="O18" s="152"/>
+      <c r="P18" s="153"/>
+      <c r="Q18" s="154"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="124" t="s">
+      <c r="C19" s="115" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4"/>
@@ -5920,16 +5383,16 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="152"/>
-      <c r="O19" s="153"/>
-      <c r="P19" s="150"/>
-      <c r="Q19" s="151"/>
+      <c r="N19" s="151"/>
+      <c r="O19" s="152"/>
+      <c r="P19" s="153"/>
+      <c r="Q19" s="154"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="124"/>
+      <c r="C20" s="115"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
@@ -5937,36 +5400,11 @@
       <c r="D22" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I6:O6"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N11:O11"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C7:C8"/>
@@ -5983,6 +5421,31 @@
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="P11:Q11"/>
     <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="I6:O6"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P15:Q15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6015,44 +5478,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="106"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
+      <c r="C3" s="106"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="106"/>
+      <c r="F3" s="106"/>
+      <c r="G3" s="107"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="141" t="s">
+      <c r="B5" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="141"/>
-      <c r="D5" s="141"/>
+      <c r="C5" s="89"/>
+      <c r="D5" s="89"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="133" t="s">
+      <c r="G5" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="133"/>
-      <c r="O5" s="133"/>
-      <c r="P5" s="133"/>
-      <c r="Q5" s="133"/>
-      <c r="R5" s="133"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
     </row>
     <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
@@ -6065,45 +5528,45 @@
         <v>66</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="108" t="s">
+      <c r="G6" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="108" t="s">
+      <c r="H6" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="114" t="s">
+      <c r="J6" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="K6" s="142" t="s">
+      <c r="K6" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="143"/>
-      <c r="M6" s="143"/>
-      <c r="N6" s="143"/>
-      <c r="O6" s="143"/>
-      <c r="P6" s="156"/>
-      <c r="Q6" s="142" t="s">
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="156"/>
+      <c r="R6" s="86"/>
     </row>
     <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="126">
+      <c r="B7" s="97">
         <v>1</v>
       </c>
-      <c r="C7" s="137" t="s">
+      <c r="C7" s="100" t="s">
         <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="135"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="91"/>
+      <c r="J7" s="96"/>
       <c r="K7" s="23" t="s">
         <v>32</v>
       </c>
@@ -6122,14 +5585,14 @@
       <c r="P7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="Q7" s="116" t="s">
+      <c r="Q7" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="R7" s="118"/>
+      <c r="R7" s="109"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="136"/>
-      <c r="C8" s="138"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="101"/>
       <c r="D8" s="2" t="s">
         <v>76</v>
       </c>
@@ -6149,12 +5612,12 @@
       <c r="N8" s="34"/>
       <c r="O8" s="34"/>
       <c r="P8" s="34"/>
-      <c r="Q8" s="157"/>
-      <c r="R8" s="158"/>
+      <c r="Q8" s="80"/>
+      <c r="R8" s="81"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="136"/>
-      <c r="C9" s="138"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="101"/>
       <c r="D9" s="2" t="s">
         <v>78</v>
       </c>
@@ -6184,14 +5647,14 @@
       <c r="P9" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" s="148" t="s">
+      <c r="Q9" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="R9" s="149"/>
+      <c r="R9" s="83"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="136"/>
-      <c r="C10" s="138"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="101"/>
       <c r="D10" s="2" t="s">
         <v>80</v>
       </c>
@@ -6221,14 +5684,14 @@
       <c r="P10" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q10" s="157" t="s">
+      <c r="Q10" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="R10" s="158"/>
+      <c r="R10" s="81"/>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="136"/>
-      <c r="C11" s="138"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="101"/>
       <c r="D11" s="2" t="s">
         <v>84</v>
       </c>
@@ -6258,14 +5721,14 @@
       <c r="P11" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q11" s="157" t="s">
+      <c r="Q11" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="R11" s="158"/>
+      <c r="R11" s="81"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="127"/>
-      <c r="C12" s="139"/>
+      <c r="B12" s="99"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="2" t="s">
         <v>86</v>
       </c>
@@ -6295,16 +5758,16 @@
       <c r="P12" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q12" s="157" t="s">
+      <c r="Q12" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="R12" s="158"/>
+      <c r="R12" s="81"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="126">
+      <c r="B13" s="97">
         <v>2</v>
       </c>
-      <c r="C13" s="126" t="s">
+      <c r="C13" s="97" t="s">
         <v>88</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -6338,14 +5801,14 @@
       <c r="P13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="Q13" s="148" t="s">
+      <c r="Q13" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="R13" s="149"/>
+      <c r="R13" s="83"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="136"/>
-      <c r="C14" s="136"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
       <c r="D14" s="2" t="s">
         <v>91</v>
       </c>
@@ -6367,12 +5830,12 @@
       <c r="N14" s="34"/>
       <c r="O14" s="34"/>
       <c r="P14" s="34"/>
-      <c r="Q14" s="157"/>
-      <c r="R14" s="158"/>
+      <c r="Q14" s="80"/>
+      <c r="R14" s="81"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="136"/>
-      <c r="C15" s="136"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="98"/>
       <c r="D15" s="2" t="s">
         <v>92</v>
       </c>
@@ -6394,12 +5857,12 @@
       <c r="N15" s="34"/>
       <c r="O15" s="34"/>
       <c r="P15" s="34"/>
-      <c r="Q15" s="157"/>
-      <c r="R15" s="158"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="81"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="136"/>
-      <c r="C16" s="136"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="98"/>
       <c r="D16" s="2" t="s">
         <v>93</v>
       </c>
@@ -6415,12 +5878,12 @@
       <c r="N16" s="34"/>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
-      <c r="Q16" s="157"/>
-      <c r="R16" s="158"/>
+      <c r="Q16" s="80"/>
+      <c r="R16" s="81"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="136"/>
-      <c r="C17" s="136"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="98"/>
       <c r="D17" s="2" t="s">
         <v>94</v>
       </c>
@@ -6436,12 +5899,12 @@
       <c r="N17" s="34"/>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
-      <c r="Q17" s="157"/>
-      <c r="R17" s="158"/>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="81"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="127"/>
-      <c r="C18" s="127"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="2" t="s">
         <v>95</v>
       </c>
@@ -6457,14 +5920,14 @@
       <c r="N18" s="34"/>
       <c r="O18" s="34"/>
       <c r="P18" s="34"/>
-      <c r="Q18" s="157"/>
-      <c r="R18" s="158"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="81"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="126">
+      <c r="B19" s="97">
         <v>3</v>
       </c>
-      <c r="C19" s="137" t="s">
+      <c r="C19" s="100" t="s">
         <v>96</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -6482,12 +5945,12 @@
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
       <c r="P19" s="34"/>
-      <c r="Q19" s="157"/>
-      <c r="R19" s="158"/>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="81"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="136"/>
-      <c r="C20" s="138"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="2" t="s">
         <v>98</v>
       </c>
@@ -6503,12 +5966,12 @@
       <c r="N20" s="34"/>
       <c r="O20" s="34"/>
       <c r="P20" s="34"/>
-      <c r="Q20" s="157"/>
-      <c r="R20" s="158"/>
+      <c r="Q20" s="80"/>
+      <c r="R20" s="81"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="136"/>
-      <c r="C21" s="138"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="101"/>
       <c r="D21" s="2" t="s">
         <v>99</v>
       </c>
@@ -6524,12 +5987,12 @@
       <c r="N21" s="34"/>
       <c r="O21" s="34"/>
       <c r="P21" s="34"/>
-      <c r="Q21" s="157"/>
-      <c r="R21" s="158"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="81"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="136"/>
-      <c r="C22" s="138"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="101"/>
       <c r="D22" s="2" t="s">
         <v>100</v>
       </c>
@@ -6545,12 +6008,12 @@
       <c r="N22" s="34"/>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
-      <c r="Q22" s="157"/>
-      <c r="R22" s="158"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="81"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="136"/>
-      <c r="C23" s="138"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="101"/>
       <c r="D23" s="2" t="s">
         <v>101</v>
       </c>
@@ -6566,12 +6029,12 @@
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
       <c r="P23" s="34"/>
-      <c r="Q23" s="157"/>
-      <c r="R23" s="158"/>
+      <c r="Q23" s="80"/>
+      <c r="R23" s="81"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="127"/>
-      <c r="C24" s="139"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="102"/>
       <c r="D24" s="2" t="s">
         <v>102</v>
       </c>
@@ -6587,14 +6050,14 @@
       <c r="N24" s="34"/>
       <c r="O24" s="34"/>
       <c r="P24" s="34"/>
-      <c r="Q24" s="157"/>
-      <c r="R24" s="158"/>
+      <c r="Q24" s="80"/>
+      <c r="R24" s="81"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="126">
+      <c r="B25" s="97">
         <v>4</v>
       </c>
-      <c r="C25" s="137" t="s">
+      <c r="C25" s="100" t="s">
         <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -6612,68 +6075,76 @@
       <c r="N25" s="34"/>
       <c r="O25" s="34"/>
       <c r="P25" s="34"/>
-      <c r="Q25" s="157"/>
-      <c r="R25" s="158"/>
+      <c r="Q25" s="80"/>
+      <c r="R25" s="81"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="136"/>
-      <c r="C26" s="138"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="101"/>
       <c r="D26" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="136"/>
-      <c r="C27" s="138"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="101"/>
       <c r="D27" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="136"/>
-      <c r="C28" s="138"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="101"/>
       <c r="D28" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G28" s="125"/>
-      <c r="H28" s="125"/>
-      <c r="I28" s="155"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="155"/>
-      <c r="L28" s="155"/>
-      <c r="M28" s="155"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="88"/>
+      <c r="L28" s="88"/>
+      <c r="M28" s="88"/>
       <c r="N28" s="43"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="136"/>
-      <c r="C29" s="138"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="101"/>
       <c r="D29" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I29" s="154"/>
-      <c r="J29" s="154"/>
-      <c r="K29" s="154"/>
-      <c r="L29" s="154"/>
-      <c r="M29" s="154"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="103"/>
+      <c r="K29" s="103"/>
+      <c r="L29" s="103"/>
+      <c r="M29" s="103"/>
       <c r="N29" s="44"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="127"/>
-      <c r="C30" s="139"/>
+      <c r="B30" s="99"/>
+      <c r="C30" s="102"/>
       <c r="D30" s="2" t="s">
         <v>49</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K6:P6"/>
-    <mergeCell ref="Q10:R10"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="C25:C30"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
+    <mergeCell ref="C19:C24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="G5:R5"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="Q7:R7"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="I28:M28"/>
     <mergeCell ref="B5:D5"/>
@@ -6690,22 +6161,14 @@
     <mergeCell ref="Q18:R18"/>
     <mergeCell ref="Q8:R8"/>
     <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="C25:C30"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="C7:C12"/>
-    <mergeCell ref="B13:B18"/>
-    <mergeCell ref="C13:C18"/>
-    <mergeCell ref="C19:C24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="G5:R5"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="K6:P6"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q12:R12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6732,62 +6195,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="106"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="94"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="119" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="107"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="107"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="119"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="121" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="112" t="s">
+      <c r="D4" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="114" t="s">
+      <c r="E4" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="116" t="s">
+      <c r="F4" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="119" t="s">
+      <c r="G4" s="114"/>
+      <c r="H4" s="114"/>
+      <c r="I4" s="114"/>
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="119"/>
+      <c r="N4" s="126"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="109"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="115"/>
+      <c r="B5" s="120"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="125"/>
       <c r="F5" s="26" t="s">
         <v>32</v>
       </c>
@@ -6818,7 +6281,7 @@
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="102" t="s">
+      <c r="C6" s="117" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -6860,7 +6323,7 @@
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="102"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="31" t="s">
         <v>112</v>
       </c>
@@ -6898,7 +6361,7 @@
         <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="102"/>
+      <c r="C8" s="117"/>
       <c r="D8" s="31" t="s">
         <v>114</v>
       </c>
@@ -6936,7 +6399,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="102"/>
+      <c r="C9" s="117"/>
       <c r="D9" s="31" t="s">
         <v>49</v>
       </c>
@@ -6958,10 +6421,10 @@
       <c r="J9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="120" t="s">
+      <c r="K9" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="121"/>
+      <c r="L9" s="130"/>
       <c r="M9" s="12" t="s">
         <v>49</v>
       </c>
@@ -6974,7 +6437,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="117"/>
       <c r="D10" s="31" t="s">
         <v>51</v>
       </c>
@@ -6996,10 +6459,10 @@
       <c r="J10" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="84" t="s">
+      <c r="K10" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="L10" s="85"/>
+      <c r="L10" s="128"/>
       <c r="M10" s="6" t="s">
         <v>61</v>
       </c>
@@ -7012,7 +6475,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="102"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
@@ -7034,10 +6497,10 @@
       <c r="J11" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="84" t="s">
+      <c r="K11" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="L11" s="85"/>
+      <c r="L11" s="128"/>
       <c r="M11" s="5" t="s">
         <v>47</v>
       </c>
@@ -7050,7 +6513,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="31" t="s">
         <v>51</v>
       </c>
@@ -7072,10 +6535,10 @@
       <c r="J12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="84" t="s">
+      <c r="K12" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="85"/>
+      <c r="L12" s="128"/>
       <c r="M12" s="5" t="s">
         <v>47</v>
       </c>
@@ -7088,7 +6551,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="103"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="32" t="s">
         <v>49</v>
       </c>
@@ -7110,10 +6573,10 @@
       <c r="J13" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="K13" s="82" t="s">
+      <c r="K13" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="83"/>
+      <c r="L13" s="145"/>
       <c r="M13" s="25" t="s">
         <v>49</v>
       </c>
@@ -7148,98 +6611,98 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="92"/>
-      <c r="L15" s="92"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="150"/>
       <c r="M15" s="7"/>
     </row>
     <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="93" t="s">
+      <c r="C17" s="131" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="95"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="132"/>
+      <c r="F17" s="133"/>
       <c r="G17" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="131" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="96"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="93" t="s">
+      <c r="I17" s="134"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="133"/>
+      <c r="M17" s="131" t="s">
         <v>122</v>
       </c>
-      <c r="N17" s="96"/>
-      <c r="O17" s="94"/>
-      <c r="P17" s="95"/>
+      <c r="N17" s="134"/>
+      <c r="O17" s="132"/>
+      <c r="P17" s="133"/>
     </row>
     <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="97" t="s">
+      <c r="B18" s="135" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="98" t="s">
+      <c r="C18" s="136" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="90" t="s">
+      <c r="D18" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="E18" s="90" t="s">
+      <c r="E18" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="F18" s="91" t="s">
+      <c r="F18" s="138" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="99" t="s">
+      <c r="G18" s="139" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="86" t="s">
+      <c r="H18" s="146" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="87"/>
-      <c r="J18" s="90" t="s">
+      <c r="I18" s="147"/>
+      <c r="J18" s="137" t="s">
         <v>123</v>
       </c>
-      <c r="K18" s="90" t="s">
+      <c r="K18" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="L18" s="91" t="s">
+      <c r="L18" s="138" t="s">
         <v>125</v>
       </c>
-      <c r="M18" s="100" t="s">
+      <c r="M18" s="140" t="s">
         <v>128</v>
       </c>
-      <c r="N18" s="90" t="s">
+      <c r="N18" s="137" t="s">
         <v>123</v>
       </c>
-      <c r="O18" s="90" t="s">
+      <c r="O18" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="P18" s="91" t="s">
+      <c r="P18" s="138" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="97"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="90"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="91"/>
-      <c r="M19" s="101"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="91"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="136"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="138"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="148"/>
+      <c r="I19" s="149"/>
+      <c r="J19" s="137"/>
+      <c r="K19" s="137"/>
+      <c r="L19" s="138"/>
+      <c r="M19" s="141"/>
+      <c r="N19" s="137"/>
+      <c r="O19" s="137"/>
+      <c r="P19" s="138"/>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="42" t="s">
@@ -7256,10 +6719,10 @@
       </c>
       <c r="F20" s="41"/>
       <c r="G20" s="46"/>
-      <c r="H20" s="80" t="s">
+      <c r="H20" s="142" t="s">
         <v>129</v>
       </c>
-      <c r="I20" s="81"/>
+      <c r="I20" s="143"/>
       <c r="J20" s="2">
         <v>3</v>
       </c>
@@ -7287,12 +6750,20 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="L18:L19"/>
-    <mergeCell ref="O18:O19"/>
-    <mergeCell ref="P18:P19"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="N18:N19"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="B3:N3"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="C6:C13"/>
     <mergeCell ref="B4:B5"/>
@@ -7309,20 +6780,12 @@
     <mergeCell ref="H18:I19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="K18:K19"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="F4:L4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="B3:N3"/>
+    <mergeCell ref="L18:L19"/>
+    <mergeCell ref="O18:O19"/>
+    <mergeCell ref="P18:P19"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="N18:N19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7331,12 +6794,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7478,15 +6938,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7510,10 +6974,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47FE877D-432C-44A9-9889-489A1D266CB2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B9CA12-8961-4BEB-8D70-94D8CF82FF06}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
+++ b/docs/Lab02/Lab02_BBT_TCs_Form.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB41C950-DB73-400C-B495-A0D2754EBD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90A9436-E400-4D4A-A92B-AF225327042E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -188,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="211">
   <si>
     <t>VVSS, Info Romana, 2025-2026</t>
   </si>
@@ -1079,6 +1082,12 @@
   </si>
   <si>
     <t>TC9_BVA</t>
+  </si>
+  <si>
+    <t>Sandru Stefan Tiberius</t>
+  </si>
+  <si>
+    <t>Error: type is empty!</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -1830,26 +1839,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="double">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2022,265 +2016,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2292,21 +2028,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2325,6 +2046,276 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2694,37 +2685,37 @@
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
   <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="32.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.53515625" customWidth="1"/>
+    <col min="8" max="8" width="10.69140625" customWidth="1"/>
+    <col min="9" max="9" width="32.84375" customWidth="1"/>
+    <col min="10" max="10" width="10.53515625" customWidth="1"/>
+    <col min="12" max="12" width="12.15234375" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="92" t="s">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="C1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="94"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="98"/>
       <c r="H1" s="51" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="51"/>
       <c r="J1" s="51"/>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="H2" s="111" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="H2" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
         <v>3</v>
@@ -2733,7 +2724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
@@ -2744,7 +2735,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
       <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
@@ -2755,48 +2746,52 @@
         <v>236</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B6" s="37"/>
       <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I6" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J6" s="2">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B8" s="49" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
         <v>12</v>
       </c>
@@ -2804,7 +2799,7 @@
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -2812,7 +2807,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -2820,32 +2815,32 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B18" s="49" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C20" s="47" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B21" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B22" s="1" t="s">
         <v>18</v>
       </c>
@@ -2862,7 +2857,7 @@
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
@@ -2879,25 +2874,25 @@
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
     </row>
-    <row r="24" spans="1:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="48"/>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="110"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="110"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="95"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C26" s="50"/>
     </row>
   </sheetData>
@@ -2917,58 +2912,58 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:M26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.15234375" customWidth="1"/>
+    <col min="4" max="4" width="20.3828125" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" customWidth="1"/>
+    <col min="6" max="6" width="5.84375" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.42578125" customWidth="1"/>
+    <col min="8" max="8" width="17.3046875" customWidth="1"/>
+    <col min="9" max="9" width="14.15234375" customWidth="1"/>
+    <col min="10" max="10" width="25.53515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.69140625" customWidth="1"/>
+    <col min="12" max="12" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B1" s="92" t="s">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B3" s="105" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B3" s="101" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="113" t="s">
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="103"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.4">
+      <c r="B5" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="G5" s="104" t="s">
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="G5" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B6" s="23" t="s">
         <v>23</v>
       </c>
@@ -2981,35 +2976,35 @@
       <c r="E6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="90" t="s">
+      <c r="G6" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="95" t="s">
+      <c r="H6" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
       <c r="M6" s="23" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="112" t="s">
         <v>132</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>132</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="96"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="109"/>
       <c r="I7" s="23" t="s">
         <v>140</v>
       </c>
@@ -3026,11 +3021,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="115"/>
+      <c r="C8" s="112"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>133</v>
@@ -3057,11 +3052,11 @@
         <v>205</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="112" t="s">
+      <c r="C9" s="100" t="s">
         <v>134</v>
       </c>
       <c r="D9" s="59" t="s">
@@ -3090,11 +3085,11 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="112"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>139</v>
@@ -3121,11 +3116,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="115" t="s">
+      <c r="C11" s="112" t="s">
         <v>135</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -3154,11 +3149,11 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="115"/>
+      <c r="C12" s="112"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>136</v>
@@ -3185,11 +3180,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C13" s="114" t="s">
         <v>137</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -3206,11 +3201,11 @@
       <c r="L13" s="9"/>
       <c r="M13" s="78"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="99"/>
+      <c r="C14" s="115"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>138</v>
@@ -3225,11 +3220,11 @@
       <c r="L14" s="9"/>
       <c r="M14" s="78"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="115" t="s">
+      <c r="C15" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="4"/>
@@ -3244,11 +3239,11 @@
       <c r="L15" s="18"/>
       <c r="M15" s="21"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="115"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19">
@@ -3261,11 +3256,11 @@
       <c r="L16" s="18"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="115" t="s">
+      <c r="C17" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="4"/>
@@ -3278,11 +3273,11 @@
       <c r="L17" s="18"/>
       <c r="M17" s="21"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="115"/>
+      <c r="C18" s="112"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -3293,11 +3288,11 @@
       <c r="L18" s="18"/>
       <c r="M18" s="21"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="115" t="s">
+      <c r="C19" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4"/>
@@ -3310,25 +3305,25 @@
       <c r="L19" s="2"/>
       <c r="M19" s="21"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="115"/>
+      <c r="C20" s="112"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.4">
       <c r="D22" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="87"/>
-      <c r="G22" s="87"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.4">
       <c r="M24" s="65"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.4">
       <c r="M26" s="64"/>
     </row>
   </sheetData>
@@ -3360,61 +3355,61 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:O31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.69140625" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="5.53515625" customWidth="1"/>
+    <col min="7" max="7" width="9.3828125" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.28515625" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="33.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.3828125" customWidth="1"/>
+    <col min="12" max="12" width="18.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.3046875" customWidth="1"/>
+    <col min="14" max="14" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33.15234375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B1" s="92" t="s">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="116" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B3" s="120" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107"/>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="103"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B5" s="121" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="104" t="s">
+      <c r="G5" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
-    </row>
-    <row r="6" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+    </row>
+    <row r="6" spans="2:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
         <v>68</v>
       </c>
@@ -3425,42 +3420,42 @@
         <v>66</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="90" t="s">
+      <c r="G6" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="90" t="s">
+      <c r="H6" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="90" t="s">
+      <c r="I6" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="95" t="s">
+      <c r="J6" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="K6" s="84" t="s">
+      <c r="K6" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="123"/>
+      <c r="N6" s="123"/>
       <c r="O6" s="56" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="97">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B7" s="114">
         <v>1</v>
       </c>
-      <c r="C7" s="100" t="s">
+      <c r="C7" s="117" t="s">
         <v>151</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="96"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="109"/>
       <c r="K7" s="23" t="s">
         <v>140</v>
       </c>
@@ -3477,9 +3472,9 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="98"/>
-      <c r="C8" s="101"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B8" s="116"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="2" t="s">
         <v>153</v>
       </c>
@@ -3509,9 +3504,9 @@
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="98"/>
-      <c r="C9" s="101"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B9" s="116"/>
+      <c r="C9" s="118"/>
       <c r="D9" s="2" t="s">
         <v>154</v>
       </c>
@@ -3543,9 +3538,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="98"/>
-      <c r="C10" s="101"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B10" s="116"/>
+      <c r="C10" s="118"/>
       <c r="D10" s="2" t="s">
         <v>155</v>
       </c>
@@ -3575,9 +3570,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="98"/>
-      <c r="C11" s="101"/>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B11" s="116"/>
+      <c r="C11" s="118"/>
       <c r="D11" s="2" t="s">
         <v>156</v>
       </c>
@@ -3607,9 +3602,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="99"/>
-      <c r="C12" s="102"/>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B12" s="115"/>
+      <c r="C12" s="119"/>
       <c r="D12" s="2" t="s">
         <v>157</v>
       </c>
@@ -3639,11 +3634,11 @@
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="97">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B13" s="114">
         <v>2</v>
       </c>
-      <c r="C13" s="100" t="s">
+      <c r="C13" s="117" t="s">
         <v>134</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -3677,9 +3672,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="98"/>
-      <c r="C14" s="101"/>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B14" s="116"/>
+      <c r="C14" s="118"/>
       <c r="D14" s="2" t="s">
         <v>159</v>
       </c>
@@ -3709,9 +3704,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="98"/>
-      <c r="C15" s="101"/>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B15" s="116"/>
+      <c r="C15" s="118"/>
       <c r="D15" s="2" t="s">
         <v>160</v>
       </c>
@@ -3741,9 +3736,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="98"/>
-      <c r="C16" s="101"/>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B16" s="116"/>
+      <c r="C16" s="118"/>
       <c r="D16" s="2" t="s">
         <v>161</v>
       </c>
@@ -3773,9 +3768,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="98"/>
-      <c r="C17" s="101"/>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B17" s="116"/>
+      <c r="C17" s="118"/>
       <c r="D17" s="2" t="s">
         <v>162</v>
       </c>
@@ -3805,9 +3800,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="99"/>
-      <c r="C18" s="102"/>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B18" s="115"/>
+      <c r="C18" s="119"/>
       <c r="D18" s="2" t="s">
         <v>163</v>
       </c>
@@ -3839,11 +3834,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="97">
+    <row r="19" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="114">
         <v>3</v>
       </c>
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="117" t="s">
         <v>135</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -3875,9 +3870,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="98"/>
-      <c r="C20" s="101"/>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B20" s="116"/>
+      <c r="C20" s="118"/>
       <c r="D20" s="2" t="s">
         <v>176</v>
       </c>
@@ -3907,9 +3902,9 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="98"/>
-      <c r="C21" s="101"/>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B21" s="116"/>
+      <c r="C21" s="118"/>
       <c r="D21" s="2" t="s">
         <v>177</v>
       </c>
@@ -3941,9 +3936,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="98"/>
-      <c r="C22" s="101"/>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B22" s="116"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="2" t="s">
         <v>178</v>
       </c>
@@ -3973,9 +3968,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="98"/>
-      <c r="C23" s="101"/>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B23" s="116"/>
+      <c r="C23" s="118"/>
       <c r="D23" s="2" t="s">
         <v>179</v>
       </c>
@@ -4005,9 +4000,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="99"/>
-      <c r="C24" s="102"/>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B24" s="115"/>
+      <c r="C24" s="119"/>
       <c r="D24" s="2" t="s">
         <v>180</v>
       </c>
@@ -4037,11 +4032,11 @@
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="97">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B25" s="114">
         <v>4</v>
       </c>
-      <c r="C25" s="100" t="s">
+      <c r="C25" s="117" t="s">
         <v>137</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -4075,9 +4070,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="98"/>
-      <c r="C26" s="101"/>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B26" s="116"/>
+      <c r="C26" s="118"/>
       <c r="D26" s="2" t="s">
         <v>182</v>
       </c>
@@ -4104,12 +4099,12 @@
         <v>54</v>
       </c>
       <c r="O26" s="57" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="98"/>
-      <c r="C27" s="101"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B27" s="116"/>
+      <c r="C27" s="118"/>
       <c r="D27" s="2" t="s">
         <v>183</v>
       </c>
@@ -4141,9 +4136,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="98"/>
-      <c r="C28" s="101"/>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B28" s="116"/>
+      <c r="C28" s="118"/>
       <c r="D28" s="2" t="s">
         <v>184</v>
       </c>
@@ -4173,9 +4168,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="98"/>
-      <c r="C29" s="101"/>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B29" s="116"/>
+      <c r="C29" s="118"/>
       <c r="D29" s="2" t="s">
         <v>185</v>
       </c>
@@ -4205,9 +4200,9 @@
         <v>205</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="99"/>
-      <c r="C30" s="102"/>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B30" s="115"/>
+      <c r="C30" s="119"/>
       <c r="D30" s="2" t="s">
         <v>186</v>
       </c>
@@ -4237,7 +4232,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.4">
       <c r="G31" s="67">
         <v>24</v>
       </c>
@@ -4296,77 +4291,77 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:P22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
-    <col min="13" max="13" width="35.140625" customWidth="1"/>
-    <col min="14" max="14" width="22.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.3046875" customWidth="1"/>
+    <col min="6" max="6" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.53515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.3828125" customWidth="1"/>
+    <col min="9" max="9" width="13.15234375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.84375" customWidth="1"/>
+    <col min="13" max="13" width="35.15234375" customWidth="1"/>
+    <col min="14" max="14" width="22.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="92" t="s">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="119" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B3" s="127" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="90" t="s">
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B4" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="123" t="s">
+      <c r="D4" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="95" t="s">
+      <c r="E4" s="108" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="108" t="s">
+      <c r="F4" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="126" t="s">
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="126"/>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="120"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="125"/>
+      <c r="N4" s="135"/>
+    </row>
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="128"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="133"/>
       <c r="F5" s="26" t="s">
         <v>140</v>
       </c>
@@ -4389,44 +4384,46 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="165">
+    <row r="6" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="80">
         <v>1</v>
       </c>
-      <c r="C6" s="166" t="s">
+      <c r="C6" s="124" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="79" t="s">
         <v>198</v>
       </c>
-      <c r="E6" s="167" t="s">
+      <c r="E6" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="168" t="s">
+      <c r="F6" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="G6" s="169">
+      <c r="G6" s="83">
         <v>10.4</v>
       </c>
-      <c r="H6" s="168" t="s">
+      <c r="H6" s="82" t="s">
         <v>145</v>
       </c>
-      <c r="I6" s="168" t="s">
+      <c r="I6" s="82" t="s">
         <v>144</v>
       </c>
-      <c r="J6" s="170"/>
+      <c r="J6" s="84"/>
       <c r="K6" s="73"/>
       <c r="L6" s="74"/>
-      <c r="M6" s="171" t="s">
+      <c r="M6" s="85" t="s">
         <v>205</v>
       </c>
-      <c r="N6" s="172"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N6" s="85" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B7" s="58">
         <v>2</v>
       </c>
-      <c r="C7" s="173"/>
+      <c r="C7" s="125"/>
       <c r="D7" s="31" t="s">
         <v>199</v>
       </c>
@@ -4451,13 +4448,15 @@
       <c r="M7" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="N7" s="174"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="165">
+      <c r="N7" s="93" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B8" s="80">
         <v>3</v>
       </c>
-      <c r="C8" s="173"/>
+      <c r="C8" s="125"/>
       <c r="D8" s="31" t="s">
         <v>200</v>
       </c>
@@ -4482,13 +4481,15 @@
       <c r="M8" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="N8" s="174"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="165">
+      <c r="N8" s="70" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B9" s="80">
         <v>4</v>
       </c>
-      <c r="C9" s="173"/>
+      <c r="C9" s="125"/>
       <c r="D9" s="30" t="s">
         <v>201</v>
       </c>
@@ -4513,13 +4514,15 @@
       <c r="M9" s="70" t="s">
         <v>148</v>
       </c>
-      <c r="N9" s="174"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N9" s="70" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B10" s="58">
         <v>5</v>
       </c>
-      <c r="C10" s="173"/>
+      <c r="C10" s="125"/>
       <c r="D10" s="30" t="s">
         <v>202</v>
       </c>
@@ -4544,13 +4547,15 @@
       <c r="M10" s="70" t="s">
         <v>149</v>
       </c>
-      <c r="N10" s="174"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="165">
+      <c r="N10" s="70" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B11" s="80">
         <v>6</v>
       </c>
-      <c r="C11" s="173"/>
+      <c r="C11" s="125"/>
       <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
@@ -4570,18 +4575,20 @@
         <v>144</v>
       </c>
       <c r="J11" s="67"/>
-      <c r="K11" s="177"/>
-      <c r="L11" s="178"/>
+      <c r="K11" s="86"/>
+      <c r="L11" s="87"/>
       <c r="M11" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="N11" s="174"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N11" s="94" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B12" s="58">
         <v>7</v>
       </c>
-      <c r="C12" s="173"/>
+      <c r="C12" s="125"/>
       <c r="D12" s="31" t="s">
         <v>51</v>
       </c>
@@ -4601,18 +4608,20 @@
         <v>144</v>
       </c>
       <c r="J12" s="67"/>
-      <c r="K12" s="177"/>
-      <c r="L12" s="178"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="87"/>
       <c r="M12" s="57" t="s">
         <v>205</v>
       </c>
-      <c r="N12" s="174"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="165">
+      <c r="N12" s="94" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B13" s="80">
         <v>8</v>
       </c>
-      <c r="C13" s="173"/>
+      <c r="C13" s="125"/>
       <c r="D13" s="31" t="s">
         <v>51</v>
       </c>
@@ -4632,45 +4641,49 @@
         <v>144</v>
       </c>
       <c r="J13" s="67"/>
-      <c r="K13" s="177"/>
-      <c r="L13" s="178"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="87"/>
       <c r="M13" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="N13" s="174"/>
-    </row>
-    <row r="14" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="165">
+      <c r="N13" s="94" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="80">
         <v>9</v>
       </c>
-      <c r="C14" s="175"/>
+      <c r="C14" s="126"/>
       <c r="D14" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="179" t="s">
+      <c r="E14" s="88" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="180" t="s">
+      <c r="F14" s="89" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="180">
+      <c r="G14" s="89">
         <v>1</v>
       </c>
-      <c r="H14" s="180" t="s">
+      <c r="H14" s="89" t="s">
         <v>145</v>
       </c>
-      <c r="I14" s="180" t="s">
+      <c r="I14" s="89" t="s">
         <v>144</v>
       </c>
-      <c r="J14" s="179"/>
-      <c r="K14" s="181"/>
-      <c r="L14" s="182"/>
-      <c r="M14" s="183" t="s">
+      <c r="J14" s="88"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="92" t="s">
         <v>205</v>
       </c>
-      <c r="N14" s="176"/>
-    </row>
-    <row r="15" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="N14" s="92" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B15" s="27"/>
       <c r="C15" s="27"/>
       <c r="D15" s="28"/>
@@ -4685,7 +4698,7 @@
       <c r="M15" s="27"/>
       <c r="N15" s="27"/>
     </row>
-    <row r="16" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="27" t="s">
         <v>118</v>
       </c>
@@ -4697,100 +4710,100 @@
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="150"/>
+      <c r="K16" s="136"/>
+      <c r="L16" s="136"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="131" t="s">
+    <row r="18" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="C18" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="133"/>
+      <c r="D18" s="138"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="139"/>
       <c r="G18" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="H18" s="131" t="s">
+      <c r="H18" s="137" t="s">
         <v>121</v>
       </c>
-      <c r="I18" s="134"/>
-      <c r="J18" s="132"/>
-      <c r="K18" s="132"/>
-      <c r="L18" s="133"/>
-      <c r="M18" s="131" t="s">
+      <c r="I18" s="140"/>
+      <c r="J18" s="138"/>
+      <c r="K18" s="138"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="137" t="s">
         <v>122</v>
       </c>
-      <c r="N18" s="134"/>
-      <c r="O18" s="132"/>
-      <c r="P18" s="133"/>
-    </row>
-    <row r="19" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="135" t="s">
+      <c r="N18" s="140"/>
+      <c r="O18" s="138"/>
+      <c r="P18" s="139"/>
+    </row>
+    <row r="19" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="137" t="s">
+      <c r="D19" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="E19" s="137" t="s">
+      <c r="E19" s="143" t="s">
         <v>125</v>
       </c>
-      <c r="F19" s="138" t="s">
+      <c r="F19" s="144" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="139" t="s">
+      <c r="G19" s="145" t="s">
         <v>127</v>
       </c>
-      <c r="H19" s="146" t="s">
+      <c r="H19" s="150" t="s">
         <v>128</v>
       </c>
-      <c r="I19" s="147"/>
-      <c r="J19" s="137" t="s">
+      <c r="I19" s="151"/>
+      <c r="J19" s="143" t="s">
         <v>123</v>
       </c>
-      <c r="K19" s="137" t="s">
+      <c r="K19" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="L19" s="138" t="s">
+      <c r="L19" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="M19" s="140" t="s">
+      <c r="M19" s="146" t="s">
         <v>128</v>
       </c>
-      <c r="N19" s="137" t="s">
+      <c r="N19" s="143" t="s">
         <v>123</v>
       </c>
-      <c r="O19" s="137" t="s">
+      <c r="O19" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="P19" s="138" t="s">
+      <c r="P19" s="144" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B20" s="135"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="139"/>
-      <c r="H20" s="148"/>
-      <c r="I20" s="149"/>
-      <c r="J20" s="137"/>
-      <c r="K20" s="137"/>
-      <c r="L20" s="138"/>
-      <c r="M20" s="141"/>
-      <c r="N20" s="137"/>
-      <c r="O20" s="137"/>
-      <c r="P20" s="138"/>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B20" s="141"/>
+      <c r="C20" s="142"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="145"/>
+      <c r="H20" s="152"/>
+      <c r="I20" s="153"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="143"/>
+      <c r="L20" s="144"/>
+      <c r="M20" s="147"/>
+      <c r="N20" s="143"/>
+      <c r="O20" s="143"/>
+      <c r="P20" s="144"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B21" s="42" t="s">
         <v>109</v>
       </c>
@@ -4805,10 +4818,10 @@
       </c>
       <c r="F21" s="41"/>
       <c r="G21" s="46"/>
-      <c r="H21" s="142" t="s">
+      <c r="H21" s="148" t="s">
         <v>129</v>
       </c>
-      <c r="I21" s="143"/>
+      <c r="I21" s="149"/>
       <c r="J21" s="2">
         <v>0</v>
       </c>
@@ -4831,7 +4844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.4">
       <c r="M22" s="3"/>
     </row>
   </sheetData>
@@ -4876,63 +4889,63 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:Q22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.15234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.84375" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.53515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.3828125" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B1" s="92" t="s">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-    </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="105" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B3" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107"/>
-    </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="113" t="s">
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="103"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.4">
+      <c r="B5" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="G5" s="104" t="s">
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="G5" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="104"/>
-      <c r="Q5" s="104"/>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B6" s="23" t="s">
         <v>23</v>
       </c>
@@ -4945,39 +4958,39 @@
       <c r="E6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="90" t="s">
+      <c r="G6" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="95" t="s">
+      <c r="H6" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="114"/>
-      <c r="N6" s="114"/>
-      <c r="O6" s="109"/>
-      <c r="P6" s="126" t="s">
+      <c r="J6" s="111"/>
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="134"/>
+      <c r="P6" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="Q6" s="126"/>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q6" s="135"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="115" t="s">
+      <c r="C7" s="112" t="s">
         <v>31</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="91"/>
-      <c r="H7" s="96"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="109"/>
       <c r="I7" s="23" t="s">
         <v>32</v>
       </c>
@@ -4993,20 +5006,20 @@
       <c r="M7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N7" s="108" t="s">
+      <c r="N7" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="109"/>
-      <c r="P7" s="108" t="s">
+      <c r="O7" s="134"/>
+      <c r="P7" s="110" t="s">
         <v>38</v>
       </c>
-      <c r="Q7" s="109"/>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q7" s="134"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="115"/>
+      <c r="C8" s="112"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
         <v>39</v>
@@ -5032,22 +5045,22 @@
       <c r="M8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="N8" s="151" t="s">
+      <c r="N8" s="154" t="s">
         <v>45</v>
       </c>
-      <c r="O8" s="152" t="s">
+      <c r="O8" s="155" t="s">
         <v>46</v>
       </c>
-      <c r="P8" s="151" t="s">
+      <c r="P8" s="154" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="152"/>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q8" s="155"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B9" s="4">
         <v>3</v>
       </c>
-      <c r="C9" s="115" t="s">
+      <c r="C9" s="112" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -5075,22 +5088,22 @@
       <c r="M9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="151" t="s">
+      <c r="N9" s="154" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="152" t="s">
+      <c r="O9" s="155" t="s">
         <v>51</v>
       </c>
-      <c r="P9" s="151" t="s">
+      <c r="P9" s="154" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" s="152"/>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q9" s="155"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B10" s="4">
         <v>4</v>
       </c>
-      <c r="C10" s="115"/>
+      <c r="C10" s="112"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
         <v>52</v>
@@ -5116,20 +5129,20 @@
       <c r="M10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="N10" s="155" t="s">
+      <c r="N10" s="160" t="s">
         <v>45</v>
       </c>
-      <c r="O10" s="156"/>
-      <c r="P10" s="155" t="s">
+      <c r="O10" s="161"/>
+      <c r="P10" s="160" t="s">
         <v>55</v>
       </c>
-      <c r="Q10" s="156"/>
-    </row>
-    <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q10" s="161"/>
+    </row>
+    <row r="11" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="4">
         <v>5</v>
       </c>
-      <c r="C11" s="115" t="s">
+      <c r="C11" s="112" t="s">
         <v>56</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -5157,20 +5170,20 @@
       <c r="M11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="155" t="s">
+      <c r="N11" s="160" t="s">
         <v>49</v>
       </c>
-      <c r="O11" s="156"/>
-      <c r="P11" s="155" t="s">
+      <c r="O11" s="161"/>
+      <c r="P11" s="160" t="s">
         <v>49</v>
       </c>
-      <c r="Q11" s="156"/>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q11" s="161"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B12" s="4">
         <v>6</v>
       </c>
-      <c r="C12" s="115"/>
+      <c r="C12" s="112"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
         <v>58</v>
@@ -5200,16 +5213,16 @@
         <v>45</v>
       </c>
       <c r="O12" s="9"/>
-      <c r="P12" s="82" t="s">
+      <c r="P12" s="158" t="s">
         <v>61</v>
       </c>
-      <c r="Q12" s="83"/>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q12" s="159"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C13" s="114" t="s">
         <v>62</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -5237,20 +5250,20 @@
       <c r="M13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="82" t="s">
+      <c r="N13" s="158" t="s">
         <v>49</v>
       </c>
-      <c r="O13" s="83"/>
-      <c r="P13" s="82" t="s">
+      <c r="O13" s="159"/>
+      <c r="P13" s="158" t="s">
         <v>49</v>
       </c>
-      <c r="Q13" s="83"/>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q13" s="159"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="99"/>
+      <c r="C14" s="115"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
         <v>63</v>
@@ -5276,18 +5289,18 @@
       <c r="M14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="157" t="s">
+      <c r="N14" s="162" t="s">
         <v>64</v>
       </c>
-      <c r="O14" s="158"/>
-      <c r="P14" s="153"/>
-      <c r="Q14" s="154"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="O14" s="163"/>
+      <c r="P14" s="156"/>
+      <c r="Q14" s="157"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="115" t="s">
+      <c r="C15" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="4"/>
@@ -5303,16 +5316,16 @@
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="18"/>
-      <c r="N15" s="151"/>
-      <c r="O15" s="152"/>
-      <c r="P15" s="153"/>
-      <c r="Q15" s="154"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N15" s="154"/>
+      <c r="O15" s="155"/>
+      <c r="P15" s="156"/>
+      <c r="Q15" s="157"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B16" s="4">
         <v>10</v>
       </c>
-      <c r="C16" s="115"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="G16" s="19"/>
@@ -5322,16 +5335,16 @@
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="18"/>
-      <c r="N16" s="151"/>
-      <c r="O16" s="152"/>
-      <c r="P16" s="153"/>
-      <c r="Q16" s="154"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N16" s="154"/>
+      <c r="O16" s="155"/>
+      <c r="P16" s="156"/>
+      <c r="Q16" s="157"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B17" s="4">
         <v>11</v>
       </c>
-      <c r="C17" s="115" t="s">
+      <c r="C17" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D17" s="4"/>
@@ -5343,16 +5356,16 @@
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
-      <c r="N17" s="151"/>
-      <c r="O17" s="152"/>
-      <c r="P17" s="153"/>
-      <c r="Q17" s="154"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N17" s="154"/>
+      <c r="O17" s="155"/>
+      <c r="P17" s="156"/>
+      <c r="Q17" s="157"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B18" s="4">
         <v>12</v>
       </c>
-      <c r="C18" s="115"/>
+      <c r="C18" s="112"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="G18" s="19"/>
@@ -5362,16 +5375,16 @@
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18"/>
-      <c r="N18" s="151"/>
-      <c r="O18" s="152"/>
-      <c r="P18" s="153"/>
-      <c r="Q18" s="154"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N18" s="154"/>
+      <c r="O18" s="155"/>
+      <c r="P18" s="156"/>
+      <c r="Q18" s="157"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B19" s="4">
         <v>13</v>
       </c>
-      <c r="C19" s="115" t="s">
+      <c r="C19" s="112" t="s">
         <v>49</v>
       </c>
       <c r="D19" s="4"/>
@@ -5383,25 +5396,25 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="151"/>
-      <c r="O19" s="152"/>
-      <c r="P19" s="153"/>
-      <c r="Q19" s="154"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="N19" s="154"/>
+      <c r="O19" s="155"/>
+      <c r="P19" s="156"/>
+      <c r="Q19" s="157"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.4">
       <c r="B20" s="4">
         <v>14</v>
       </c>
-      <c r="C20" s="115"/>
+      <c r="C20" s="112"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.4">
       <c r="D22" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="87"/>
-      <c r="G22" s="87"/>
+      <c r="F22" s="113"/>
+      <c r="G22" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -5457,67 +5470,67 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="B1:R30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.15234375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="5.53515625" customWidth="1"/>
+    <col min="7" max="7" width="9.3828125" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" customWidth="1"/>
-    <col min="18" max="18" width="9.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.15234375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.53515625" customWidth="1"/>
+    <col min="12" max="12" width="18.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.84375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.15234375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.3046875" customWidth="1"/>
+    <col min="18" max="18" width="9.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B1" s="92" t="s">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="105" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="3" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B3" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107"/>
-    </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="89" t="s">
+      <c r="C3" s="102"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="103"/>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B5" s="121" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
       <c r="E5" s="3"/>
-      <c r="G5" s="104" t="s">
+      <c r="G5" s="105" t="s">
         <v>67</v>
       </c>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="104"/>
-      <c r="N5" s="104"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="104"/>
-      <c r="Q5" s="104"/>
-      <c r="R5" s="104"/>
-    </row>
-    <row r="6" spans="2:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="105"/>
+      <c r="M5" s="105"/>
+      <c r="N5" s="105"/>
+      <c r="O5" s="105"/>
+      <c r="P5" s="105"/>
+      <c r="Q5" s="105"/>
+      <c r="R5" s="105"/>
+    </row>
+    <row r="6" spans="2:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
         <v>68</v>
       </c>
@@ -5528,45 +5541,45 @@
         <v>66</v>
       </c>
       <c r="E6" s="10"/>
-      <c r="G6" s="90" t="s">
+      <c r="G6" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="90" t="s">
+      <c r="H6" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="90" t="s">
+      <c r="I6" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="95" t="s">
+      <c r="J6" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="K6" s="84" t="s">
+      <c r="K6" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="86"/>
-      <c r="Q6" s="84" t="s">
+      <c r="L6" s="123"/>
+      <c r="M6" s="123"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="166"/>
+      <c r="Q6" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="86"/>
-    </row>
-    <row r="7" spans="2:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="97">
+      <c r="R6" s="166"/>
+    </row>
+    <row r="7" spans="2:18" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="B7" s="114">
         <v>1</v>
       </c>
-      <c r="C7" s="100" t="s">
+      <c r="C7" s="117" t="s">
         <v>73</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91"/>
-      <c r="I7" s="91"/>
-      <c r="J7" s="96"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="109"/>
       <c r="K7" s="23" t="s">
         <v>32</v>
       </c>
@@ -5585,14 +5598,14 @@
       <c r="P7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="Q7" s="108" t="s">
+      <c r="Q7" s="110" t="s">
         <v>75</v>
       </c>
-      <c r="R7" s="109"/>
-    </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="98"/>
-      <c r="C8" s="101"/>
+      <c r="R7" s="134"/>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B8" s="116"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="2" t="s">
         <v>76</v>
       </c>
@@ -5612,12 +5625,12 @@
       <c r="N8" s="34"/>
       <c r="O8" s="34"/>
       <c r="P8" s="34"/>
-      <c r="Q8" s="80"/>
-      <c r="R8" s="81"/>
-    </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="98"/>
-      <c r="C9" s="101"/>
+      <c r="Q8" s="164"/>
+      <c r="R8" s="165"/>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B9" s="116"/>
+      <c r="C9" s="118"/>
       <c r="D9" s="2" t="s">
         <v>78</v>
       </c>
@@ -5647,14 +5660,14 @@
       <c r="P9" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="Q9" s="82" t="s">
+      <c r="Q9" s="158" t="s">
         <v>61</v>
       </c>
-      <c r="R9" s="83"/>
-    </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="98"/>
-      <c r="C10" s="101"/>
+      <c r="R9" s="159"/>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B10" s="116"/>
+      <c r="C10" s="118"/>
       <c r="D10" s="2" t="s">
         <v>80</v>
       </c>
@@ -5684,14 +5697,14 @@
       <c r="P10" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q10" s="80" t="s">
+      <c r="Q10" s="164" t="s">
         <v>47</v>
       </c>
-      <c r="R10" s="81"/>
-    </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="98"/>
-      <c r="C11" s="101"/>
+      <c r="R10" s="165"/>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B11" s="116"/>
+      <c r="C11" s="118"/>
       <c r="D11" s="2" t="s">
         <v>84</v>
       </c>
@@ -5721,14 +5734,14 @@
       <c r="P11" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q11" s="80" t="s">
+      <c r="Q11" s="164" t="s">
         <v>47</v>
       </c>
-      <c r="R11" s="81"/>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="99"/>
-      <c r="C12" s="102"/>
+      <c r="R11" s="165"/>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B12" s="115"/>
+      <c r="C12" s="119"/>
       <c r="D12" s="2" t="s">
         <v>86</v>
       </c>
@@ -5758,16 +5771,16 @@
       <c r="P12" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Q12" s="80" t="s">
+      <c r="Q12" s="164" t="s">
         <v>47</v>
       </c>
-      <c r="R12" s="81"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="97">
+      <c r="R12" s="165"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B13" s="114">
         <v>2</v>
       </c>
-      <c r="C13" s="97" t="s">
+      <c r="C13" s="114" t="s">
         <v>88</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -5801,14 +5814,14 @@
       <c r="P13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="Q13" s="82" t="s">
+      <c r="Q13" s="158" t="s">
         <v>61</v>
       </c>
-      <c r="R13" s="83"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
+      <c r="R13" s="159"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
       <c r="D14" s="2" t="s">
         <v>91</v>
       </c>
@@ -5830,12 +5843,12 @@
       <c r="N14" s="34"/>
       <c r="O14" s="34"/>
       <c r="P14" s="34"/>
-      <c r="Q14" s="80"/>
-      <c r="R14" s="81"/>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
+      <c r="Q14" s="164"/>
+      <c r="R14" s="165"/>
+    </row>
+    <row r="15" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
       <c r="D15" s="2" t="s">
         <v>92</v>
       </c>
@@ -5857,12 +5870,12 @@
       <c r="N15" s="34"/>
       <c r="O15" s="34"/>
       <c r="P15" s="34"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="81"/>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
+      <c r="Q15" s="164"/>
+      <c r="R15" s="165"/>
+    </row>
+    <row r="16" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
       <c r="D16" s="2" t="s">
         <v>93</v>
       </c>
@@ -5878,12 +5891,12 @@
       <c r="N16" s="34"/>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
-      <c r="Q16" s="80"/>
-      <c r="R16" s="81"/>
-    </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="98"/>
-      <c r="C17" s="98"/>
+      <c r="Q16" s="164"/>
+      <c r="R16" s="165"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B17" s="116"/>
+      <c r="C17" s="116"/>
       <c r="D17" s="2" t="s">
         <v>94</v>
       </c>
@@ -5899,12 +5912,12 @@
       <c r="N17" s="34"/>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
-      <c r="Q17" s="80"/>
-      <c r="R17" s="81"/>
-    </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="99"/>
-      <c r="C18" s="99"/>
+      <c r="Q17" s="164"/>
+      <c r="R17" s="165"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B18" s="115"/>
+      <c r="C18" s="115"/>
       <c r="D18" s="2" t="s">
         <v>95</v>
       </c>
@@ -5920,14 +5933,14 @@
       <c r="N18" s="34"/>
       <c r="O18" s="34"/>
       <c r="P18" s="34"/>
-      <c r="Q18" s="80"/>
-      <c r="R18" s="81"/>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="97">
+      <c r="Q18" s="164"/>
+      <c r="R18" s="165"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B19" s="114">
         <v>3</v>
       </c>
-      <c r="C19" s="100" t="s">
+      <c r="C19" s="117" t="s">
         <v>96</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -5945,12 +5958,12 @@
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
       <c r="P19" s="34"/>
-      <c r="Q19" s="80"/>
-      <c r="R19" s="81"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="98"/>
-      <c r="C20" s="101"/>
+      <c r="Q19" s="164"/>
+      <c r="R19" s="165"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B20" s="116"/>
+      <c r="C20" s="118"/>
       <c r="D20" s="2" t="s">
         <v>98</v>
       </c>
@@ -5966,12 +5979,12 @@
       <c r="N20" s="34"/>
       <c r="O20" s="34"/>
       <c r="P20" s="34"/>
-      <c r="Q20" s="80"/>
-      <c r="R20" s="81"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B21" s="98"/>
-      <c r="C21" s="101"/>
+      <c r="Q20" s="164"/>
+      <c r="R20" s="165"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B21" s="116"/>
+      <c r="C21" s="118"/>
       <c r="D21" s="2" t="s">
         <v>99</v>
       </c>
@@ -5987,12 +6000,12 @@
       <c r="N21" s="34"/>
       <c r="O21" s="34"/>
       <c r="P21" s="34"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="81"/>
-    </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="98"/>
-      <c r="C22" s="101"/>
+      <c r="Q21" s="164"/>
+      <c r="R21" s="165"/>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B22" s="116"/>
+      <c r="C22" s="118"/>
       <c r="D22" s="2" t="s">
         <v>100</v>
       </c>
@@ -6008,12 +6021,12 @@
       <c r="N22" s="34"/>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="81"/>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B23" s="98"/>
-      <c r="C23" s="101"/>
+      <c r="Q22" s="164"/>
+      <c r="R22" s="165"/>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B23" s="116"/>
+      <c r="C23" s="118"/>
       <c r="D23" s="2" t="s">
         <v>101</v>
       </c>
@@ -6029,12 +6042,12 @@
       <c r="N23" s="34"/>
       <c r="O23" s="34"/>
       <c r="P23" s="34"/>
-      <c r="Q23" s="80"/>
-      <c r="R23" s="81"/>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B24" s="99"/>
-      <c r="C24" s="102"/>
+      <c r="Q23" s="164"/>
+      <c r="R23" s="165"/>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B24" s="115"/>
+      <c r="C24" s="119"/>
       <c r="D24" s="2" t="s">
         <v>102</v>
       </c>
@@ -6050,14 +6063,14 @@
       <c r="N24" s="34"/>
       <c r="O24" s="34"/>
       <c r="P24" s="34"/>
-      <c r="Q24" s="80"/>
-      <c r="R24" s="81"/>
-    </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B25" s="97">
+      <c r="Q24" s="164"/>
+      <c r="R24" s="165"/>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B25" s="114">
         <v>4</v>
       </c>
-      <c r="C25" s="100" t="s">
+      <c r="C25" s="117" t="s">
         <v>49</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -6075,54 +6088,54 @@
       <c r="N25" s="34"/>
       <c r="O25" s="34"/>
       <c r="P25" s="34"/>
-      <c r="Q25" s="80"/>
-      <c r="R25" s="81"/>
-    </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="98"/>
-      <c r="C26" s="101"/>
+      <c r="Q25" s="164"/>
+      <c r="R25" s="165"/>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B26" s="116"/>
+      <c r="C26" s="118"/>
       <c r="D26" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B27" s="98"/>
-      <c r="C27" s="101"/>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B27" s="116"/>
+      <c r="C27" s="118"/>
       <c r="D27" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B28" s="98"/>
-      <c r="C28" s="101"/>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B28" s="116"/>
+      <c r="C28" s="118"/>
       <c r="D28" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G28" s="87"/>
-      <c r="H28" s="87"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="167"/>
+      <c r="J28" s="167"/>
+      <c r="K28" s="167"/>
+      <c r="L28" s="167"/>
+      <c r="M28" s="167"/>
       <c r="N28" s="43"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B29" s="98"/>
-      <c r="C29" s="101"/>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B29" s="116"/>
+      <c r="C29" s="118"/>
       <c r="D29" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I29" s="103"/>
-      <c r="J29" s="103"/>
-      <c r="K29" s="103"/>
-      <c r="L29" s="103"/>
-      <c r="M29" s="103"/>
+      <c r="I29" s="168"/>
+      <c r="J29" s="168"/>
+      <c r="K29" s="168"/>
+      <c r="L29" s="168"/>
+      <c r="M29" s="168"/>
       <c r="N29" s="44"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B30" s="99"/>
-      <c r="C30" s="102"/>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B30" s="115"/>
+      <c r="C30" s="119"/>
       <c r="D30" s="2" t="s">
         <v>49</v>
       </c>
@@ -6182,75 +6195,75 @@
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="B1:P21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
-    <col min="13" max="13" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.15234375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.53515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.53515625" customWidth="1"/>
+    <col min="9" max="9" width="13.15234375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.84375" customWidth="1"/>
+    <col min="13" max="13" width="30.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="92" t="s">
+    <row r="1" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="94"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="119" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B3" s="127" t="s">
         <v>103</v>
       </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
-      <c r="G3" s="119"/>
-      <c r="H3" s="119"/>
-      <c r="I3" s="119"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="119"/>
-      <c r="L3" s="119"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="119"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="90" t="s">
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B4" s="106" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="129" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="123" t="s">
+      <c r="D4" s="131" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="95" t="s">
+      <c r="E4" s="108" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="108" t="s">
+      <c r="F4" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="109"/>
-      <c r="M4" s="126" t="s">
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="134"/>
+      <c r="M4" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="126"/>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="120"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="125"/>
+      <c r="N4" s="135"/>
+    </row>
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="128"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="133"/>
       <c r="F5" s="26" t="s">
         <v>32</v>
       </c>
@@ -6266,10 +6279,10 @@
       <c r="J5" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="159" t="s">
+      <c r="K5" s="173" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="160"/>
+      <c r="L5" s="174"/>
       <c r="M5" s="26" t="s">
         <v>38</v>
       </c>
@@ -6277,11 +6290,11 @@
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B6" s="24">
         <v>1</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="169" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="30" t="s">
@@ -6305,10 +6318,10 @@
       <c r="J6" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="161" t="s">
+      <c r="K6" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="162" t="s">
+      <c r="L6" s="176" t="s">
         <v>46</v>
       </c>
       <c r="M6" s="29" t="s">
@@ -6318,12 +6331,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B7" s="12">
         <f>B6+1</f>
         <v>2</v>
       </c>
-      <c r="C7" s="117"/>
+      <c r="C7" s="169"/>
       <c r="D7" s="31" t="s">
         <v>112</v>
       </c>
@@ -6345,10 +6358,10 @@
       <c r="J7" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="163" t="s">
+      <c r="K7" s="179" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="164"/>
+      <c r="L7" s="180"/>
       <c r="M7" s="8" t="s">
         <v>113</v>
       </c>
@@ -6356,12 +6369,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B8" s="12">
         <f t="shared" ref="B8:B13" si="0">B7+1</f>
         <v>3</v>
       </c>
-      <c r="C8" s="117"/>
+      <c r="C8" s="169"/>
       <c r="D8" s="31" t="s">
         <v>114</v>
       </c>
@@ -6394,12 +6407,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="12">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C9" s="117"/>
+      <c r="C9" s="169"/>
       <c r="D9" s="31" t="s">
         <v>49</v>
       </c>
@@ -6421,10 +6434,10 @@
       <c r="J9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="129" t="s">
+      <c r="K9" s="181" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="130"/>
+      <c r="L9" s="182"/>
       <c r="M9" s="12" t="s">
         <v>49</v>
       </c>
@@ -6432,12 +6445,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B10" s="12">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C10" s="117"/>
+      <c r="C10" s="169"/>
       <c r="D10" s="31" t="s">
         <v>51</v>
       </c>
@@ -6459,10 +6472,10 @@
       <c r="J10" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K10" s="127" t="s">
+      <c r="K10" s="177" t="s">
         <v>45</v>
       </c>
-      <c r="L10" s="128"/>
+      <c r="L10" s="178"/>
       <c r="M10" s="6" t="s">
         <v>61</v>
       </c>
@@ -6470,12 +6483,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B11" s="12">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C11" s="117"/>
+      <c r="C11" s="169"/>
       <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
@@ -6497,10 +6510,10 @@
       <c r="J11" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K11" s="127" t="s">
+      <c r="K11" s="177" t="s">
         <v>45</v>
       </c>
-      <c r="L11" s="128"/>
+      <c r="L11" s="178"/>
       <c r="M11" s="5" t="s">
         <v>47</v>
       </c>
@@ -6508,12 +6521,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B12" s="12">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C12" s="117"/>
+      <c r="C12" s="169"/>
       <c r="D12" s="31" t="s">
         <v>51</v>
       </c>
@@ -6535,10 +6548,10 @@
       <c r="J12" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="127" t="s">
+      <c r="K12" s="177" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="128"/>
+      <c r="L12" s="178"/>
       <c r="M12" s="5" t="s">
         <v>47</v>
       </c>
@@ -6546,12 +6559,12 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B13" s="25">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C13" s="118"/>
+      <c r="C13" s="170"/>
       <c r="D13" s="32" t="s">
         <v>49</v>
       </c>
@@ -6573,10 +6586,10 @@
       <c r="J13" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="K13" s="144" t="s">
+      <c r="K13" s="171" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="145"/>
+      <c r="L13" s="172"/>
       <c r="M13" s="25" t="s">
         <v>49</v>
       </c>
@@ -6584,7 +6597,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B14" s="27"/>
       <c r="C14" s="27"/>
       <c r="D14" s="28"/>
@@ -6599,7 +6612,7 @@
       <c r="M14" s="27"/>
       <c r="N14" s="27"/>
     </row>
-    <row r="15" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="27" t="s">
         <v>118</v>
       </c>
@@ -6611,100 +6624,100 @@
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="150"/>
+      <c r="K15" s="136"/>
+      <c r="L15" s="136"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="131" t="s">
+    <row r="17" spans="2:16" ht="15" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="C17" s="137" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="133"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="139"/>
       <c r="G17" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="131" t="s">
+      <c r="H17" s="137" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="134"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
-      <c r="L17" s="133"/>
-      <c r="M17" s="131" t="s">
+      <c r="I17" s="140"/>
+      <c r="J17" s="138"/>
+      <c r="K17" s="138"/>
+      <c r="L17" s="139"/>
+      <c r="M17" s="137" t="s">
         <v>122</v>
       </c>
-      <c r="N17" s="134"/>
-      <c r="O17" s="132"/>
-      <c r="P17" s="133"/>
-    </row>
-    <row r="18" spans="2:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="135" t="s">
+      <c r="N17" s="140"/>
+      <c r="O17" s="138"/>
+      <c r="P17" s="139"/>
+    </row>
+    <row r="18" spans="2:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="141" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="136" t="s">
+      <c r="C18" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="137" t="s">
+      <c r="D18" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="E18" s="137" t="s">
+      <c r="E18" s="143" t="s">
         <v>125</v>
       </c>
-      <c r="F18" s="138" t="s">
+      <c r="F18" s="144" t="s">
         <v>126</v>
       </c>
-      <c r="G18" s="139" t="s">
+      <c r="G18" s="145" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="146" t="s">
+      <c r="H18" s="150" t="s">
         <v>128</v>
       </c>
-      <c r="I18" s="147"/>
-      <c r="J18" s="137" t="s">
+      <c r="I18" s="151"/>
+      <c r="J18" s="143" t="s">
         <v>123</v>
       </c>
-      <c r="K18" s="137" t="s">
+      <c r="K18" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="L18" s="138" t="s">
+      <c r="L18" s="144" t="s">
         <v>125</v>
       </c>
-      <c r="M18" s="140" t="s">
+      <c r="M18" s="146" t="s">
         <v>128</v>
       </c>
-      <c r="N18" s="137" t="s">
+      <c r="N18" s="143" t="s">
         <v>123</v>
       </c>
-      <c r="O18" s="137" t="s">
+      <c r="O18" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="P18" s="138" t="s">
+      <c r="P18" s="144" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="135"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="137"/>
-      <c r="E19" s="137"/>
-      <c r="F19" s="138"/>
-      <c r="G19" s="139"/>
-      <c r="H19" s="148"/>
-      <c r="I19" s="149"/>
-      <c r="J19" s="137"/>
-      <c r="K19" s="137"/>
-      <c r="L19" s="138"/>
-      <c r="M19" s="141"/>
-      <c r="N19" s="137"/>
-      <c r="O19" s="137"/>
-      <c r="P19" s="138"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B19" s="141"/>
+      <c r="C19" s="142"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="144"/>
+      <c r="G19" s="145"/>
+      <c r="H19" s="152"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="143"/>
+      <c r="K19" s="143"/>
+      <c r="L19" s="144"/>
+      <c r="M19" s="147"/>
+      <c r="N19" s="143"/>
+      <c r="O19" s="143"/>
+      <c r="P19" s="144"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.4">
       <c r="B20" s="42" t="s">
         <v>109</v>
       </c>
@@ -6719,10 +6732,10 @@
       </c>
       <c r="F20" s="41"/>
       <c r="G20" s="46"/>
-      <c r="H20" s="142" t="s">
+      <c r="H20" s="148" t="s">
         <v>129</v>
       </c>
-      <c r="I20" s="143"/>
+      <c r="I20" s="149"/>
       <c r="J20" s="2">
         <v>3</v>
       </c>
@@ -6745,7 +6758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.4">
       <c r="M21" s="3"/>
     </row>
   </sheetData>
